--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -1965,11 +1965,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>129684</v>
+        <v>40727</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 09/11/1443 | مقتطف: : عد عد أما االله رسول ع ع والسلام والصلاة مد مد ا ا ـ ۱٤٤٤٤۲/۱۲۱۲/۲۵۲۵ خ خ وتار ٤۲۸۲ ۲۸۲٤۷۱۷ ۷۱۷ رقم القضية ع ع ناء و و الثانية ناف ست ست دائرة فلدى ھتفص تسالاب فان فارطأ ةيضقلا ىدلف بالقضية صفتھ سية ا ة و ال رقم ة و ال نوع سم مستأنف المد سعودي ۱۰۱۷۰۹۲۷۳۳ الوطنية ة و ال ز عباس احمد عدنان ضده مستأنف</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 478,757,110، 11,574,017، 450,000، 170 ريال | مقتطف: 25 1 ةيدوعسلا ةيبرعلا ةكلمللا كلا ل 3 الا حا لست _حجججججججججججججججججبببجب ‏ 3 3 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ 97 م 0_0 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: 8١/8./ة44١‏ 3 90 الآ الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 17/ا27801'4</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>129684</v>
+        <v>130737</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 09/11/1443 | مقتطف: : عد عد أما االله رسول ع ع والسلام والصلاة مد مد ا ا ـ ۱٤٤٤٤۲/۱۲۱۲/۲۵۲۵ خ خ وتار ٤۲۸۲ ۲۸۲٤۷۱۷ ۷۱۷ رقم القضية ع ع ناء و و الثانية ناف ست ست دائرة فلدى ھتفص تسالاب فان فارطأ ةيضقلا ىدلف بالقضية صفتھ سية ا ة و ال رقم ة و ال نوع سم مستأنف المد سعودي ۱۰۱۷۰۹۲۷۳۳ الوطنية ة و ال ز عباس احمد عدنان ضده مستأنف</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 367,757,931، 331,882,138، 120,000,000 ريال | تواريخ هجرية: 12/2/1432، 12/3/1433، 12/4/1438، 1431-09-20 | مقتطف: 2 ' ةيدوعسلا ةيبرعلا ةعلمملا | ككل 5 وزارة العدل صك رقم 7١7.551557هغع‏ للم 3 5-0 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ 2 2 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: ١١/”./ه::5١‏ 1 9 ا الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم /١/ا‏ 578175 وتاريخ</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3992,11 +3992,11 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>12265</v>
+        <v>10238</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 1,445 ريال | تواريخ هجرية: 05 / 10 / 1441، 08 / 01 / 1447، 08 / 04 / 1445، 1445 / 04 / 08 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ ھتفص ةيضقلاب فارطأ ةيضقلا ىدلف ةرئاد ذيفنت</t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1440/4/1 | مقتطف: 2 1 ةيدوعسلا ةيبرعلا ةكلمملا كلا 0 سس _ سبل ف محكمة التنفيذ بمحافظة جدة رقم الصفحة: ‎١‏ ا دائرة التنفيذ الثانية تاريخ الصك: ‎١547/.54/١‏ -النطه [س] الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى دائرة التنفيذ الثانية وبناء على القكبية رقم ١812551١/الا2‏ وتاريخ 5/.8./ا55١‏ ه سل ا سس ظل ةيضقلا </t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4055,11 +4055,11 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>3717</v>
+        <v>11451</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ : عد عد أما االله رسول ع ع والسلام والصلاة</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | صكوك: 4630548401 | تواريخ هجرية: 03 / 06 / 1447، 24/04/1446، 25/08/1445 | مقتطف: حصت العربية السعودية صك رقم 87١41١41١1"1/اء‏ مي _-_-_- #6 محكمة الاستئناف بمحافقظة جدة رقم الصفحة: ‎١‏ نا 0 ‏١440/.0/97‎ :كصلا خيرات | لوألا ةيقوقحلا ةرئادلا الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الحقوقية الأولى وبناء على القاضية رقم ‎852591١‏ الالا2 وتاريخ ./5.//ا55١‏ ه با ا</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>مستند مالي</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6547,11 +6547,11 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>5384</v>
+        <v>4657</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>النوع: مستند مالي | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ : عد عد أما االله رسول ع ع والسلام والصلاة</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعدمما كالا هما وزارة العدل ضبط انا لالا 2س -- وير المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 2417814017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎1</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6610,11 +6610,11 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>5778</v>
+        <v>4724</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 241474111 رقمالجلسة: ‎١7‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>5332</v>
+        <v>4627</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2578148017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6736,11 +6736,11 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>5247</v>
+        <v>4602</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 47814117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١55</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -6799,11 +6799,11 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>5240</v>
+        <v>4611</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2478148117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6862,11 +6862,11 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>5179</v>
+        <v>4461</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعدشتا' | ككل 5ه وزارة اتعدل ضبط لكا صدية: لكا لجو2- 4 المحكمة التجارية بجدة رقم الصفحة ‎١ ١+‏ م الدائرة الاولى ‎١‏ رقم القضية: ‏ 15918151107 رقمالجلسة: 5” 02 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6925,11 +6925,11 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>5406</v>
+        <v>4631</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t xml:space="preserve">النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: ةيدوعسلا ةيبرعلا ةعلتتا | ك2 5ه وزارة اتعدل ضبط ل 1 لا 3 0 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى رقم القضية: 159178151117 رقمالجلسة: 7" عد 0 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى الدائرة الاولى وبناء على القضية رقم ا١/ا75‏ 3548© وتاريخ ‎82/١7/١557‏ ه يبي جا ل </t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -6988,11 +6988,11 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>5304</v>
+        <v>4600</v>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعنا ةعدمتل ككل 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 257414117 رقمالجلسة: ‎١/‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7051,11 +7051,11 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>5523</v>
+        <v>4783</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | تواريخ هجرية: 22/10/1444 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ : عد عد أما االله رسول ع ع والسلام والصلاة</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 0 طا ةيدوعسلا ةيبرعلا ةكلمملا كن .وزارة العدل ‎١‏ ‏رزلا ‏ع و7722 يي المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 417814111 رقمالجلسة: ‎١5‏ ساو ل [ه] الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7114,11 +7114,11 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>5475</v>
+        <v>4799</v>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | تواريخ هجرية: 22/10/1444 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلطتا كا 5ه وزارة اتعدل ضبط لالري زلا عل 1-7 رك ماا ص ‏١ ١‎ ةحفصلا مقر ةدجب ةيراجتلا ةمكحملا الدائرة الاولى ‎١‏ رقم القضية: 57414111 رقمالجلسة: ‎١5‏ ساو ل [ه] الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7177,11 +7177,11 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>8628</v>
+        <v>7727</v>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | تواريخ هجرية: 1432-11-07، 20/9/1431، 7/11/1432 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ : عد عد أما االله رسول ع ع والسلام والصلاة</t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلمما كالا هما وزارة العدل ضبط لال انا 0000022222220 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‏ 2141748751107 رقمالجلسة: .”, جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 </t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7240,11 +7240,11 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>8584</v>
+        <v>7399</v>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | تواريخ هجرية: 1432-11-07، 20/9/1431، 7/11/1432 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ : عد عد أما االله رسول ع ع والسل</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: ةيدوعسلا ةيبرعلا ةعلتتا | ك2 5ه وزارة اتعدل ضبط ل 1 لا 3 0 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى رقم القضية: 1591414110 رقمالجلسة: .”» عد 1 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى الدائرة الاولى وبناء على القضية رقم ا١/ا75‏ 3548© وتاريخ ‎82/١7/١557‏ ه ب ببب(؟(؟؛</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>12717</v>
+        <v>11672</v>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | تواريخ هجرية: 08/06/1433، 10/2/1434، 22/02/1432 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ : عد عد أما االله رسول ع ع والسلام والصلاة</t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 120 ريال | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلمما كاك هما وزارة العدل ضبط لاملا ع2 77722 و المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‎14178741١07‏ رقمالجلسة: ‎"١‏ جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 وتاريخ </t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7492,11 +7492,11 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>36236</v>
+        <v>31989</v>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | تواريخ هجرية: 1/1/1445، 1/12/1442، 1/8/1444، 10/11/1444 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ تحتف ا ا ةسل روضحب : : فارطأ ةيض</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | مبالغ: 331,882,138، 120,000,000، 110,672,379، 97,762,042 ريال | تواريخ هجرية: 18/11/1393 | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلطتا كا هما وزارة اتعدل ضبط إل ا ألا حم ممم هك المحكمة التجارية بجدة ‎١‏ رقم الصفحة ‎١ ١+‏ ا قر دائرة الاستئناف الثانية رقم القضية: 2474740107 رقمالجلسة: ‎١‏ 1 إلا الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 4781761117 وتار</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -11733,11 +11733,11 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>129684</v>
+        <v>130408</v>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 09/11/1443 | مقتطف: : عد عد أما االله رسول ع ع والسلام والصلاة مد مد ا ا ـ ۱٤٤٤٤۲/۱۲۱۲/۲۵۲۵ خ خ وتار ٤۲۸۲ ۲۸۲٤۷۱۷ ۷۱۷ رقم القضية ع ع ناء و و الثانية ناف ست ست دائرة فلدى ھتفص تسالاب فان فارطأ ةيضقلا ىدلف بالقضية صفتھ سية ا ة و ال رقم ة و ال نوع سم مستأنف المد سعودي ۱۰۱۷۰۹۲۷۳۳ الوطنية ة و ال ز عباس احمد عدنان ضده مستأنف</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 367,757,931، 331,882,138، 120,000,000 ريال | تواريخ هجرية: 10/ 03/ 1445، 12/2/1432، 12/3/1433، 12/4/1438 | مقتطف: 8 ةيدوعسلا ةيبرعلاةكلمملا فت ملك وزارة العدل صك رقم 7١551557١.7هغع‏ لتو + اشر ا المحكمة التجارية يجدة رقم الصفحة: ‎١‏ 0 دائرة الاستئناف الثانية تاريخ الصك: ‎١:44/.”/١١‏ 0-0 5 5 الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 1١/ا1‏ 2758752 وتاريخ 8؟</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -1776,11 +1776,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>906</v>
+        <v>33174</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | صكوك: 4431025114 | مقتطف: : عد عد أما االله رسول ع ع والسلام والصلاة مد مد ا ا ـ ۱٤٤٤٤۲/۱۲۱۲/۲۵۲۵ خ خ وتار ٤۲۸۲ ۲۸۲٤۷۱۷ ۷۱۷ رقم القضية ع ع ناء و و و و الدائرة فلدى ھتفص ةيضقلاب فارطأ ةيضقلا ىدلف دم ھيلع ةقتاع حيدمحم عدمحم ا يزار لا و ة ةينطولا ۷٤۸٦۵۰۷۰۰۱ يدوعس دم ھيلع ناندع دمحا سابع ز لا و ة ةينطولا ۳۳۷۲۹۰۷۱۰۱ يدوعس دملا مس</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية | مبالغ: 372,426,828، 368,757,931، 120,000,000، 78,000,000 ريال | تواريخ هجرية: 2/11/1443، 20/9/1431 | مقتطف: ةيدوعسلا ةيبرعلا ةكلمملا رك - 50 ل يد م ات 0 0 53 ا 5 3 5 ا - المحكمة التجارية بجدة رقم الصفحة: ‎١‏ 2 2 الدائرة الاوى تاريخ الصك: ‎١5458/.١/.١‏ 1 9 الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى الدائرة الاولى وبناء على القضية رقم /1١/ا1‏ 275875 وتاريخ 17/178١/5517اه‏ كا آ#جآآجط!ط!|/!|!|!|!|آ</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>835</v>
+        <v>29914</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | مقتطف: 9-24 تاقفرملا و تاركذملا CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner CamScanner &lt;https://v3.camscanner.com/user/download&gt; &lt;https://v3.camscanner.com/user/download&gt; &lt;https://v3.camscanner.com</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 8,849,447,678، 184,887,445، 8,844,470، 87,445 ريال | تواريخ هجرية: 1/17/1460 | مقتطف: رم اذخ ريسرطذلء دنه لجيو ف ةدجب ةيرادإلا ةمكحملا ‏١/11‎ يوني فنك ةرشع ةعبسا ةئلا با منل) ترو ظ حتكه رقم ‎١/17/1460‏ لعام ١؟4اه‏ ظ 32 ا لقتصصسن رقم 4ة/س0ة/ "اق ملقم 1ه وار فهر ا اق لهام ردند” المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد ظ عباس زيسي ظ | ضد / أسامة بن أح</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -4976,11 +4976,11 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>10451</v>
+        <v>10328</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني | قضايا: 42824717 | صكوك: 4431025114، 4530241622 | تواريخ هجرية: 01 / 01 / 1445، 13 / 03 / 1445، 13 /3/ 1445، 1438 / 10 / 25 | مقتطف: ةدجب فانئتسلاا ةمکحمب ةیناثلا ةیفانئتسلاا ةرئادلا ءاضعأو سیئر ةلیضفلا باحصأ الله مھظفح ، ھتاکربو الله ةمحرو مکیلع ملاسلا ) مقر مکحلا يف تاضقانتلا مھأ نایبب ةیقاحلإ ةرکذم :عوضوملا ٤٤٣١٠٢٥١١٤ خیراتو ( ٠١ / ٠١ / ١٤٤٥ ـھ ) مقر ةیضقلا يف ٤٢٨٢٤٧١٧ خیراتو ( ٢٥ / ١٢ / ١٤٤٢ ةمکحملاب ةیناثلا فانئتسلاا ةرئاد ن</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | مقتطف: أصحاب الفضيلة رئيس وأعضاء الدائرة الاستئنافية الثانية بمحكمة الاستئناف بجدة حفظهم الله السلام عليكم ورحمة الله وبركاته الموضوع: مذكرة إلحاقية ببيان أهم التناقضات في الحكم رقم (5 ‎575١٠١751١١‏ 5) وتاريخ ١0/١555/0١اه‏ في القضية رقم ‎)577517١1(‏ وتاريخ ‎557/1١7/75‏ ١ه‏ والمؤيد من دائرة الاستئناف الثاني</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5543,11 +5543,11 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>1923</v>
+        <v>7297</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 20,043,862 ريال | مقتطف: تعقيب الملتمس (أسامة زيني) جوابا على المذكرة المقدمة من المستلمَس ضدهما (عدنان زيني وعاتقة الحرازي) بشأن صك حكم الاستئناف رقم 4530241622 وتاريخ 13/03/1445هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة. أبرز ما ورد: - أولا: أن الادعاء بملكية عائلية للحصص دفع مردود؛ الدعوى المقامة تتعلق ف</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف | صكوك: 4530241622 | مبالغ: 135، 120 ريال | تواريخ هجرية: 1445/ 08/16 | مقتطف: ١ ١ ١ .: 1445/ 08/16 : ‏التاريخ‎ أصحاب الفضيلة/ رئيس وأعضاء الدائرة الثانية بمحكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته» وبعد: الموضوع مذكرة بالرد والتعقيب على جواب الملتمس ضدهما على لائحة التماس إعادة النظر المقدمة من موكلي على الحكم الصادر من دائرتكم الموقرة با</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7366,11 +7366,11 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>2553</v>
+        <v>11401</v>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | مبالغ: 372,426,828، 368,757,931، 335,184,145، 97,762,042 ريال | تواريخ هجرية: 08/06/1433، 10/2/1434، 22/02/1432، 24-11-1444 | مقتطف: أسامة بن احمد بن عباس زيني ضبط - المحكمة التجارية بجدة - الدائرة - رقم القضية 42824717 - رقم الجلسة 31 - عدد الصفحات 5 .يفقثلا فيفر ،فرشم نب يلع ،يمايلا حلاص ،جوخ مازع ،يريدسلا ناميلس ،يناطحقلا رصان دجام ناطلس ،يبلعثلا زاوف دمحم ،عئاش يلالب ملاس هللادبع ،يثراحلا فلخ قراط :نوماحم .هليكوو يريطملا دعس </t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 372,426,828، 120 ريال | تواريخ هجرية: 10/ 2/ 1438 | مقتطف: 2 ةيدوعسلا ةيبرعنا ةعدمتل ككل 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 247814017 رقمالجلسة: ام سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -1780,7 +1780,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية | مبالغ: 372,426,828، 368,757,931، 120,000,000، 78,000,000 ريال | تواريخ هجرية: 2/11/1443، 20/9/1431 | مقتطف: ةيدوعسلا ةيبرعلا ةكلمملا رك - 50 ل يد م ات 0 0 53 ا 5 3 5 ا - المحكمة التجارية بجدة رقم الصفحة: ‎١‏ 2 2 الدائرة الاوى تاريخ الصك: ‎١5458/.١/.١‏ 1 9 الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى الدائرة الاولى وبناء على القضية رقم /1١/ا1‏ 275875 وتاريخ 17/178١/5517اه‏ كا آ#جآآجط!ط!|/!|!|!|!|آ</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية | مبالغ: 372,426,828، 368,757,931، 120,000,000، 78,000,000 ريال | تواريخ هجرية: 2/11/1443، 20/9/1431 | مقتطف: كر المملكة العربية السعودية - 50 ل يد م ات 0 0 53 ا 5 3 5 ا - المحكمة التجارية بجدة رقم الصفحة: ‎١‏ 2 2 الدائرة الاوى تاريخ الصك: ‎١5458/.١/.١‏ 1 9 الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى الدائرة الاولى وبناء على القضية رقم /1١/ا1‏ 275875 وتاريخ 17/178١/5517اه‏ لد قللطراق القضية ل آ|!|</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1902,11 +1902,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1148</v>
+        <v>13683</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4630548401 | مقتطف: أسامھ بن احمد بن عباس زيني صك حكم نهائي رقم 4630548401 وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، القاضي بعدم قبول التماس إعادة النظر المقدم من أسامة أحمد عباس زيني، المقيد برقم (4611037394) وتاريخ 02/06/1446هـ، على الحكم الصادر في الدعوى رقم 42824717. المستأنف: عد</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | مقتطف: 83 المملكة العربية السعودية ها وزارة العدل صك رقم ‎557.4584.١‏ ‏1 ‏ج22 ‎١ 5 0‏ 0 ةرجا 5 0 الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على اللنقضية رقم /ا1١/ا1‏ 278515 وتاريخ 17/78١/557١1ه‏ ل أطراق القضية ‏ 2333332323327 6س ييل ا عدنان احمد عباس زيني الهوية الو</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 367,757,931، 331,882,138، 120,000,000 ريال | تواريخ هجرية: 12/2/1432، 12/3/1433، 12/4/1438، 1431-09-20 | مقتطف: 2 ' ةيدوعسلا ةيبرعلا ةعلمملا | ككل 5 وزارة العدل صك رقم 7١7.551557هغع‏ للم 3 5-0 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ 2 2 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: ١١/”./ه::5١‏ 1 9 ا الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم /١/ا‏ 578175 وتاريخ</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 367,757,931، 331,882,138، 120,000,000 ريال | تواريخ هجرية: 12/2/1432، 12/3/1433، 12/4/1438، 1431-09-20 | مقتطف: 2 لكك | المملعة العربية السعودية ' 5 وزارة العدل صك رقم 7١7.551557هغع‏ للم 3 5-0 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ 2 2 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: ١١/”./ه::5١‏ 1 9 ا الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم /١/ا‏ 578175 وتاريخ</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>النوع: وكالة | الأطراف: عاتقة الحرازي | تواريخ هجرية: 1445/03/19، 1446/03/19 | مقتطف: : فارطلأا ةفصلا ة و لا مقر ة و لا عون ةيس ا مسلاا فرطلا \# هسفن نع ةلاصأ ١٠٠٧٠٥٦٨٤٧ ي دم ل ةيدوعس يزار ا عدمحم يدمحم هقتاع ل وم ١ هسفن نع ةلاصأ النطاق : ٢ وكيل محمد فواز بن من الثع سعودي ل مد ي ١٠٩٨٩٠٨٢٧٨ ميلس لا و ملاتسلاا - كلذ بلطتي اميف عيقوتلاو ةمزلالا تاءارجلإا عيمج ءا إو ةقلاعلا تاذ تا ا عيمج</t>
+          <t>النوع: وكالة | الأطراف: عاتقة الحرازي | تواريخ هجرية: 1445/03/19، 1446/03/19 | مقتطف: : فارطلأا أصالة عن نفسه ١ مو ل عاتقه محمدي محمدع ا رازي سعودية ل مد ي ١٠٠٧٠٥٦٨٤٧ أصالة عن نفسه #\ الطرف االسم ا سية نوع ال و ة رقم ال و ة الصفة النطاق : ٢ وكيل محمد فواز بن من الثع سعودي ل مد ي ١٠٩٨٩٠٨٢٧٨ ميلس لا و ملاتسلاا - كلذ بلطتي اميف عيقوتلاو ةمزلالا تاءارجلإا عيمج ءا إو ةقلاعلا تاذ تا ا عيمج</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446، 1,769,886,051 ريال | تواريخ هجرية: 1411/4/11، 1432/12/1 | مقتطف: ةيدوعسلا ةيبرعلا ةكلمملا يحلا زرخلا هللا مسب ةدجب ةيرادإلا ةمكحملا ملاظملا ناويد ةرشع ةعباسلا ةرئادلا في رقم ٢/١٧/١٨٥ لعام ١٤٣٢هـ القضيتين رقم ٢/٥٧٩٨/ق لعام ١٤٣١ هـ ورقم ٢/١٣٧٥/ق لعام ١٤٣٢هـ المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد عباس زيني ضد / أسامة بن أحمد بن </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446، 1,769,886,051 ريال | تواريخ هجرية: 1411/4/11، 1432/12/1 | مقتطف: المملكة العربية السعودية يحلا زرخلا هللا مسب ةدجب ةيرادإلا ةمكحملا ملاظملا ناويد ةرشع ةعباسلا ةرئادلا في رقم ٢/١٧/١٨٥ لعام ١٤٣٢هـ القضيتين رقم ٢/٥٧٩٨/ق لعام ١٤٣١ هـ ورقم ٢/١٣٧٥/ق لعام ١٤٣٢هـ المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد عباس زيني ضد / أسامة بن أحمد بن </t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أحمد زيني (المورّث)، عاتقة الحرازي | صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219 ريال | مقتطف: 5149 قباــسلا تحميل إخطار بمطالبة مالية 440300010192 مقر ةيلاملا ةبلاطملا ـ بلطلا مدقمل ةيصخشلا تانايبلا الاسم: محمد بن فواز بن منير الثعلي 1098908278 :ةماقإلا وأ ةيوهلا مقر ةلاكولا تانايب اسم الموكل: عدنان احمد عباس زيني رقم هوية الموكل: 1017092733 ةيلاملا ةبلاطملا تانايب 556355663 لاوجلا مقر ـ 100</t>
+          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أحمد زيني (المورّث)، عاتقة الحرازي | صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219 ريال | مقتطف: 5149 قباــسلا تحميل إخطار بمطالبة مالية 440300010192 مقر ةيلاملا ةبلاطملا ـ بلطلا مدقمل ةيصخشلا تانايبلا الاسم: محمد بن فواز بن منير الثعلي رقم الهوية أو الإقامة: 1098908278 ةلاكولا تانايب اسم الموكل: عدنان احمد عباس زيني رقم هوية الموكل: 1017092733 ةيلاملا ةبلاطملا تانايب 556355663 لاوجلا مقر ـ 100</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1440/4/1 | مقتطف: 2 1 ةيدوعسلا ةيبرعلا ةكلمملا كلا 0 سس _ سبل ف محكمة التنفيذ بمحافظة جدة رقم الصفحة: ‎١‏ ا دائرة التنفيذ الثانية تاريخ الصك: ‎١547/.54/١‏ -النطه [س] الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى دائرة التنفيذ الثانية وبناء على القكبية رقم ١812551١/الا2‏ وتاريخ 5/.8./ا55١‏ ه سل ا سس ظل ةيضقلا </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1440/4/1 | مقتطف: 2 الك المملكة العربية السعودية 1 0 سس _ سبل ف محكمة التنفيذ بمحافظة جدة رقم الصفحة: ‎١‏ ا دائرة التنفيذ الثانية تاريخ الصك: ‎١547/.54/١‏ -النطه [س] الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى دائرة التنفيذ الثانية وبناء على القكبية رقم ١812551١/الا2‏ وتاريخ 5/.8./ا55١‏ ه ل أطراق القضية لظ </t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | صكوك: 4630548401 | تواريخ هجرية: 03 / 06 / 1447، 24/04/1446، 25/08/1445 | مقتطف: حصت العربية السعودية صك رقم 87١41١41١1"1/اء‏ مي _-_-_- #6 محكمة الاستئناف بمحافقظة جدة رقم الصفحة: ‎١‏ نا 0 ‏١440/.0/97‎ :كصلا خيرات | لوألا ةيقوقحلا ةرئادلا الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الحقوقية الأولى وبناء على القاضية رقم ‎852591١‏ الالا2 وتاريخ ./5.//ا55١‏ ه با ا</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | صكوك: 4630548401 | تواريخ هجرية: 03 / 06 / 1447، 24/04/1446، 25/08/1445 | مقتطف: حصت العربية السعودية صك رقم 87١41١41١1"1/اء‏ مي _-_-_- #6 محكمة الاستئناف بمحافقظة جدة رقم الصفحة: ‎١‏ نا 0 ‏١440/.0/97‎ :كصلا خيرات | لوألا ةيقوقحلا ةرئادلا الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الحقوقية الأولى وبناء على القاضية رقم ‎852591١‏ الالا2 وتاريخ ./5.//ا55١‏ ه لل د</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: أسامة زيني | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني ،لدعلا ةرازول ةينو كللإا تامد ا ع ةقيثولا ة نم ققحتلا نكم و ، قيثوتلا تامد ي و كللإا ماظنلا نم ةقيثولا هذ تردص : فارطلأا ةفصلا ة و لا مقر ة و لا عون ةيس ا مسلاا فرطلا \# هسفن نع ةلاصأ ١٠٠٨٠١٧٣٠١ ي دم ل يدوعس ز سابع نب د</t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: أسامة زيني | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني ،لدعلا ةرازول ةينو كللإا تامد ا ع ةقيثولا ة نم ققحتلا نكم و ، قيثوتلا تامد ي و كللإا ماظنلا نم ةقيثولا هذ تردص : فارطلأا أصالة عن نفسه ١ مو ل أسامه بن احمد بن عباس ز سعودي ل مد ي ١٠٠٨٠١٧٣٠١ أصالة عن نفسه #\ الطرف االسم </t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5165,11 +5165,11 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1965</v>
+        <v>9238</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 79,924,901 ريال | مقتطف: الموضوع: مذكرة إلحاقية على الحكم النهائي رقم (4530241622) وتاريخ 13/03/1445هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، المقدمة من الملتمس/ أسامة، ضد المستلمَس ضدهم عاتقة (الوالدة) وعدنان (الشقيق) وآخرون، بشأن التماس إعادة النظر في صك الحكم. ملخص دعوى المدعين (عدنان ووالدته عاتقة وآخ</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | صكوك: 4530241622 | مبالغ: 450,000، 170، 120 ريال | مقتطف: السلام عليكم ورحمه الله وبركاته»: وبعد الموضوع/ مذكرة إلحاقية بشأن التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم( 4530241622) بتاريخ 1445/03/13ه والمقدم من الملتمس/أسامة زيني ضد الملتمس ضدهم وهما شقيقه عدنان ووالدته عاتقة إشارة لموضوع الدعوى والحك</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | مقتطف: == ةيدوعسلا ةيبرعلا ةكلمملا ،لدعلا ةرازو - ةلاكو ةقيثو == .لدعلا ةرازول ةينورتكلإلا تامدخلا ربع اهتحص نم ققحتلا نكميو ،قيثوتلا تامدخو ينورتكلإلا ماظنلا نم ةقيثولا هذه تردص :فارطألا 1 - الموكل: أسامة بن أحمد بن عباس زيني، سعودي، رقم هوية 1008017301، أصالة عن نفسه. 2 - الوكيل: علي بن مشرف بن مفرح بن ر</t>
+          <t>النوع: مذكرة قضائية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | مقتطف: == وثيقة وكالة - وزارة العدل، المملكة العربية السعودية == .لدعلا ةرازول ةينورتكلإلا تامدخلا ربع اهتحص نم ققحتلا نكميو ،قيثوتلا تامدخو ينورتكلإلا ماظنلا نم ةقيثولا هذه تردص :فارطألا 1 - الموكل: أسامة بن أحمد بن عباس زيني، سعودي، رقم هوية 1008017301، أصالة عن نفسه. 2 - الوكيل: علي بن مشرف بن مفرح بن ر</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: أسامة زيني | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 23-09-1445 | مقتطف: .لدعلا ةرازول ةينورتكلإلا تامدخلا ربع ةقيثولا ةحص نم ققحتلا نكميو ،قيثوتلا تامدخ نمو ينورتكلإلا ماظنلا نم ةقيثولا هذه تردص ةيدوعسلا ةيبرعلا ةكلمملا - لدعلا ةرازو - ةلاكو ةقيثو ةدمتعم :ةلاكولا ةلاح - ةينورتكلإلا تالاكولا تامدخ :فارطألا الطرف الموكل: أسامة بن احمد بن عباس زيني - سعودي - رقم الهوية 100</t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 23-09-1445 | مقتطف: .لدعلا ةرازول ةينورتكلإلا تامدخلا ربع ةقيثولا ةحص نم ققحتلا نكميو ،قيثوتلا تامدخ نمو ينورتكلإلا ماظنلا نم ةقيثولا هذه تردص وثيقة وكالة - وزارة العدل - المملكة العربية السعودية ةدمتعم :ةلاكولا ةلاح - ةينورتكلإلا تالاكولا تامدخ :فارطألا الطرف الموكل: أسامة بن احمد بن عباس زيني - سعودي - رقم الهوية 100</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1434/02/10، 1445/03/13 | مقتطف: يماحملا بتكم دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدصلا ةرازو (٢٣/١٤٠ ) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم مسودة) Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 ال</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1434/02/10، 1445/03/13 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدصلا ةرازو (٢٣/١٤٠ ) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم مسودة) Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 ال</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | تواريخ هجرية: 1431/10/16 | مقتطف: يماحملا بتكم دشار وبأ يماس دلاخ للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا Law office of Khalid Sami Abu Rashed (AA) بسم الله الرحمن الرحيم Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | تواريخ هجرية: 1431/10/16 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا Law office of Khalid Sami Abu Rashed (AA) بسم الله الرحمن الرحيم Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | مقتطف: ريماني. Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 23/HD يماحملا بتكم دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الر</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | مقتطف: ريماني. Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 23/HD مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الر</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: يماحملا بتكم دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم ٢١/١</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم ٢١/١</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: يماحملا بتكم دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT NO.: 310041499400003 ( ةيصخشلا </t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT NO.: 310041499400003 ( ةيصخشلا </t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعدمما كالا هما وزارة العدل ضبط انا لالا 2س -- وير المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 2417814017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎1</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك اممدعة العربية السعودية هما وزارة العدل ضبط انا لالا 2س -- وير المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 2417814017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎1</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 241474111 رقمالجلسة: ‎١7‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 241474111 رقمالجلسة: ‎١7‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2578148017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2578148017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 47814117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١55</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 47814117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١55</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا علمت كالا 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2478148117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2478148117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعدشتا' | ككل 5ه وزارة اتعدل ضبط لكا صدية: لكا لجو2- 4 المحكمة التجارية بجدة رقم الصفحة ‎١ ١+‏ م الدائرة الاولى ‎١‏ رقم القضية: ‏ 15918151107 رقمالجلسة: 5” 02 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 لكك | 'اتشدعة العربية السعودية 5ه وزارة اتعدل ضبط لكا صدية: لكا لجو2- 4 المحكمة التجارية بجدة رقم الصفحة ‎١ ١+‏ م الدائرة الاولى ‎١‏ رقم القضية: ‏ 15918151107 رقمالجلسة: 5” 02 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: ةيدوعسلا ةيبرعلا ةعلتتا | ك2 5ه وزارة اتعدل ضبط ل 1 لا 3 0 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى رقم القضية: 159178151117 رقمالجلسة: 7" عد 0 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى الدائرة الاولى وبناء على القضية رقم ا١/ا75‏ 3548© وتاريخ ‎82/١7/١557‏ ه يبي جا ل </t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2ك | اتتلعة العربية السعودية 5ه وزارة اتعدل ضبط ل 1 لا 3 0 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى رقم القضية: 159178151117 رقمالجلسة: 7" عد 0 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى الدائرة الاولى وبناء على القضية رقم ا١/ا75‏ 3548© وتاريخ ‎82/١7/١557‏ ه ل د وأطرا</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعنا ةعدمتل ككل 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 257414117 رقمالجلسة: ‎١/‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 لكك لتمدعة انعربية السعودية 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 257414117 رقمالجلسة: ‎١/‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 0 طا ةيدوعسلا ةيبرعلا ةكلمملا كن .وزارة العدل ‎١‏ ‏رزلا ‏ع و7722 يي المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 417814111 رقمالجلسة: ‎١5‏ ساو ل [ه] الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎14/١5/</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 0 المملكة العربية السعودية اط كن .وزارة العدل ‎١‏ ‏رزلا ‏ع و7722 يي المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 417814111 رقمالجلسة: ‎١5‏ ساو ل [ه] الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلطتا كا 5ه وزارة اتعدل ضبط لالري زلا عل 1-7 رك ماا ص ‏١ ١‎ ةحفصلا مقر ةدجب ةيراجتلا ةمكحملا الدائرة الاولى ‎١‏ رقم القضية: 57414111 رقمالجلسة: ‎١5‏ ساو ل [ه] الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 اك اتطلعة العربية السعودية 5ه وزارة اتعدل ضبط لالري زلا عل 1-7 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ ص اام كر الدائرة الاولى ‎١‏ رقم القضية: 57414111 رقمالجلسة: ‎١5‏ ساو ل [ه] الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلمما كالا هما وزارة العدل ضبط لال انا 0000022222220 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‏ 2141748751107 رقمالجلسة: .”, جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك امملعة العربية السعودية هما وزارة العدل ضبط لال انا 0000022222220 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‏ 2141748751107 رقمالجلسة: .”, جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 </t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: ةيدوعسلا ةيبرعلا ةعلتتا | ك2 5ه وزارة اتعدل ضبط ل 1 لا 3 0 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى رقم القضية: 1591414110 رقمالجلسة: .”» عد 1 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى الدائرة الاولى وبناء على القضية رقم ا١/ا75‏ 3548© وتاريخ ‎82/١7/١557‏ ه ب ببب(؟(؟؛</t>
+          <t xml:space="preserve">النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2ك | اتتلعة العربية السعودية 5ه وزارة اتعدل ضبط ل 1 لا 3 0 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى رقم القضية: 1591414110 رقمالجلسة: .”» عد 1 ل الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى الدائرة الاولى وبناء على القضية رقم ا١/ا75‏ 3548© وتاريخ ‎82/١7/١557‏ ه لل طلطراق </t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 120 ريال | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلمما كاك هما وزارة العدل ضبط لاملا ع2 77722 و المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‎14178741١07‏ رقمالجلسة: ‎"١‏ جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 وتاريخ </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 120 ريال | مقتطف: 2 كاك امملعة العربية السعودية هما وزارة العدل ضبط لاملا ع2 77722 و المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‎14178741١07‏ رقمالجلسة: ‎"١‏ جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 وتاريخ </t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 372,426,828، 120 ريال | تواريخ هجرية: 10/ 2/ 1438 | مقتطف: 2 ةيدوعسلا ةيبرعنا ةعدمتل ككل 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 247814017 رقمالجلسة: ام سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 372,426,828، 120 ريال | تواريخ هجرية: 10/ 2/ 1438 | مقتطف: 2 لكك لتمدعة انعربية السعودية 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 247814017 رقمالجلسة: ام سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 97,762,042، 27,932,012، 450,000 ريال | تواريخ هجرية: 02-12-1444، 12/5/1438 | مقتطف: أسامة بن احمد بن عباس زيني ضبط - المحكمة التجارية بجدة - الدائرة - رقم القضية 42824717 - رقم الجلسة 32 - عدد الصفحات 4 .يفقثلا ءازج دشار فيفر ،فرشم نب يلع ،يمايلا بلاط حلاص ،جوخ ميهاربا لصيف مازع ،يبلعثلا زاوف دمحم ،عئاش يلالب ملاس هللادبع ،يناطحقلا رصان دجام ناطلس ،يريدسلا ناميلس دمحم ناميلس ،يثراح</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 97,762,042، 27,932,012، 450,000 ريال | تواريخ هجرية: 02-12-1444، 12/5/1438 | مقتطف: أسامة بن احمد بن عباس زيني ضبط - المحكمة التجارية بجدة - الدائرة - رقم القضية 42824717 - رقم الجلسة 32 - عدد الصفحات 4 أطراف القضية: المدعي عدنان احمد عباس زيني (هوية 1017092733). المدعى عليه اسامة احمد عباس زيني (هوية 1008017301). المطعي/2003 عمر سعود سعد المطيري ووكيله. محامون: طارق خلف الحارثي، س</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | مبالغ: 331,882,138، 120,000,000، 110,672,379، 97,762,042 ريال | تواريخ هجرية: 18/11/1393 | مقتطف: 2 ةيدوعسلا ةيبرعلا ةعلطتا كا هما وزارة اتعدل ضبط إل ا ألا حم ممم هك المحكمة التجارية بجدة ‎١‏ رقم الصفحة ‎١ ١+‏ ا قر دائرة الاستئناف الثانية رقم القضية: 2474740107 رقمالجلسة: ‎١‏ 1 إلا الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 4781761117 وتار</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | مبالغ: 331,882,138، 120,000,000، 110,672,379، 97,762,042 ريال | تواريخ هجرية: 18/11/1393 | مقتطف: 2 اك اتطلعة العربية السعودية هما وزارة اتعدل ضبط إل ا ألا حم ممم هك المحكمة التجارية بجدة ‎١‏ رقم الصفحة ‎١ ١+‏ ا قر دائرة الاستئناف الثانية رقم القضية: 2474740107 رقمالجلسة: ‎١‏ 1 إلا الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 4781761117 وتار</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 20,000، 17,000، 1,000 ريال | تواريخ هجرية: 1434/06/30، 1434/11/24، 1454/05/9 | مقتطف: ===== ملف داخلي: 1434/1434 fil no-14- inv 1422.pdf ===== [صفحة 1 - OCR] ‏Co Sons Guthmi AL 0. Mohd.‎ يمثقلا ديبع دمحم ءانبا ةكرش ‏QS Quotation‎ يمثقلا ديبع دمحم ءانبا ةكرش ةيلحتلا:عرفلا التاريخ ‎Date: 1 / Verte Vive‏ أسم العميل: الشيخاحمدزيني ا ‎Clients‏ ‏Clients‎ ظلي طق للمعلم : ليمعلا مقر‏ ‏رقم ال</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 20,000، 17,000، 1,000 ريال | تواريخ هجرية: 1434/06/30، 1434/11/24، 1454/05/9 | مقتطف: ===== ملف داخلي: 1434/1434 fil no-14- inv 1422.pdf ===== [صفحة 1 - OCR] شركة ابناء محمد عبيد القثمي ‎Mohd. 0. AL Guthmi Sons Co‏ شركة ابناء محمد عبيد القثمي ‎Quotation QS‏ ةيلحتلا:عرفلا التاريخ ‎Date: 1 / Verte Vive‏ أسم العميل: الشيخاحمدزيني ا ‎Clients‏ ‏Clients‎ ظلي طق للمعلم : ليمعلا مقر‏ ‏رقم ال</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -8888,11 +8888,11 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>2022</v>
+        <v>40727</v>
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530828230 | تواريخ هجرية: 13/03/1445، 1445/08/25، 25-08-1445 | مقتطف: أسامة بن احمد بن عباس زيني أسامة بن احمد بن عباس زيني حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس [محكمة الاستئناف - الدائرة الثانية - المحكمة التجارية بجدة] صك رقم ٤٥٣٠٨٢٨٢٣٠ - تاريخ الصك ١٤٤٥/٠٨/٢٥ القضية رقم 42824717 - دائرة الاستئناف الثانية بجدة. :ةيضقلا فارطأ - مستأنف (المد</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 478,757,110، 11,574,017، 450,000، 170 ريال | مقتطف: 25 1 ةيدوعسلا ةيبرعلا ةكلمللا كلا ل 3 الا حا لست _حجججججججججججججججججبببجب ‏ 3 3 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ 97 م 0_0 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: 8١/8./ة44١‏ 3 90 الآ الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 17/ا27801'4</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: ءاضقلل ىلعألا سلجملا :. ةينورتكلإلا ىوكشلا ةمدخ ةينوتركللإا نييز سابع نب دمحا نب هماسأ ابحرم بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا ةيسيئرلا لولأا مسلاا زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية هسفن نع</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: ءاضقلل ىلعألا سلجملا :. ةينورتكلإلا ىوكشلا ةمدخ ةينوتركللإا نييز سابع نب دمحا نب هماسأ ابحرم بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا ةيسيئرلا لولأا مسلاا زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة ع</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ىوكشلا ةدعاسملا ó°¡3⁄4 تيانايب ó°­μ ةيسيئرلا ó° خي راتلا ةفصلا ةيضقلا مقر رقم الشكوى 1445/06/18 هسفن ن</t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ىوكشلا ةدعاسملا ó°¡3⁄4 تيانايب ó°­μ ةيسيئرلا ó° خي راتلا ةفصلا رقم القضية رقم الشكوى 1445/06/18 أصالة </t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | تواريخ هجرية: 1445/04/30 | مقتطف: ءاضقلا ءالطلا مرحبا أسامه بن احمد بن عباس زيني طلباتي ةينورتكلإلا ىوكشلا ةمدخ ةيسيئرلا طلباتي طلبات غير مكتملة بياناتي 2 للمساعدة ن خروج رقم الشكوى ةيضقلا عون رقم القضية الصفة 230747621 42824717 أصالة عن نفسه تاريخ الشكوى 1445/04/30 عرض</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | تواريخ هجرية: 1445/04/30 | مقتطف: ءاضقلا ءالطلا مرحبا أسامه بن احمد بن عباس زيني طلباتي ةينورتكلإلا ىوكشلا ةمدخ ةيسيئرلا طلباتي طلبات غير مكتملة بياناتي 2 للمساعدة ن خروج رقم الشكوى نوع القضية رقم القضية الصفة 230747621 42824717 أصالة عن نفسه تاريخ الشكوى 1445/04/30 عرض</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01، 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ةساردلا ديق بلطلا ó° °ó بيانات مقدم الشكوى خي راتلا 1445/01/05 خي راتلا 1445/06/18 خي راتلا 1446/04/27 ةفصلا هسفن نع ةلاص</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01، 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ةساردلا ديق بلطلا ó° °ó بيانات مقدم الشكوى خي راتلا 1445/01/05 خي راتلا 1445/06/18 خي راتلا 1446/04/27 ةفصلا أصالة عن نفس</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/06/19 | مقتطف: 5/26/24, 9:48 AM دیعاوملا ماظن https://appointments.scj.gov.sa/appointment/appointmentrequest/e2020455-ca34-4f3e-b67c-960e07a223a1 ق 1/2 5/26/24, 9:48 AM دیعاوملا ماظن طلب رقم معلومات مقدم الطلب °ó بلطلا ليصافت دعوملا ببس شأن قضايئ بلطلا مدقم ةفص هسفن نع ةلاصأ ةيضقلا مقر 42824717 رقم الشكوى 23074762</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/06/19 | مقتطف: 5/26/24, 9:48 AM دیعاوملا ماظن https://appointments.scj.gov.sa/appointment/appointmentrequest/e2020455-ca34-4f3e-b67c-960e07a223a1 ق 1/2 5/26/24, 9:48 AM دیعاوملا ماظن طلب رقم معلومات مقدم الطلب °ó بلطلا ليصافت دعوملا ببس شأن قضايئ بلطلا مدقم ةفص أصالة عن نفسه رقم القضية 42824717 رقم الشكوى 23074762</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا لولأا مسلاا ةينورتكللإا ىوكشلا ةمدخ ينيز سابع نب دمحا نب هماسأ ابحرم زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية هسفن نع ةلاصأ ةيدوعسلا ةيبرعلا ةكلمملا 0556355663 1008017301 ةيضقلا ليصافت ةرئادلا / ةمكحملا ةيضقلا عون ىلولاا</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا لولأا مسلاا ةينورتكللإا ىوكشلا ةمدخ ينيز سابع نب دمحا نب هماسأ ابحرم زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 ةيضقلا ليصافت ةرئادلا / ةمكحملا ةيضقلا عون ىلولاا</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 367,757,931، 331,882,138، 120,000,000 ريال | تواريخ هجرية: 10/ 03/ 1445، 12/2/1432، 12/3/1433، 12/4/1438 | مقتطف: 8 ةيدوعسلا ةيبرعلاةكلمملا فت ملك وزارة العدل صك رقم 7١551557١.7هغع‏ لتو + اشر ا المحكمة التجارية يجدة رقم الصفحة: ‎١‏ 0 دائرة الاستئناف الثانية تاريخ الصك: ‎١:44/.”/١١‏ 0-0 5 5 الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 1١/ا1‏ 2758752 وتاريخ 8؟</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 367,757,931، 331,882,138، 120,000,000 ريال | تواريخ هجرية: 10/ 03/ 1445، 12/2/1432، 12/3/1433، 12/4/1438 | مقتطف: المملكةالعربية السعودية 8 فت ملك وزارة العدل صك رقم 7١551557١.7هغع‏ لتو + اشر ا المحكمة التجارية يجدة رقم الصفحة: ‎١‏ 0 دائرة الاستئناف الثانية تاريخ الصك: ‎١:44/.”/١١‏ 0-0 5 5 الحمد لله والصلاة والسلام على رسول الله أما بعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 1١/ا1‏ 2758752 وتاريخ 8؟</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 100,000,000، 1,000 ريال | تواريخ هجرية: 10/ 2 / 1434، 1411/08/03، 1413/10/26، 15 / 2 / 1434 | مقتطف: untitled لدعلا ةرازو ةيدوعسلا ةيبرعلا ةكلملا وزارة العدل الموضوع : الرقم ٣٤٧٤٩ التاريخ : ١٠/ ٢ / ١٤٣٤ هـ المرفقات : ةدج ةظفاحمب ةراجتلا ةرازو عرف ماع ريدم ةداعس سلمه الله السلام عليكم ورحمة الله وبركاته وبعد إشارة إلى خطاب سعادتكم رقم : ٦١٦٠٨٩ وتاريخ ٢٧/ ١١ / ١٤٣٩هـ والمقيد لدينا بالرقم : ٣٤٧١٤٩ وتا</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 100,000,000، 1,000 ريال | تواريخ هجرية: 10/ 2 / 1434، 1411/08/03، 1413/10/26، 15 / 2 / 1434 | مقتطف: untitled الملكة العربية السعودية وزارة العدل وزارة العدل الموضوع : الرقم ٣٤٧٤٩ التاريخ : ١٠/ ٢ / ١٤٣٤ هـ المرفقات : ةدج ةظفاحمب ةراجتلا ةرازو عرف ماع ريدم ةداعس سلمه الله السلام عليكم ورحمة الله وبركاته وبعد إشارة إلى خطاب سعادتكم رقم : ٦١٦٠٨٩ وتاريخ ٢٧/ ١١ / ١٤٣٩هـ والمقيد لدينا بالرقم : ٣٤٧١٤٩ وتا</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 3,700,000,000، 370,000,000، 120,000,000، 5,000,000 ريال | تواريخ هجرية: 1396/2/15، 1430/4/4، 1432/3/4، 1432/6/8 | مقتطف: untitled وزارة العدل \[۲۷۷\] ةدج ةظفاحمب ةماعلا ةمكحملا رقم الصك : ٣٤٢٨١٤٤٩ تاريخه : ١٤٣٤/٠٧/٢٦ هـ صك يضاقلا عيقوتو متخ ةحص ىلع قداصلا هدحو هللدمحلا يديازلا دمحم وزارة العدل ةماعلا ةمكحملا سيئر ماعلا ةمكحملا اج ةظفاحمب ةماعلا ة صفحة رقم: 1 من ۱۰ دعوى في موضوع حكم منقوض : غير مشتركة /٠٤/٢٠ خيراتو ٣٤٩</t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 3,700,000,000، 370,000,000، 120,000,000، 5,000,000 ريال | تواريخ هجرية: 1396/2/15، 1430/4/4، 1432/3/4، 1432/6/8 | مقتطف: untitled وزارة العدل \[۲۷۷\] ةدج ةظفاحمب ةماعلا ةمكحملا رقم الصك : ٣٤٢٨١٤٤٩ تاريخه : ١٤٣٤/٠٧/٢٦ هـ صك يضاقلا عيقوتو متخ ةحص ىلع قداصلا هدحو هللدمحلا يديازلا دمحم وزارة العدل ةماعلا ةمكحملا سيئر ماعلا ةمكحملا اج ةظفاحمب ةماعلا ة صفحة رقم: 1 من ۱۰ دعوى في موضوع حكم منقوض : غير مشتركة /٠٤/٢٠ الحمد لله </t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: التفتيش القضائي، المحكمة العليا | قضايا: 42824717 | مقتطف: الساعة الاحمر زيني بد الله الرحمن الرحيم Ossama A. Zainy (يئاضقلا شيتفتلا) ءاضقلل ىلعألا سلجملا سيئر يلاعم السلام عليكم ورحمة الله وبركاته وبعد : حفظه الله فإشارة إلى أحكام لائحة التفتيش القضائي وبصفته إدارة رقابية على أعمال المحاكم وقضاتها وفقا للمادة الثامنة ونصها: " التفتيش القضائي إدارة فضائية ر</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: التفتيش القضائي، المحكمة العليا | قضايا: 42824717 | مقتطف: الساعة الاحمر زيني بد الله الرحمن الرحيم Ossama A. Zainy معالي رئيس المجلس الأعلى للقضاء (التفتيش القضائي) السلام عليكم ورحمة الله وبركاته وبعد : حفظه الله فإشارة إلى أحكام لائحة التفتيش القضائي وبصفته إدارة رقابية على أعمال المحاكم وقضاتها وفقا للمادة الثامنة ونصها: " التفتيش القضائي إدارة فضائية ر</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450,000 ريال | مقتطف: ةيسيئرلا اياضقلا ىلع تابلطلا ءاضقلا ةحفصلا ضقن بلط ةيضقلا عون ةيضقلا فينصت ةيضقلا ةلاح ةرئادلا ةمكحملا ةيضقلا خيرات ةيضقلا مقر ةيماظنلا تاكرشلا فانئتسلاا ةمكحم ىلإ ةلاحم ىلولاا ةرئادلا ةدجب ةيراجتلا ةمكحملا ١٤٤٢ ةجحلا وذ ٢٥ 42824717 ó° ó° ةيضقلا تانايب ó° بلطلا مدقم تانايب ó° \* بلطلا مدقم تانايب ó°</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450,000 ريال | مقتطف: ةيسيئرلا اياضقلا ىلع تابلطلا طلب نقض الصفحة القضاء ةيضقلا عون ةيضقلا فينصت ةيضقلا ةلاح ةرئادلا ةمكحملا ةيضقلا خيرات ةيضقلا مقر ةيماظنلا تاكرشلا فانئتسلاا ةمكحم ىلإ ةلاحم ىلولاا ةرئادلا ةدجب ةيراجتلا ةمكحملا ١٤٤٢ ةجحلا وذ ٢٥ 42824717 ó° ó° ةيضقلا تانايب ó° بلطلا مدقم تانايب ó° \* بلطلا مدقم تانايب ó°</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000، 1,000 ريال | تواريخ هجرية: 1/6/1442، 10 / 5 / 1436، 11/ 2 / 1434، 1392/2/15 | مقتطف: التنفيذيون شركة التنفيذيون للمحاماة والاستشارات القانونية التاريخ: ١٤٤٥/٠٤/١٠هـ ايلعلا ةمكحملا سيئر ةليضف سلمه الله السلام عليكم ورحمه الله وبركاته، وبعد: طلب نقض الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بالصك رقم ( ٤٥٣٠٢٤١٦٢٢) بتاريخ ١٤٤٥/٠٣/١٣هـ في القضية رقم ( ٤٢٨٢٤٧١٧) وتار</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000، 1,000 ريال | تواريخ هجرية: 1/6/1442، 10 / 5 / 1436، 11/ 2 / 1434، 1392/2/15 | مقتطف: التنفيذيون شركة التنفيذيون للمحاماة والاستشارات القانونية التاريخ: ١٤٤٥/٠٤/١٠هـ فضيلة رئيس المحكمة العليا سلمه الله السلام عليكم ورحمه الله وبركاته، وبعد: طلب نقض الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بالصك رقم ( ٤٥٣٠٢٤١٦٢٢) بتاريخ ١٤٤٥/٠٣/١٣هـ في القضية رقم ( ٤٢٨٢٤٧١٧) وتار</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة العامة بجدة | مبالغ: 500,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/10/26، 1413/9/8 | مقتطف: untitled مكتب عزام فيصل خوج امون ومستشارون قـ انونيون Law Office of Azzam Faisal Khouj ATTORNEYS &amp; LEGAL CONSULTANTS م٢٠١٣/٥/١٥ قفاوملا ـه١٤٣٤/٧/٥ صاحب الفضيلة الشيخ / السلام عليكم ورحمة الله و وبر ةدجب ةماعلا ةمكحملاب يضاقلا ركاته،، ةيماتخ ةركذم عوضوملا الرقم : ٢٠١٣/٤/١٤٧ حفظه الله أتقدم لمقام فضيل</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة العامة بجدة | مبالغ: 500,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/10/26، 1413/9/8 | مقتطف: untitled مكتب عزام فيصل خوج امون ومستشارون قـ انونيون Law Office of Azzam Faisal Khouj ATTORNEYS &amp; LEGAL CONSULTANTS م٢٠١٣/٥/١٥ قفاوملا ـه١٤٣٤/٧/٥ صاحب الفضيلة الشيخ / السلام عليكم ورحمة الله و وبر ةدجب ةماعلا ةمكحملاب يضاقلا ركاته،، الموضوع مذكرة ختامية الرقم : ٢٠١٣/٤/١٤٧ حفظه الله أتقدم لمقام فضيل</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: ءاضقلل ىلعألا سلجملا :. ةينورتكلإلا ىوكشلا ةمدخ ةينوتركللإا نييز سابع نب دمحا نب هماسأ ابحرم بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا ةيسيئرلا لولأا مسلاا زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة ع</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: خدمة الشكوى الإلكترونية :. المجلس الأعلى للقضاء ةينوتركللإا نييز سابع نب دمحا نب هماسأ ابحرم بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا ةيسيئرلا لولأا مسلاا زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة ع</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ىوكشلا ةدعاسملا ó°¡3⁄4 تيانايب ó°­μ ةيسيئرلا ó° خي راتلا ةفصلا رقم القضية رقم الشكوى 1445/06/18 أصالة </t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ىوكشلا ةدعاسملا ó°¡3⁄4 تيانايب ó°­μ ةيسيئرلا ó° خي راتلا ةفصلا رقم القضية رقم الشكوى 1445/06/18 أصالة </t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | تواريخ هجرية: 1445/06/18 | مقتطف: ةينورتكلإلا ىوكشلا ةمدخ المجند الاعلى للقضاء تفاصيل الشكوى ةيسيئرلا طلباتي طلبات غير مكتملة بياناتي للمساعدة ن خروج مرحبا أسامه بن احمد بن عباس زيق بلطلا ةجلاعم مت :ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعترا</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | تواريخ هجرية: 1445/06/18 | مقتطف: خدمة الشكوى الإلكترونية المجند الاعلى للقضاء تفاصيل الشكوى الرئيسية طلباتي طلبات غير مكتملة بياناتي للمساعدة ن خروج مرحبا أسامه بن احمد بن عباس زيق بلطلا ةجلاعم مت :ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعترا</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/06/18، 1445/11/13 | مقتطف: ةينورتكلإلا ىوكشلا .اهنلا عارصلا ةيسيئرلا :: طلبانی طلبات غير مكتملة معدلاو لصاوتلا زكرم مرحبا أسامه بن احمد بن عباس زيني بلطلا ةجلاعم مت ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد.. فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/06/18، 1445/11/13 | مقتطف: الشكوى الإلكترونية .اهنلا عارصلا :: الرئيسية طلبانی طلبات غير مكتملة معدلاو لصاوتلا زكرم مرحبا أسامه بن احمد بن عباس زيني بلطلا ةجلاعم مت ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد.. فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | تواريخ هجرية: 1445/04/30 | مقتطف: ءاضقلا ءالطلا مرحبا أسامه بن احمد بن عباس زيني طلباتي ةينورتكلإلا ىوكشلا ةمدخ ةيسيئرلا طلباتي طلبات غير مكتملة بياناتي 2 للمساعدة ن خروج رقم الشكوى نوع القضية رقم القضية الصفة 230747621 42824717 أصالة عن نفسه تاريخ الشكوى 1445/04/30 عرض</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | تواريخ هجرية: 1445/04/30 | مقتطف: الطلاء القضاء مرحبا أسامه بن احمد بن عباس زيني طلباتي خدمة الشكوى الإلكترونية الرئيسية طلباتي طلبات غير مكتملة بياناتي 2 للمساعدة ن خروج رقم الشكوى نوع القضية رقم القضية الصفة 230747621 42824717 أصالة عن نفسه تاريخ الشكوى 1445/04/30 عرض</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° °ó بيانات مقدم الشكوى ةيضقلا تانايب ó°· ةمكحملا جتلا ةمكحملا ةلئاعلا مسا نييز خي راتلا 1445/06/18 لاوجلا مقر 56355663 دجلا مسا سابع نب يراجت</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° °ó بيانات مقدم الشكوى ةيضقلا تانايب ó°· ةمكحملا جتلا ةمكحملا ةلئاعلا مسا نييز خي راتلا 1445/06/18 لاوجلا مقر 56355663 دجلا مسا سابع نب يراجت</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: ةينورتكلإلا ىوكشلا ةمدخ ةيسيئرلا بیاناتی ةدعاسملا *\ بلطلا رقم الحكم رقم القضية 4431025114 ةفلاخملا يف رظنلا إلغاء 42824717 حدد الحكم المعين تاريخ النطق بالحكم تاريخ تسليم الحكم 1445/01/01 1445/01/01 قباسلا تقديم أسامه بن احمد بن عباس زيني</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوى الإلكترونية الرئيسية بیاناتی ةدعاسملا *\ بلطلا رقم الحكم رقم القضية 4431025114 ةفلاخملا يف رظنلا إلغاء 42824717 حدد الحكم المعين تاريخ النطق بالحكم تاريخ تسليم الحكم 1445/01/01 1445/01/01 قباسلا تقديم أسامه بن احمد بن عباس زيني</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: :خیراتلا ٢٦ / ٠٤ / ١٤٤٦ ھـ الله ھملس ،، ءاضقلل یلعلأا سلجملا سیئرو لدعلا ریزو يناعمصلا دمحم نب دیلو /روتکدلا يلاعم ا دعبو .. ھــــتاکربو الله ةمحرو مکیلع ملاـــسل : ھـ ١٤٤٥ - ١١ - ١٣ في ١٩٩٠٥٨ رقم وإلحاقا للشکوى ) ٤٢٨٢٤٧١٧ ھـ في القضیة رقم ( ١٤٤٥ / ٠٣ / ١٣ ) وتاریخ ٤٥٣٠٢٤١٦٢٢ رقم( دائرة االستئناف ال</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: :خیراتلا ٢٦ / ٠٤ / ١٤٤٦ ھـ : لســـالم علیکم ورحمة هللا وبرکاتــــھ .. وبعد ا معالي الدکتور/ ولید بن محمد الصمعاني وزیر العدل ورئیس المجلس األعلی للقضاء ،، سلمھ هللا ھـ ١٤٤٥ - ١١ - ١٣ في ١٩٩٠٥٨ رقم وإلحاقا للشکوى ) ٤٢٨٢٤٧١٧ ھـ في القضیة رقم ( ١٤٤٥ / ٠٣ / ١٣ ) وتاریخ ٤٥٣٠٢٤١٦٢٢ رقم( دائرة االستئناف ال</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | قضايا: 42824717 | تواريخ هجرية: 25/12/1442 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت ىوكشلا عون ديدحت ىجري أخرى محاكم التنفيذ مرتبطة بقضية ماعلا ءاضقلا في ةروظنملا اياضقلاب ةطبترملا ىواكشلا يدلايم خيراتلا ó°­ عونلا ó° ةفصل</t>
+          <t>النوع: شكوى | قضايا: 42824717 | تواريخ هجرية: 25/12/1442 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت يرجى تحديد نوع الشكوى أخرى محاكم التنفيذ مرتبطة بقضية ماعلا ءاضقلا في ةروظنملا اياضقلاب ةطبترملا ىواكشلا يدلايم خيراتلا ó°­ عونلا ó° ةفصل</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01، 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ ةيسيئرلا ةحفصلا ةينوتركللإا ىوكشلا ةمدخ ةيسيئرلا ةحفصلا ó° ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ةساردلا ديق بلطلا ó° °ó بيانات مقدم الشكوى خي راتلا 1445/01/05 خي راتلا 1445/06/18 خي راتلا 1446/04/27 ةفصلا أصالة عن نفس</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01، 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ةساردلا ديق بلطلا ó° °ó بيانات مقدم الشكوى خي راتلا 1445/01/05 خي راتلا 1445/06/18 خي راتلا 1446/04/27 ةفصلا أصالة عن نفس</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450، 120 ريال | مقتطف: التاريخ: 17/11 /1445هـ هللا هظفح زيزعلا دبع نب ناملس نب دمحم /ريمألا يكلملا ومسلا بحاص يديس ءارزولا سلجم سيئر دهعلا يلو الســـلام عليكم ورحمة الله وبركاتــــه، وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم رقم( 4530241622) وتاريخ 13/03/1445هـ</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450، 120 ريال | مقتطف: التاريخ: 17/11 /1445هـ هللا هظفح زيزعلا دبع نب ناملس نب دمحم /ريمألا يكلملا ومسلا بحاص يديس ولي العهد رئيس مجلس الوزراء الســـلام عليكم ورحمة الله وبركاتــــه، وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم رقم( 4530241622) وتاريخ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/17، 1445/11/22 | مقتطف: تفاصيل الشكوى 5/30/24, 11:12 AM ىوكشلا لیصافت جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/3 ىوكشلا ليصافت « لصاوت « ردص : : يه يه ةيلاحلا ىوكشلا ةلاح ةيصخشلا تامولعملا 05</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/17، 1445/11/22 | مقتطف: تفاصيل الشكوى تفاصیل الشكوى AM 11:12 ,5/30/24 جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/3 » تواصل » تفاصيل الشكوى ردص : : يه يه ةيلاحلا ىوكشلا ةلاح ةيصخشلا تامولعملا 05</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تفاصيل الشكوى 5/24/24, 11:02 PM ىوكشلا لیصافت جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/2 ىوكشلا ليصافت « لصاوت « ديدج : : يه يه ةيلاحلا ىوكشلا ةلاح ةيصخشلا تامولعملا 0</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تفاصيل الشكوى تفاصیل الشكوى PM 11:02 ,5/24/24 جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/2 » تواصل » تفاصيل الشكوى ديدج : : يه يه ةيلاحلا ىوكشلا ةلاح ةيصخشلا تامولعملا 0</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تأكيد الشكوى 5/24/24, 10:55 PM ىوكشلا دیكأت جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ ىوكشلا ديكأت « لصاوت « 2 ةوطخلا ةيصخشلا تامولعملا 0556355663 :لاوجلا ينيز سابع نب دمحا نب هماسأ :لماكلا مسلاا ossama.zainy@ozco.com :ينورتكللإا ديربلا 1008017301 :ةيوهلا مقر ىوكشلا ليصافت ديدج : ىوكشلا ةلاح نوع الش</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تأكيد الشكوى تأكید الشكوى PM 10:55 ,5/24/24 جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ » تواصل » تأكيد الشكوى 2 ةوطخلا ةيصخشلا تامولعملا 0556355663 :لاوجلا ينيز سابع نب دمحا نب هماسأ :لماكلا مسلاا ossama.zainy@ozco.com :ينورتكللإا ديربلا 1008017301 :ةيوهلا مقر ىوكشلا ليصافت ديدج : ىوكشلا ةلاح نوع الش</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا لولأا مسلاا ةينورتكللإا ىوكشلا ةمدخ ينيز سابع نب دمحا نب هماسأ ابحرم زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 ةيضقلا ليصافت ةرئادلا / ةمكحملا ةيضقلا عون ىلولاا</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا مرحبا أسامه بن احمد بن عباس زيني خدمة الشكوى اإللكترونية االسم األول زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 ةيضقلا ليصافت ةرئادلا / ةمكحملا ةيضقلا عون ىلولاا</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/13 | مقتطف: بلطلا ةيلاعم مت :ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما قررته المادة (176) من نظام مكاعري هللاو مكلصاوت مكل نيركاش ةيعرشلا تاعفارملا ةعجارملا تحت لاز امو لسرم حتف ةداعا بلط كي</t>
+          <t>النوع: تقرير خبرة | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/13 | مقتطف: حالة الشكوى: تم معالية الطلب عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما قررته المادة (176) من نظام مكاعري هللاو مكلصاوت مكل نيركاش ةيعرشلا تاعفارملا ةعجارملا تحت لاز امو لسرم حتف ةداعا بلط كي</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة العامة بجدة | مبالغ: 1,769,886,051 ريال | مقتطف: بسم الله الرحمن الرحيم كية تنفيذ بتاريخ ١٤٣٤/٠٢/٠٩هـ الموافق ٢٠١٢/١٢/٢٢م ةدج ةنيدمب ةماعلا ةمكحملاب ذيفنتلا يضاق ، يرقيرقلا يلع / خيشلا ةليضف ىدل الحمد لله وحده وبعد ، وفي الساعة العاشرة من صباح هذا اليوم السبت الموافق ١٤٣٤/۰۲/۰۹هـ ، وبالإشارة إلى تنفيذ الحكم رقم ( ٢/١٧/١٨٥ ) لعام ١٤٣٦هـ في القضيتين</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة العامة بجدة | مبالغ: 1,769,886,051 ريال | مقتطف: بسم الله الرحمن الرحيم كية تنفيذ بتاريخ ١٤٣٤/٠٢/٠٩هـ الموافق ٢٠١٢/١٢/٢٢م لدى فضيلة الشيخ / علي القريقري ، قاضي التنفيذ بالمحكمة العامة بمدينة جدة الحمد لله وحده وبعد ، وفي الساعة العاشرة من صباح هذا اليوم السبت الموافق ١٤٣٤/۰۲/۰۹هـ ، وبالإشارة إلى تنفيذ الحكم رقم ( ٢/١٧/١٨٥ ) لعام ١٤٣٦هـ في القضيتين</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني | مقتطف: إخطار بمطالبة مالية بلطلا خيرات ةيلاملا ةبلاطملا تانايب ةبلاطملا ةيلاملا ةليسو راطخإلا لاوجلا لجسملا رشبأب 1008017301 1008017301 مسا لبقتسم بلطلا - مقر ةيوه لبقتسم بلطلا 1008017301 1008017301 مسا غلبملا ناندع دمحا سابع ينيز مقر ةيوه غلبملا 1017092733 1017092733 مسا مدقم بلطلا دمحم نبنب زاوف نبنب رين</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني | مقتطف: إخطار بمطالبة مالية الإخطار 440300010192 440300010192 الإخطار رقم 1098908278 1098908278 الطلب مقدم هوية رقم الثعلي منير بنبن فواز بنبن محمد الطلب مقدم اسم 1017092733 1017092733 المبلغ هوية رقم زيني عباس احمد عدنان المبلغ اسم 1008017301 1008017301 الطلب مستقبل هوية رقم - الطلب مستقبل اسم 1008017301 1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>النوع: وكالة | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ</t>
+          <t>النوع: وكالة | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 331,882,138، 120 ريال | مقتطف: Saud Mansouri From: Sent: To: Cc: Subject: Dr.Mohammed Al Banna Sunday, October 12, 2025 4:11 PM Saud Mansouri Dr.Said Yehya; Sameer Bawazir; Hussain Kaff; Yasser Mutairi; Lfshjeddah; Hussam Al- Hejailan; Eid Abdulmawjood RE دراسة الحكمين الابتدائي والاستئناف في القضية رقم 42824717 التناقضات في صك ا</t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 368,757,931، 331,882,138، 450,000، 120 ريال | مقتطف: Saud Mansouri From: Sent: To: Cc: Subject: Dr.Mohammed Al Banna Sunday, October 12, 2025 4:11 PM Saud Mansouri Dr.Said Yehya; Sameer Bawazir; Hussain Kaff; Yasser Mutairi; Lfshjeddah; Hussam Al- Hejailan; Eid Abdulmawjood RE دراسة الحكمين الابتدائي والاستئناف في القضية رقم 42824717 التناقضات في صك ا</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530828230، 4630548401 | تواريخ هجرية: 24/04/1446 | مقتطف: رظــــــــنلا ةداــــعإ "ساـــــمتلا" بــــلط صاحب الفضيلة/ رئيس محكمة الاستئناف بالمحكمة التجارية بجدة حفظه الله السلام عليكم ورحمة الله وبركاته،،، الموضوع: نلتمس من فضيلتكم إعادة النظر بشأن الحكم الصادر عن دائرة الاستئناف الثانية بمحكمتكم الموقرة برقم: (4530828230) وتاريخ: 25/08/1445هـ "مرفق رقم 1</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530828230، 4630548401 | تواريخ هجرية: 24/04/1446 | مقتطف: طلــــب "التمـــــاس" إعــــادة النــــــــظر صاحب الفضيلة/ رئيس محكمة الاستئناف بالمحكمة التجارية بجدة حفظه الله السلام عليكم ورحمة الله وبركاته،،، الموضوع: نلتمس من فضيلتكم إعادة النظر بشأن الحكم الصادر عن دائرة الاستئناف الثانية بمحكمتكم الموقرة برقم: (4530828230) وتاريخ: 25/08/1445هـ "مرفق رقم 1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: بسم الله الرحمن الرحيم صلاح الحجيلات للمحاماة والاستشارات القانونية منذ ١٩٦٨ (ذ.م.م) بالتعاون مع فريشفيلدز بروكهاوس ديرنغر ( تقرير ) دة فرع جـ ص.ب ١٥١٤١ جدة ٢١٤٤٤ ترخيص (٢٧/١٧٦) هاتف: ۱۹۸۵۸۸۸-۰۱۲ فاكس: ۲۸۲۱۲۷۷-۰۱۲ ةيدوعسلا ةيبرعلا ةكلمملا www.hajailanlaw.com Web: : عقوملا Lfalijeddah@hejallanlaw.com</t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: بسم الله الرحمن الرحيم صلاح الحجيلات للمحاماة والاستشارات القانونية منذ ١٩٦٨ (ذ.م.م) بالتعاون مع فريشفيلدز بروكهاوس ديرنغر ( تقرير ) دة فرع جـ ص.ب ١٥١٤١ جدة ٢١٤٤٤ ترخيص (٢٧/١٧٦) هاتف: ۱۹۸۵۸۸۸-۰۱۲ فاكس: ۲۸۲۱۲۷۷-۰۱۲ بريد الكتروني : Lfalijeddah@hejallanlaw.com الموقع : Web: www.hajailanlaw.com المملكة </t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 4,690,483، 2,463,761 ريال | تواريخ هجرية: 1432/4/10، 1432/4/30 | مقتطف: تقرير خبرة ـلوألا ةلحرملا مقدم إلى أطراف النزاع فيما يتعلق ةدجب ةيرادإلا ةمكحملا يف رشع ةعباسلا ةرئادلا ىدل نيتروظنملاو ـه١٤٣٢ ماعل ق ٢/١٣٧٥/ مقرو ـه ١٤٣١ ماعل ق ٢/٥٧٩٨/ مقر نيتيضقلاب مئاقلا عازنلا صوصخب بين المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد زيني والمدعى عليه ال</t>
+          <t>النوع: تقرير خبرة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 4,690,483، 2,463,761 ريال | تواريخ هجرية: 1432/4/10، 1432/4/30 | مقتطف: تقرير خبرة المرحلة الأولـ مقدم إلى أطراف النزاع فيما يتعلق بالقضيتين رقم ٢/٥٧٩٨/ ق لعام ١٤٣١ هـ ورقم ٢/١٣٧٥/ ق لعام ١٤٣٢هـ والمنظورتين لدى الدائرة السابعة عشر في المحكمة الإدارية بجدة بخصوص النزاع القائم بين المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد زيني والمدعى عليه ال</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | مقتطف: بسم الله الرحمن الرحيم صلاح المجالات للمحاماة والاستشارات القانونية منذ ١٩٦٨ (ذ.م.م) بالتعاون مع فريشفيلدز بروكهاوس ديرنغر ةيدوعسلا ةيبرعلا ةكلمملا www.hejailanlaw.com Web: :عقوملا Lfshjoddah@hejailanlaw.com : ينورتكلا ديرب ۲۱۰-۷۷۲۱۲۸۲ : سكاف -۸۸۸۸۹۱ :فتاه (۲۷۱/۷۲) صيخرت ٢١٤٤٤ ةدج ١٥١٤١ ب.ص ةدج عرف </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | مقتطف: بسم الله الرحمن الرحيم صلاح المجالات للمحاماة والاستشارات القانونية منذ ١٩٦٨ (ذ.م.م) بالتعاون مع فريشفيلدز بروكهاوس ديرنغر فرع جدة ص.ب ١٥١٤١ جدة ٢١٤٤٤ ترخيص (۲۷/۱۷۲) هاتف: ۱۹۸۸۸۸- فاكس : ۲۸۲۱۲۷۷-۰۱۲ بريد الكتروني : Lfshjoddah@hejailanlaw.com الموقع: Web: www.hejailanlaw.com المملكة العربية السعودية </t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | تواريخ هجرية: 1443/01/03، 1443/01/04، 1443/01/08، 1443/01/09 | مقتطف: ٧E٥A٢E٢A٨٣١B٢C٢٥٤٥A٩٤٠١٤٣C٧٠ أسامه بن احمد بن عباس زيني م ١٢:٥٨ تقولا ١٤٤٣/٠١/٠٣ : خيراتلا مواعيد وتبادل مذكرات ومستندات ىوعدلا تانایب ١٤٤٣/٠١/٠٣ خیراتلا ءاعبرلاا مویلا ١٤٤٢ ماعل عاتقة محمديحيى محمدعلي الحرازي,وآخرون المدعي الدائرة رقم الدعوى ھیلع یعدملا لدابتلاو عاديلإا ديعاوم عدنان احمد عباس زيني </t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | تواريخ هجرية: 1443/01/03، 1443/01/04، 1443/01/08، 1443/01/09 | مقتطف: ٧E٥A٢E٢A٨٣١B٢C٢٥٤٥A٩٤٠١٤٣C٧٠ أسامه بن احمد بن عباس زيني م ١٢:٥٨ تقولا ١٤٤٣/٠١/٠٣ : خيراتلا مواعيد وتبادل مذكرات ومستندات بیانات الدعوى ١٤٤٣/٠١/٠٣ خیراتلا ءاعبرلاا مویلا ١٤٤٢ ماعل عاتقة محمديحيى محمدعلي الحرازي,وآخرون المدعي الدائرة رقم الدعوى ھیلع یعدملا لدابتلاو عاديلإا ديعاوم عدنان احمد عباس زيني </t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 3,700,000,000، 370,000,000، 120,000,000، 5,000,000 ريال | تواريخ هجرية: 1396/2/15، 1430/4/4، 1432/3/4، 1432/6/8 | مقتطف: untitled وزارة العدل \[۲۷۷\] ةدج ةظفاحمب ةماعلا ةمكحملا رقم الصك : ٣٤٢٨١٤٤٩ تاريخه : ١٤٣٤/٠٧/٢٦ هـ صك يضاقلا عيقوتو متخ ةحص ىلع قداصلا هدحو هللدمحلا يديازلا دمحم وزارة العدل ةماعلا ةمكحملا سيئر ماعلا ةمكحملا اج ةظفاحمب ةماعلا ة صفحة رقم: 1 من ۱۰ دعوى في موضوع حكم منقوض : غير مشتركة /٠٤/٢٠ الحمد لله </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 3,700,000,000، 370,000,000، 120,000,000، 5,000,000 ريال | تواريخ هجرية: 1396/2/15، 1430/4/4، 1432/3/4، 1432/6/8 | مقتطف: untitled وزارة العدل \[۲۷۷\] المحكمة العامة بمحافظة جدة رقم الصك : ٣٤٢٨١٤٤٩ تاريخه : ١٤٣٤/٠٧/٢٦ هـ صك الحمدلله وحده الصادق على صحة ختم وتوقيع القاضي محمد الزايدي وزارة العدل رئيس المحكمة العامة المحكمة العام ة العامة بمحافظة جا صفحة رقم: 1 من ۱۰ دعوى في موضوع حكم منقوض : غير مشتركة /٠٤/٢٠ الحمد لله </t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 450 ريال | تواريخ هجرية: 1431/12/2، 1432/02/26، 1432/03/11، 1432/11/21 | مقتطف: untitled وزارة العدلك \[۲۷۷\] نسيصادق على صحة ختم وتوقيع القاضي دعاسملا ةدج ةظفاحمب ةماعلا ةمكحملا ناديعسلا رمع نم نأ ىلوم ينتلا حلاص نب ةدج ةظفاحمب ةماعلا ةمكحملا رقم الصك : ٣٣٢٨٦٣٩٢ تاريخه : ١٤٣٣/٠٦/٠٨ هـ مك إقامة ولي على من طرأ عليه القصور عقلا صفحة رقم: 1 من ه الحمد لله وحده والصلاة والسلام على </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 450 ريال | تواريخ هجرية: 1431/12/2، 1432/02/26، 1432/03/11، 1432/11/21 | مقتطف: untitled وزارة العدلك \[۲۷۷\] نسيصادق على صحة ختم وتوقيع القاضي مولى أن من عمر السعيدان المحكمة العامة بمحافظة جدة المساعد بن صالح التني المحكمة العامة بمحافظة جدة رقم الصك : ٣٣٢٨٦٣٩٢ تاريخه : ١٤٣٣/٠٦/٠٨ هـ مك إقامة ولي على من طرأ عليه القصور عقلا صفحة رقم: 1 من ه الحمد لله وحده والصلاة والسلام على </t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>النوع: مراسلة | مقتطف: 25 page تاقفرملا و تايركذلا CamScanner &lt;https://v3.camscanner.com/user/download&gt;</t>
+          <t>النوع: مراسلة | مقتطف: الذكريات و المرفقات page 25 CamScanner &lt;https://v3.camscanner.com/user/download&gt;</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>النوع: صحيفة دعوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | تواريخ هجرية: 1440/05/23، 1442/12/17، 1442/12/26 | مقتطف: ةدجب ةيراجتلا ةمكحملا (٥٠٠٣) ىواعدلا ةرادإ ماظن ريراقت مويب ىلولأا ةسلجلا دعوم لبق كلذو ،يعدملا ىوعد ىلع درلل ةينورتكلإ ةركذم عاديإ هيلع ىعدملا ىلع بجي-٢ .ددحملا دعوملا يف روضحلا -١ :بولطملا للاخ نم (ىلولأا عافدلا ةركذم عاديإ) ةمدخ ربع اينورتكلإ ةركذملا عاديإ متيو ،ةيعرشلا تاعفارملا ماظن نم نيعبرلأا</t>
+          <t>النوع: صحيفة دعوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | تواريخ هجرية: 1440/05/23، 1442/12/17، 1442/12/26 | مقتطف: تقارير نظام إدارة الدعاوى (٥٠٠٣) المحكمة التجارية بجدة الخطوات التالية: (موقع وزارة العدل &gt;\ الخدمات اإللكترونية &gt;\ بوابة القضاء التجاري &gt;\ الدخول على الخدمة). على األقل، عمال بحكم المادة الخامسة واألربعين من نظام المرافعات الشرعية، ويتم إيداع المذكرة إلكترونيا عبر خدمة (إيداع مذكرة الدفاع األولى) م</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 8,849,447,678، 184,887,445، 8,844,470، 87,445 ريال | تواريخ هجرية: 1/17/1460 | مقتطف: رم اذخ ريسرطذلء دنه لجيو ف ةدجب ةيرادإلا ةمكحملا ‏١/11‎ يوني فنك ةرشع ةعبسا ةئلا با منل) ترو ظ حتكه رقم ‎١/17/1460‏ لعام ١؟4اه‏ ظ 32 ا لقتصصسن رقم 4ة/س0ة/ "اق ملقم 1ه وار فهر ا اق لهام ردند” المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد ظ عباس زيسي ظ | ضد / أسامة بن أح</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 8,849,447,678، 184,887,445، 8,844,470، 87,445 ريال | تواريخ هجرية: 1/17/1460 | مقتطف: رم اذخ ريسرطذلء دنه لجيو ف كنف ينوي ‎١/11‏ المحكمة الإدارية بجدة ورت (لنم اب الئة اسبعة عشرة ظ حتكه رقم ‎١/17/1460‏ لعام ١؟4اه‏ ظ 32 ا لقتصصسن رقم 4ة/س0ة/ "اق ملقم 1ه وار فهر ا اق لهام ردند” المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد ظ عباس زيسي ظ | ضد / أسامة بن أح</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 478,757,110، 11,574,017، 450,000، 170 ريال | مقتطف: 25 1 ةيدوعسلا ةيبرعلا ةكلمللا كلا ل 3 الا حا لست _حجججججججججججججججججبببجب ‏ 3 3 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ 97 م 0_0 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: 8١/8./ة44١‏ 3 90 الآ الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 17/ا27801'4</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 478,757,110، 368,757,931، 11,574,017، 450,000 ريال | مقتطف: 25 الك اللملكة العربية السعودية 1 ل 3 الا حا لست _حجججججججججججججججججبببجب ‏ 3 3 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ 97 م 0_0 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: 8١/8./ة44١‏ 3 90 الآ الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 17/ا27801'4</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/06/18، 1445/11/13 | مقتطف: ةينورتكلإلا يركشلا المعلما طلباتي طلبات غير مكتملة معدلاو لصاوتلا زكرم مرحبا أسامه بن احمد بن عباس زيني بلطلا ةجلاعم مت :ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد.. فلفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما قررته المادة (17</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/06/18، 1445/11/13 | مقتطف: الشكري الإلكترونية المعلما طلباتي طلبات غير مكتملة مركز التواصل والدعم مرحبا أسامه بن احمد بن عباس زيني حالة الشكوى: تم معالجة الطلب عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد.. فلفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما قررته المادة (17</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 يلدعلا غيلبتلا ةيئاضقلا فيلاكتلا يلدعلا لصاوتلا 1950 ديعاوملا صيخارتلا ةيلدعلا قيثوتلا ذيفنتلا سلافلإا ءاضقلا ... محا نب هماسأ تامولعملا / ابحرم ةحول ةلحرم ءاهنلاا هيلاملا ةكرحلا رشؤم الدائرة تاريخ تقديم ةمكحملا دنسلا عون دنسلا </t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية محا نب هماسأ تامولعملا / ابحرم ةحول ةلحرم ءاهنلاا هيلاملا ةكرحلا رشؤم الدائرة تاريخ تقديم الطلب الصفة في نوع السند</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: بسم الله الرحمن الرحيم عقد بيع إنه في مدينة جدة وبتاريخ 20 / 9 / 1431هـ تم الاتفاق بين كلا من : الطرف الأول / أحمد عباس زيني ينيز دمحأ هماسأ / يناثلا فرطلا تمهيد حيث أن الطرف الأول يملك حصص في شركة أحمد زيني التجارية سجل تجاري : 4030169102 بعدد (450 ) حصة وحيث أن الطرف الثاني مدير الشركة المذكورة أع</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: بسم الله الرحمن الرحيم عقد بيع إنه في مدينة جدة وبتاريخ 20 / 9 / 1431هـ تم الاتفاق بين كلا من : الطرف الأول / أحمد عباس زيني الطرف الثاني / أسامه أحمد زيني تمهيد حيث أن الطرف الأول يملك حصص في شركة أحمد زيني التجارية سجل تجاري : 4030169102 بعدد (450 ) حصة وحيث أن الطرف الثاني مدير الشركة المذكورة أع</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير طبي | الأطراف: أسامة زيني | تواريخ هجرية: 1445/03/24، 1445/03/25، 1445/03/28، 1445/03/29 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 3991 يلدعلا غيلبتلا ةيئاضقلا فيلاكتلا يلدعلا لصاوتلا 1950 ديعاوملا صيخارتلا ةيلدعلا قيثوتلا ذيفنتلا سلافلإا ءاضقلا ... محا نب هماسأ تامولعملا / ابحرم ةحول 46 رارق ليصافت رارقلا ةلاح مقر لاعف 400464504823219 رارقلا رادصإ تقو رارقلا را</t>
+          <t>النوع: تقرير طبي | الأطراف: أسامة زيني | تواريخ هجرية: 1445/03/24، 1445/03/25، 1445/03/28، 1445/03/29 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 3991 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية محا نب هماسأ تامولعملا / ابحرم ةحول 46 رارق ليصافت رارقلا ةلاح فعال رقم 400464504823219 رارقلا رادصإ تقو 7:17:05 ص</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: بسم الله الرحمن الرحيم عقد بيع إنه في مدينة جدة وبتاريخ 20/ 9 / 1431هـ تم الاتفاق بين كلا من : الطرف الأول / أحمد عباس زيني ينيز دمحأ هماسأ / يناثلا فرطلا تمهيد حيث أن الطرف الأول يملك حصص في شركة أحمد زيني التجارية سجل تجاري : 4030169102 بعدد (450) حصة وحيث أن الطرف الثاني مدير الشركة المذكورة أعلا</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: بسم الله الرحمن الرحيم عقد بيع إنه في مدينة جدة وبتاريخ 20/ 9 / 1431هـ تم الاتفاق بين كلا من : الطرف الأول / أحمد عباس زيني الطرف الثاني / أسامه أحمد زيني تمهيد حيث أن الطرف الأول يملك حصص في شركة أحمد زيني التجارية سجل تجاري : 4030169102 بعدد (450) حصة وحيث أن الطرف الثاني مدير الشركة المذكورة أعلا</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: محضر | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 10-07-1434 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن = من عبا شرکةس تخارج زين أباري .279*000,750,136 وزیني ( ١٤٢٨ ) : ينیز سابع دمحأ خیشلا ةصح 38,153,250 ينيز سابع نب دمحا نب هماسأ ( ١٤٢٩ ماعل ةمیقلا) 178,223,956.69*.279 228,785,567 ةیراقعلا ي:ينیز نيز لامعلأل :ةکرشلا سابع x سةفایضلا نم .779 دمحأ ينیز ابع = </t>
+          <t xml:space="preserve">النوع: محضر | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 3,000,000 ريال | تواريخ هجرية: 10-07-1434 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن = من عبا شرکةس تخارج زين أباري .279*000,750,136 وزیني ( ١٤٢٨ ) : أسامه بن احمد بن عباس زيني 250,153,38 حصة الشیخ أحمد عباس زیني ( ١٤٢٩ ماعل ةمیقلا) 178,223,956.69*.279 228,785,567 ةیراقعلا ي:ينیز نيز لامعلأل :ةکرشلا سابع x سةفایضلا نم .779 دمحأ ينیز ابع = </t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 250,000,000، 217,250,000، 172,613,467، 172,613,466 ريال | تواريخ هجرية: 01-01-1430، 09/08/1431، 10/19/1431، 1411/8/30 | مقتطف: AD تقرير خبرة مقدم إلى أطراف النزاع فيما يتعلق ةدجب ةيرادإلا ةمكحملا يف رشع ةعباسلا ةرئادلا ىدل نيتروظنملاو ـه١٤٣٢ ماعل ق ٢/١٣٧٥/ مقرو ـه١٤٣١ ماعل ق / ٢/٥٧٩٨ مقر نيتيضقلاب مئاقلا عازنلا صوصخب بين المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد زيني والمدعى عليه السيد / أسامة </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 250,000,000، 217,250,000، 172,613,467، 172,613,466 ريال | تواريخ هجرية: 01-01-1430، 09/08/1431، 10/19/1431، 1411/8/30 | مقتطف: AD تقرير خبرة مقدم إلى أطراف النزاع فيما يتعلق بالقضيتين رقم ٢/٥٧٩٨ / ق لعام ١٤٣١هـ ورقم ٢/١٣٧٥/ ق لعام ١٤٣٢هـ والمنظورتين لدى الدائرة السابعة عشر في المحكمة الإدارية بجدة بخصوص النزاع القائم بين المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد زيني والمدعى عليه السيد / أسامة </t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: تقرير خبرة | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ ابع نب دمحا نب </t>
+          <t>النوع: تقرير خبرة | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا أسامھ بن احمد ب</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 500,000، 450,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/10/26، 1413/9/8 | مقتطف: untitled شركة أحمد زيني التجارية ست ٤٠٣٠١٦۹۱۰۲ لایر ۰۰۰,۰۰۵ :لاملا سأر Ahmed Zainy Trading Co. C.R: 4030169102 Capital SR: 500.000 قرار الشركاء بتعديل بعض بنود عقد تأسيس شركة أحمد زيني التجارية - شركة ذات مسئولية محدودة بتاريخ ١٤٣١/٠٩/٢٠هـ الموافق ٢٠١٠/٠٨/٣٠ م لقد سبق للاطراف الاتية اسمائهم :- أحمد </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 500,000، 450,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/10/26، 1413/9/8 | مقتطف: untitled شركة أحمد زيني التجارية ست ٤٠٣٠١٦۹۱۰۲ رأس المال: ۵۰۰,۰۰۰ ریال Ahmed Zainy Trading Co. C.R: 4030169102 Capital SR: 500.000 قرار الشركاء بتعديل بعض بنود عقد تأسيس شركة أحمد زيني التجارية - شركة ذات مسئولية محدودة بتاريخ ١٤٣١/٠٩/٢٠هـ الموافق ٢٠١٠/٠٨/٣٠ م لقد سبق للاطراف الاتية اسمائهم :- أحمد </t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 11,679,151، 737,500 ريال | مقتطف: untitled ملخص تقرير خبرة مقدم إلى المحكمة الادارية العامة في جدة الدائرة السابعة عشرة ةدجب ةيرادإلا ةمكحملا يف رشع ةعباسلا ةرئادلا ىدل نيتروظنملاو ـه١٤٣٢ ماعل ق٢/١٣٧٥/ مقرو ـه١٤٣١ ماعل ق٢/٥٧٩٨/ مقر نيتيضقلاب مئاقلا عازنلا صوصخب المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 1,037,259,019، 172,613,467، 14,282,008، 11,679,151 ريال | مقتطف: untitled ملخص تقرير خبرة مقدم إلى المحكمة الادارية العامة في جدة الدائرة السابعة عشرة بالقضيتين رقم ٢/٥٧٩٨/ق لعام ١٤٣١هـ ورقم ٢/١٣٧٥/ق لعام ١٤٣٢هـ والمنظورتين لدى الدائرة السابعة عشر في المحكمة الإدارية بجدة بخصوص النزاع القائم المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد </t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | المحاكم: ديوان المظالم | تواريخ هجرية: 02 / 12 / 1432، 10 / 02 / 1434، 16 / 10 / 1431 | مقتطف: مدع ثیح يعدملا ةفص : خیراتب صصحلا لقن ثروملا نا ١٦ / ١٠ / ١٤٣١ ) ةدمل ةایحلا دیق یلع اھدعب يقبو ـھ ٧ يعدی ملو ماوعأ ( : خیراتب مھصصح يف ةوخلاا جراخت مت مث ، نبغلا ١٠ / ٠٢ / ١٤٣٤ ـھ نبغلا وعدی ملو اضیا . وبعد وفاة المورث رفعو دعوى الغبن في قیمة حصة السھم عند شرائي ماع يف دلاولا نم ١٦ / ١٠ / ١٤٣١ ىوعد</t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | المحاكم: ديوان المظالم | تواريخ هجرية: 02 / 12 / 1432، 1431 / 10 / 16، 1434 / 02 / 10 | مقتطف: ان المورث نقل الحصص بتاریخ : صفة المدعي حیث عدم ھـ ١٤٣٤ / ٠٢ / ١٠ الغبن ، ثم تم تخارج االخوة في حصصھم بتاریخ : ) أعوام ولم یدعي ٧ ھـ وبقي بعدھا علی قید الحیاة لمدة ( ١٤٣١ / ١٠ / ١٦ . ایضا ولم یدعو الغبن وبعد وفاة المورث رفعو دعوى الغبن في قیمة حصة السھم عند شرائي ھـ ، مما یدل عدم صفتھم فالدعوى ١٤٣١ </t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>النوع: وكالة | الأطراف: عاتقة الحرازي | تواريخ هجرية: 1445/03/19، 1446/03/19 | مقتطف: : فارطلأا أصالة عن نفسه ١ مو ل عاتقه محمدي محمدع ا رازي سعودية ل مد ي ١٠٠٧٠٥٦٨٤٧ أصالة عن نفسه #\ الطرف االسم ا سية نوع ال و ة رقم ال و ة الصفة النطاق : ٢ وكيل محمد فواز بن من الثع سعودي ل مد ي ١٠٩٨٩٠٨٢٧٨ ميلس لا و ملاتسلاا - كلذ بلطتي اميف عيقوتلاو ةمزلالا تاءارجلإا عيمج ءا إو ةقلاعلا تاذ تا ا عيمج</t>
+          <t>النوع: وكالة | الأطراف: عاتقة الحرازي | تواريخ هجرية: 1445/03/19، 1446/03/19 | مقتطف: : فارطلأا أصالة عن نفسه ١ مو ل عاتقه محمدي محمدع ا رازي سعودية ل مد ي ١٠٠٧٠٥٦٨٤٧ أصالة عن نفسه #\ الطرف االسم ا سية نوع ال و ة رقم ال و ة الصفة النطاق : ٢ وكيل محمد فواز بن من الثع سعودي ل مد ي ١٠٩٨٩٠٨٢٧٨ - يحق للوكيل توكيل الغ - مراجعة جميع ا ات ذات العالقة وإ اء جميع اإلجراءات الالزمة والتوقيع فيم</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-04-17، 1445/04/08، 1445/04/14 | مقتطف: منصة ناجز زيني سابع نب دمحا نب هماسأ / ابحرم بلطلا ليصافت ذيفنتلا تامولعملا ةحول ليصافتلا ةفاك بلطلا لحارم غيلبتلا ةلحرم بلطلا ميدقت دادس ةروتاف رادصإ بلطلا لوبق مت 08/04/1445 08/04/1445 ةيمقرلا بلطلا ةظفحم بلطلا ليصافت ةمكحملا يعرفلا دنسلا عون يسيئرلا دنسلا عون بلطلا يف ةفصلا محكمة التنفيذ بجدة حكم</t>
+          <t xml:space="preserve">النوع: محضر | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-04-17، 1445/04/08، 1445/04/14 | مقتطف: منصة ناجز زيني مرحلة التبليغ مراحل الطلب كافة التفاصيل لوحة المعلومات التنفيذ تفاصيل الطلب مرحبا / أسامه بن احمد بن عباس بلطلا ميدقت دادس ةروتاف رادصإ 08/04/1445 تم قبول الطلب 08/04/1445 محفظة الطلب الرقمية بلطلا ليصافت المحكمة يعرفلا دنسلا عون نوع السند الرئيسي الصفة في الطلب محكمة التنفيذ بجدة نم </t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: منصة ناجز AM 9:02 ,10/3/23 بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 مقر ذيفنت بلط بلطلا ميدقت ينمزلا طخلا بلطلا تانايب نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 ... محا نب هماسأ / ابحرم https://new.najiz.sa/applications/iexecution/Request</t>
+          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: 10/3/23, 9:02 AM زجان ةصنم بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 دليل المرخصين بيانات الطلب الخط الزمني تقديم الطلب طلب تنفيذ رقم ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 ... محا نب هماسأ / ابحرم https://new.najiz.sa/applications/iexecution/Request</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446، 1,769,886,051 ريال | تواريخ هجرية: 1411/4/11، 1432/12/1 | مقتطف: المملكة العربية السعودية يحلا زرخلا هللا مسب ةدجب ةيرادإلا ةمكحملا ملاظملا ناويد ةرشع ةعباسلا ةرئادلا في رقم ٢/١٧/١٨٥ لعام ١٤٣٢هـ القضيتين رقم ٢/٥٧٩٨/ق لعام ١٤٣١ هـ ورقم ٢/١٣٧٥/ق لعام ١٤٣٢هـ المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد عباس زيني ضد / أسامة بن أحمد بن </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: ديوان المظالم | مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446، 1,769,886,051 ريال | تواريخ هجرية: 1411/4/11، 1432/12/1 | مقتطف: المملكة العربية السعودية بسم الله الخرز الحي المحكمة الإدارية بجدة ديوان المظالم الدائرة السابعة عشرة في رقم ٢/١٧/١٨٥ لعام ١٤٣٢هـ القضيتين رقم ٢/٥٧٩٨/ق لعام ١٤٣١ هـ ورقم ٢/١٣٧٥/ق لعام ١٤٣٢هـ المقامة من / عدنان بن أحمد بن عباس زيني وطلال وفيصل وغدير أولاد غازي بن أحمد عباس زيني ضد / أسامة بن أحمد بن </t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أحمد زيني (المورّث)، عاتقة الحرازي | صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219 ريال | مقتطف: 5149 قباــسلا تحميل إخطار بمطالبة مالية 440300010192 مقر ةيلاملا ةبلاطملا ـ بلطلا مدقمل ةيصخشلا تانايبلا الاسم: محمد بن فواز بن منير الثعلي رقم الهوية أو الإقامة: 1098908278 ةلاكولا تانايب اسم الموكل: عدنان احمد عباس زيني رقم هوية الموكل: 1017092733 ةيلاملا ةبلاطملا تانايب 556355663 لاوجلا مقر ـ 100</t>
+          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أحمد زيني (المورّث)، عاتقة الحرازي | صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219 ريال | مقتطف: 5149 الســابق تحميل إخطار بمطالبة مالية البيانات الشخصية لمقدم الطلب ـ المطالبة المالية رقم 440300010192 الاسم: محمد بن فواز بن منير الثعلي رقم الهوية أو الإقامة: 1098908278 بيانات الوكالة اسم الموكل: عدنان احمد عباس زيني رقم هوية الموكل: 1017092733 بيانات المطالبة المالية صفة المراد إخطاره: فرد ـ ر</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة، ديوان المظالم | مبالغ: 368,000,000، 120,000,000، 450,000 ريال | تواريخ هجرية: 02/02/1438، 03/09/1435، 04/03/1432، 10/02/1438 | مقتطف: Page 1 of 9 المحكمة العامة بمحافظة جدة رقم الصك : ٣٨٥٥٨٤٩ تاريخه : ١٠/٠٢/١٤٣٨ هـ صك رشع ةثلاثلا ةيقولحلا ةرئادملا ةدج ةظفاحمب ةماعلا ةمكحملا لدعلا ةرازو شهورة طبق الأصل بتاريخ ٢ ) اه صفحة رقم: 1 من الحمد لله وحده وبعد فلدي أنا ايمن بن محمد عياش هاشم القاضي في المحكمة العامة بمحافظة جدة القائم بعمل ا</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة، ديوان المظالم | مبالغ: 368,000,000، 120,000,000، 450,000 ريال | تواريخ هجرية: 02/02/1438، 03/09/1435، 04/03/1432، 10/02/1438 | مقتطف: Page 1 of 9 المحكمة العامة بمحافظة جدة رقم الصك : ٣٨٥٥٨٤٩ تاريخه : ١٠/٠٢/١٤٣٨ هـ صك وزارة العدل المحكمة العامة بمحافظة جدة المدائرة الحلوقية الثالثة عشر شهورة طبق الأصل بتاريخ ٢ ) اه صفحة رقم: 1 من الحمد لله وحده وبعد فلدي أنا ايمن بن محمد عياش هاشم القاضي في المحكمة العامة بمحافظة جدة القائم بعمل ا</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | تواريخ هجرية: 1445/04/10 | مقتطف: طلب نقض رقم الطلب 4510628072 بلطلا ةلاح مرفوض المحكمة الدائرة تاريخ الطلب ١٤٤٥/٠٤/١٠ المحكمة التجارية بجدة دائرة الاستئناف الثانية الاستئناف</t>
+          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | تواريخ هجرية: 1445/04/10 | مقتطف: طلب نقض رقم الطلب 4510628072 حالة الطلب مرفوض المحكمة الدائرة تاريخ الطلب ١٤٤٥/٠٤/١٠ المحكمة التجارية بجدة دائرة الاستئناف الثانية الاستئناف</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | تواريخ هجرية: 10 / 2 / 1438، 1438/4/21 | مقتطف: دشار وبأ يماس دلاخ يماحملا بتكم للإستشارات القانونية والمحاماة ترخيص رقم ( ٢٣/١٤٠) وزارة العدل 31004149940000 :يبيرضلا مقرلا Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 ΔΙΔ بسم الله الرحمن الرحيم (عاجل </t>
+          <t xml:space="preserve">النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | تواريخ هجرية: 10 / 2 / 1438، 1438/4/21 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم ( ٢٣/١٤٠) وزارة العدل الرقم الضريبي: 31004149940000 Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 ΔΙΔ بسم الله الرحمن الرحيم (عاجل </t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
+          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
+          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 1423/02/20، 1431/11/29، 1431/9/20، 1434/11/24 | مقتطف: التنفيذيون ةينوناقلا تاراشتسالاو ةاماحملل نوب ريظنتلا ةكرش التاريخ : ١٤٤٥/٠٧/١٣هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية ١٤٤٢/١٢/٢٥هـ بجدة ب</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 1423/02/20، 1431/11/29، 1431/9/20، 1434/11/24 | مقتطف: التنفيذيون شركة التنظير بون للمحاماة والاستشارات القانونية التاريخ : ١٤٤٥/٠٧/١٣هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية ١٤٤٢/١٢/٢٥هـ بجدة ب</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | تواريخ هجرية: 1447/09/02 | مقتطف: دشار وبأ يماس دلاخ يماحملا بتكم ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل ينيز ةماسأ نب دمحأ / ديسلا Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 بسم ال</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | تواريخ هجرية: 1447/09/02 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ السيد / أحمد بن أسامة زيني Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 بسم ال</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة، ديوان المظالم | مبالغ: 368,000,000، 120,000,000، 450,000 ريال | تواريخ هجرية: 02/02/1438، 03/09/1435، 04/03/1432، 10/02/1438 | مقتطف: Page 1 of 9 المحكمة العامة بمحافظة جدة رقم الصك : ٣٨٥٥٨٤٩ تاريخه : ١٠/٠٢/١٤٣٨ هـ صك رشع ةثلاثلا ةيقولحلا ةرئادملا ةدج ةظفاحمب ةماعلا ةمكحملا لدعلا ةرازو شهورة طبق الأصل بتاريخ ٢ ) اه صفحة رقم: 1 من الحمد لله وحده وبعد فلدي أنا ايمن بن محمد عياش هاشم القاضي في المحكمة العامة بمحافظة جدة القائم بعمل ا</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة، ديوان المظالم | مبالغ: 368,000,000، 120,000,000، 450,000 ريال | تواريخ هجرية: 02/02/1438، 03/09/1435، 04/03/1432، 10/02/1438 | مقتطف: Page 1 of 9 المحكمة العامة بمحافظة جدة رقم الصك : ٣٨٥٥٨٤٩ تاريخه : ١٠/٠٢/١٤٣٨ هـ صك وزارة العدل المحكمة العامة بمحافظة جدة المدائرة الحلوقية الثالثة عشر شهورة طبق الأصل بتاريخ ٢ ) اه صفحة رقم: 1 من الحمد لله وحده وبعد فلدي أنا ايمن بن محمد عياش هاشم القاضي في المحكمة العامة بمحافظة جدة القائم بعمل ا</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | صكوك: 4630548401 | تواريخ هجرية: 03 / 06 / 1447، 24/04/1446، 25/08/1445 | مقتطف: حصت العربية السعودية صك رقم 87١41١41١1"1/اء‏ مي _-_-_- #6 محكمة الاستئناف بمحافقظة جدة رقم الصفحة: ‎١‏ نا 0 ‏١440/.0/97‎ :كصلا خيرات | لوألا ةيقوقحلا ةرئادلا الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الحقوقية الأولى وبناء على القاضية رقم ‎852591١‏ الالا2 وتاريخ ./5.//ا55١‏ ه لل د</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | صكوك: 4630548401 | تواريخ هجرية: 03 / 06 / 1447، 24/04/1446، 25/08/1445 | مقتطف: حصت العربية السعودية صك رقم 87١41١41١1"1/اء‏ مي _-_-_- #6 محكمة الاستئناف بمحافقظة جدة رقم الصفحة: ‎١‏ نا الدائرة الحقوقية الأول | تاريخ الصك: ‎١440/.0/97‏ 0 الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الحقوقية الأولى وبناء على القاضية رقم ‎852591١‏ الالا2 وتاريخ ./5.//ا55١‏ ه لل د</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، عاتقة الحرازي | مقتطف: أسامھ بن احمد بن عباس زيني تاكرشلا مكحن تابثإ عباس لزانتلا زيني جراختلاو نم ب دمحا نب ھماسأ أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ أسام</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، عاتقة الحرازي | مقتطف: أسامھ بن احمد بن عباس زيني تاكرشلا من والتخارج ينيز التنازل سابع إثبات نحكم أسامھ بن احمد ب أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسام</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | تواريخ هجرية: 07 / 10 / 1447، 1447 / 04 / 13، 1447 / 04 / 29، 1447 / 09 / 09 | مقتطف: بسم هللا الرحمن الرحيم السالم عليكم ورحمة هللا وبركاته وبعد سلمههللا أصحاب الفضيلة / رئيس وقضاة املحكمة العليا ضقنلا بلطب ضارتعا ةحئلا: عوضولما قفاولما ءاعبرلأا موي يف ةدجب ةيراجتلا فانئتسلاا ةمكحم ىدل ةفيحصلا هذه تعدوأ 07 / 10 / 1447 يماحلما نم ـه / ،.... / / خيراتو ...مقر صيخرتلا بجومب ةرازولاب ةا</t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | تواريخ هجرية: 1447 / 04 / 13، 1447 / 04 / 29، 1447 / 09 / 09، 1447 / 10 / 07 | مقتطف: بسم هللا الرحمن الرحيم السالم عليكم ورحمة هللا وبركاته وبعد سلمههللا أصحاب الفضيلة / رئيس وقضاة املحكمة العليا املوضوع :الئحة اعتراض بطلب النقض هـ من املحامي 1447 / 10 / 07 أودعت هذه الصحيفة لدى محكمة االستئناف التجارية بجدة في يوم األربعاء املوافق . ه 144 املرخص من وزارة العدل واملقيد بسجالت إدارة </t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | تواريخ هجرية: 1447/07/15 | مقتطف: طلب الاعتراض على الأحكام رقم الطلب بلطلا ةلاح المحكمة الدائرة تاريخ الطلب ١٤٤٧/٠٧/١٥ 4714060501 بانتظار انتهاء المدة الاعتراضية المحكمة التجارية بجدة الدائرة الاولى ىلوألا ةجردلا ...</t>
+          <t>النوع: حكم / صك | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | تواريخ هجرية: 1447/07/15 | مقتطف: طلب الاعتراض على الأحكام رقم الطلب حالة الطلب المحكمة الدائرة تاريخ الطلب ١٤٤٧/٠٧/١٥ 4714060501 بانتظار انتهاء المدة الاعتراضية المحكمة التجارية بجدة الدائرة الاولى الدرجة الأولى ...</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | تواريخ هجرية: 1447/04/29 | مقتطف: طلب التماس إعادة نظر رقم الطلب بلطلا ةلاح المحكمة الدائرة 4713382931 تم الاستلام في الدائرة القضائية المحكمة التجارية بجدة الدائرة الاولى تاريخ الطلب ١٤٤٧/٠٤/٢٩ ىلوألا ةجردلا ...</t>
+          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | تواريخ هجرية: 1447/04/29 | مقتطف: طلب التماس إعادة نظر رقم الطلب حالة الطلب المحكمة الدائرة 4713382931 تم الاستلام في الدائرة القضائية المحكمة التجارية بجدة الدائرة الاولى تاريخ الطلب ١٤٤٧/٠٤/٢٩ الدرجة الأولى ...</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | تواريخ هجرية: 1447/04/29 | مقتطف: طلب التماس إعادة نظر رقم الطلب بلطلا ةلاح المحكمة الدائرة 4713382931 تم الاستلام في الدائرة القضائية المحكمة التجارية بجدة الدائرة الاولى تاريخ الطلب ١٤٤٧/٠٤/٢٩ ىلوألا ةجردلا</t>
+          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | تواريخ هجرية: 1447/04/29 | مقتطف: طلب التماس إعادة نظر رقم الطلب حالة الطلب المحكمة الدائرة 4713382931 تم الاستلام في الدائرة القضائية المحكمة التجارية بجدة الدائرة الاولى تاريخ الطلب ١٤٤٧/٠٤/٢٩ الدرجة الأولى</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | مقتطف: 5] طلب نقه رقم الطلب 4714689866 ايلعلا ةمكحملا ىلإ لاحم 2 بلطلا ةلاح المحكمة التجارية بجدة الدائرة دائرة الاستئناف الثانية تاريخ الطلب ‎٠١١‏ /لاعع!</t>
+          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | مقتطف: 5] طلب نقه رقم الطلب 4714689866 حالة الطلب 2 محال إلى المحكمة العليا المحكمة التجارية بجدة الدائرة دائرة الاستئناف الثانية تاريخ الطلب ‎٠١١‏ /لاعع!</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450,000 ريال | مقتطف: ةيسيئرلا اياضقلا ىلع تابلطلا طلب نقض الصفحة القضاء ةيضقلا عون ةيضقلا فينصت ةيضقلا ةلاح ةرئادلا ةمكحملا ةيضقلا خيرات ةيضقلا مقر ةيماظنلا تاكرشلا فانئتسلاا ةمكحم ىلإ ةلاحم ىلولاا ةرئادلا ةدجب ةيراجتلا ةمكحملا ١٤٤٢ ةجحلا وذ ٢٥ 42824717 ó° ó° ةيضقلا تانايب ó° بلطلا مدقم تانايب ó° \* بلطلا مدقم تانايب ó°</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العامة بجدة، ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450,000 ريال | مقتطف: الطلبات على القضايا الرئيسية طلب نقض الصفحة القضاء °ó بيانات القضية °ó °ó 42824717 ٢٥ ذو الحجة ١٤٤٢ المحكمة التجارية بجدة الدائرة االولى محالة إلى محكمة االستئناف الشركات النظامية رقم القضية تاريخ القضية المحكمة الدائرة حالة القضية تصنيف القضية نوع القضية بلطلا مدقم تانايب ó° \* بلطلا مدقم تانايب ó°</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: أسامة زيني | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | مقتطف: ينيز سابع نب دمحا نب ھماسأ [العنوان مكرر مرات عديدة في رأس كل صفحة] CamScanner ـب ايئوض ةحوسمملا [:يلاتلاك اهصن ،لدعلا ةرازو نع ةرداص ةينورتكلإ ةلاكو ةقيثو وه دنتسملا ةياهن يف ةءارقلل لباقلا يلعفلا ىوتحملا وذ ءزجلا ."CamScanner ـب ايئوض ةحوسمملا" ةرابع عم ،ةديدع تاحفص ربع سوكعم يبرع زيمرتب رركم "يني</t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | مقتطف: أسامھ بن احمد بن عباس زيني الممسوحة ضوئيا بـ CamScanner [ملاحظة المعالجة: ملف PDF ممسوح ضوئيا بـ CamScanner، حجمه نحو 4.45 ميجابايت، ومعظم النص المستخرج عبارة عن عنوان "أسامة بن احمد بن عباس زيني" مكرر بترميز عربي معكوس عبر صفحات عديدة، مع عبارة "الممسوحة ضوئيا بـ CamScanner". الجزء ذو المحتوى الفعل</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زين | | | :-: | | [**Page 1**]() | ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احم</t>
+          <t>النوع: حكم / صك | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زين | | | :-: | | [**Page 1**]() | أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احم</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 120,000,000 ريال | مقتطف: مذكرة إلحاقية ببيان أهم التناقضات التي تعزز قبول التماس إعادة النظر :ةيلاتلا طاقنلا يف اهلمجأ :عئاقولا وقّع الملتمس عقدًا صحيحًا مع والده بتاريخ 20/09/1431هـ، وعليه أيضا توقيع البائع وهناك شهود هم: الأستاذ فيصل القثامي، والأستاذ عدنان النهدي، والأستاذ عماد القرعاوي، وهو تصرف صحيح ومتوافق مع صحيح الش</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 120,000,000 ريال | مقتطف: مذكرة إلحاقية ببيان أهم التناقضات التي تعزز قبول التماس إعادة النظر الوقائع: أجملها في النقاط التالية: وقّع الملتمس عقدًا صحيحًا مع والده بتاريخ 20/09/1431هـ، وعليه أيضا توقيع البائع وهناك شهود هم: الأستاذ فيصل القثامي، والأستاذ عدنان النهدي، والأستاذ عماد القرعاوي، وهو تصرف صحيح ومتوافق مع صحيح الش</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
+          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | صكوك: 4530241622 | مبالغ: 450,000، 170، 120 ريال | مقتطف: السلام عليكم ورحمه الله وبركاته»: وبعد الموضوع/ مذكرة إلحاقية بشأن التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم( 4530241622) بتاريخ 1445/03/13ه والمقدم من الملتمس/أسامة زيني ضد الملتمس ضدهم وهما شقيقه عدنان ووالدته عاتقة إشارة لموضوع الدعوى والحك</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | صكوك: 4530241622 | مبالغ: 368,757,931، 450,000، 170، 120 ريال | مقتطف: السلام عليكم ورحمه الله وبركاته»: وبعد الموضوع/ مذكرة إلحاقية بشأن التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم( 4530241622) بتاريخ 1445/03/13ه والمقدم من الملتمس/أسامة زيني ضد الملتمس ضدهم وهما شقيقه عدنان ووالدته عاتقة إشارة لموضوع الدعوى والحك</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | مقتطف: == وثيقة وكالة - وزارة العدل، المملكة العربية السعودية == .لدعلا ةرازول ةينورتكلإلا تامدخلا ربع اهتحص نم ققحتلا نكميو ،قيثوتلا تامدخو ينورتكلإلا ماظنلا نم ةقيثولا هذه تردص :فارطألا 1 - الموكل: أسامة بن أحمد بن عباس زيني، سعودي، رقم هوية 1008017301، أصالة عن نفسه. 2 - الوكيل: علي بن مشرف بن مفرح بن ر</t>
+          <t>النوع: مذكرة قضائية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | مقتطف: == وثيقة وكالة - وزارة العدل، المملكة العربية السعودية == صدرت هذه الوثيقة من النظام الإلكتروني وخدمات التوثيق، ويمكن التحقق من صحتها عبر الخدمات الإلكترونية لوزارة العدل. الأطراف: 1 - الموكل: أسامة بن أحمد بن عباس زيني، سعودي، رقم هوية 1008017301، أصالة عن نفسه. 2 - الوكيل: علي بن مشرف بن مفرح بن ر</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | مقتطف: ينيز سابع نب دمحا نب هماسأ [العنوان مكرر مرات عديدة بترميز معكوس في رأس كل صفحة] [ملاحظة المعالجة: مذكرة النقض إلى المحكمة العليا بتاريخ 10-04-1445هـ، القضية 42824717، مرفق بها عقود التخارج وتقرير أحمد زيني رحمه الله. ملف PDF حجمه نحو 5.2 ميجابايت. معظم النص المستخرج عبارة عن العنوان "أسامة بن أحمد </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث) | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | مقتطف: أسامه بن احمد بن عباس زيني [ملاحظة المعالجة: مذكرة النقض إلى المحكمة العليا بتاريخ 10-04-1445هـ، القضية 42824717، مرفق بها عقود التخارج وتقرير أحمد زيني رحمه الله. ملف PDF حجمه نحو 5.2 ميجابايت. معظم النص المستخرج عبارة عن العنوان "أسامة بن أحمد بن عباس زيني" مكرر بترميز عربي معكوس عبر صفحات عديدة. </t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: أسامة زيني | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 23-09-1445 | مقتطف: .لدعلا ةرازول ةينورتكلإلا تامدخلا ربع ةقيثولا ةحص نم ققحتلا نكميو ،قيثوتلا تامدخ نمو ينورتكلإلا ماظنلا نم ةقيثولا هذه تردص وثيقة وكالة - وزارة العدل - المملكة العربية السعودية ةدمتعم :ةلاكولا ةلاح - ةينورتكلإلا تالاكولا تامدخ :فارطألا الطرف الموكل: أسامة بن احمد بن عباس زيني - سعودي - رقم الهوية 100</t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني | المحاكم: محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم، المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 23-09-1445 | مقتطف: صدرت هذه الوثيقة من النظام الإلكتروني ومن خدمات التوثيق، ويمكن التحقق من صحة الوثيقة عبر الخدمات الإلكترونية لوزارة العدل. وثيقة وكالة - وزارة العدل - المملكة العربية السعودية ةدمتعم :ةلاكولا ةلاح - ةينورتكلإلا تالاكولا تامدخ الأطراف: الطرف الموكل: أسامة بن احمد بن عباس زيني - سعودي - رقم الهوية 100</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | قضايا: 42824717 | تواريخ هجرية: 04 / 03 / 1445، 06 / 03 / 1445 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ :يخراتلا 06 / 03 / 1445 ـه :قفاولما 21 / 0</t>
+          <t>النوع: مذكرة قضائية | قضايا: 42824717 | تواريخ هجرية: 06 / 03 / 1445، 1445 / 03 / 04 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا :يخراتلا 06 / 03 / 1445 ـه :قفاولما 21 / 0</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1434/02/10، 1445/03/13 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدصلا ةرازو (٢٣/١٤٠ ) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم مسودة) Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 ال</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1434/02/10، 1445/03/13 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم ( ٢٣/١٤٠) وزارة الصدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ بسم الله الرحمن الرحيم مسودة) Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 ال</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عاتقة الحرازي | قضايا: 42824717 | صكوك: 4630548401 | تواريخ هجرية: 02 / 06 / 1446، 13 / 03 / 1445، 18 / 06 / 1446، 28 / 04 / 1447 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ : يخراتلا 28 / 08 / 1447 ـه :قفاولما 16 / </t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عاتقة الحرازي | قضايا: 42824717 | صكوك: 4630548401 | تواريخ هجرية: 1445 / 03 / 13، 1446 / 06 / 02، 1446 / 06 / 18، 1447 / 04 / 28 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا : يخراتلا 28 / 08 / 1447 ـه :قفاولما 16 / </t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 135 ريال | مقتطف: التاريخ: 15/08/1445هـ (درو اذكه) م25/02/2023 :قفاوملا أصحاب الفضيلة رئيس وأعضاء دائرة الاستئناف التجارية الثانية بمحكمة الاستئناف التجارية، سلمهم الله السلام عليكم ورحمة الله وبركاته الموضوع: مذكرة جوابية مقدمة من المستلمَس ضدهم في الالتماس المقدم من أسامة أحمد زيني، بالقضية رقم 42824717. إشارة إلى </t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 135 ريال | مقتطف: التاريخ: 15/08/1445هـ الموافق: 25/02/2023م (هكذا ورد) أصحاب الفضيلة رئيس وأعضاء دائرة الاستئناف التجارية الثانية بمحكمة الاستئناف التجارية، سلمهم الله السلام عليكم ورحمة الله وبركاته الموضوع: مذكرة جوابية مقدمة من المستلمَس ضدهم في الالتماس المقدم من أسامة أحمد زيني، بالقضية رقم 42824717. إشارة إلى </t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، عاتقة الحرازي | قضايا: 42824717 | تواريخ هجرية: 1432 - 11 - 07 | مقتطف: حفظهم هللا أسامھ بن احمد بن بن عباس زيني ،،، دمحةقيرطب جاتن ا ندض رومالا ب ةماقلما ھماسنم ) 42824717 ددعل :ليي أ احيضوتو ماك لكذ ( قب قمر نايبو س ىوعلدا الماديك متهبلاطلمةتبثلماو في أت تتم دق هيلع ى عدملل ةيراجتلا نييز دحما انه أب عفدي ةراتف اهل هكلتم ةيل أو صصلحا هذه هي عيبلا ةيمق نا عمزي ىرخا ةرتا</t>
+          <t xml:space="preserve">النوع: تقرير خبرة | الأطراف: أسامة زيني، عاتقة الحرازي | قضايا: 42824717 | تواريخ هجرية: 07 - 11 - 1432 | مقتطف: حفظهم هللا أسامھ بن احمد بن بن عباس زيني ،،، دمحةقيرطب جاتن ا ندض رومالا ب ةماقلما املدعى علهيم يزمع بوجود عقد بيع احلصص مربم املدعى عليه املش بوه يف الاس تحواذ عىل حقوق 000،450 رايل واترة اخرى يزمع ان قمية البيع يه هذه احلصص وأ لية متلكه لها فتارة يدفع بأ هنا امحد زيين التجارية للمدع ى عليه قد متت </t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000، 1,000 ريال | تواريخ هجرية: 1/6/1442، 10 / 5 / 1436، 11/ 2 / 1434، 1392/2/15 | مقتطف: التنفيذيون شركة التنفيذيون للمحاماة والاستشارات القانونية التاريخ: ١٤٤٥/٠٤/١٠هـ فضيلة رئيس المحكمة العليا سلمه الله السلام عليكم ورحمه الله وبركاته، وبعد: طلب نقض الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بالصك رقم ( ٤٥٣٠٢٤١٦٢٢) بتاريخ ١٤٤٥/٠٣/١٣هـ في القضية رقم ( ٤٢٨٢٤٧١٧) وتار</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 5,000,000، 500,000، 450,000 ريال | تواريخ هجرية: 1/6/1442، 10 / 5 / 1436، 10/ 2 / 1434، 11/ 2 / 1434 | مقتطف: التنفيذيون شركة التنفيذيون للمحاماة والاستشارات القانونية التاريخ: ١٤٤٥/٠٤/١٠هـ فضيلة رئيس المحكمة العليا سلمه الله السلام عليكم ورحمه الله وبركاته، وبعد: طلب نقض الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بالصك رقم ( ٤٥٣٠٢٤١٦٢٢) بتاريخ ١٤٤٥/٠٣/١٣هـ في القضية رقم ( ٤٢٨٢٤٧١٧) وتار</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
+          <t>النوع: مذكرة قضائية | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد ب</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | تواريخ هجرية: 1431/9/20، 1432/12/2، 1432/3/4، 1433/6/8 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني ابع نب دمحا نب ھماسأ ابع نب دمحا نب ھماسأ [ةلازغ وبا ريرقت ىلع ضارتعالا ـ 20-02-1445</t>
+          <t>النوع: مذكرة قضائية | تواريخ هجرية: 1431/9/20، 1432/12/2، 1432/3/4، 1433/6/8 | مقتطف: أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عبا [ملف PDF ممسوح ضوئياً - النص مشوّش/غير قاب</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة العامة بجدة | مبالغ: 500,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/10/26، 1413/9/8 | مقتطف: untitled مكتب عزام فيصل خوج امون ومستشارون قـ انونيون Law Office of Azzam Faisal Khouj ATTORNEYS &amp; LEGAL CONSULTANTS م٢٠١٣/٥/١٥ قفاوملا ـه١٤٣٤/٧/٥ صاحب الفضيلة الشيخ / السلام عليكم ورحمة الله و وبر ةدجب ةماعلا ةمكحملاب يضاقلا ركاته،، الموضوع مذكرة ختامية الرقم : ٢٠١٣/٤/١٤٧ حفظه الله أتقدم لمقام فضيل</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة العامة بجدة | مبالغ: 500,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/10/26، 1413/9/8 | مقتطف: untitled مكتب عزام فيصل خوج امون ومستشارون قـ انونيون Law Office of Azzam Faisal Khouj ATTORNEYS &amp; LEGAL CONSULTANTS ١٤٣٤/٧/٥هـ الموافق ٢٠١٣/٥/١٥م صاحب الفضيلة الشيخ / السلام عليكم ورحمة الله و وبر القاضي بالمحكمة العامة بجدة ركاته،، الموضوع مذكرة ختامية الرقم : ٢٠١٣/٤/١٤٧ حفظه الله أتقدم لمقام فضيل</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | تواريخ هجرية: 1431/10/16 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا Law office of Khalid Sami Abu Rashed (AA) بسم الله الرحمن الرحيم Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | تواريخ هجرية: 1431/10/16 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ Law office of Khalid Sami Abu Rashed (AA) بسم الله الرحمن الرحيم Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | مبالغ: 450,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/9/8، 1428/3/14 | مقتطف: دشار وبأ يماس دلاخ يماحملا بتكم ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No. : 310041499400003 (AA) بسم الله الرحمن الرحيم الرق</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | مبالغ: 500,000، 450,000، 1,000 ريال | تواريخ هجرية: 12/3/ 1429، 1392/2/15، 1413/9/8، 1428/3/14 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No. : 310041499400003 (AA) بسم الله الرحمن الرحيم الرق</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | مقتطف: ريماني. Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 23/HD مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الر</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | مقتطف: ريماني. Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 23/HD مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ بسم الله الرحمن الر</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم ٢١/١</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 الرقم ٢١/١</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | مقتطف: دشار وبأ يماس دلاخ يماحملا بتكم للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ يبيرضلا مقرلا نادوبا ةماس CD Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 بسم الله الرحمن الر</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ سامة ابودان CD Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT No.: 310041499400003 بسم الله الرحمن الر</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: مكتب المحامي دشار وبأ يماس دلاخ ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ :يبيرضلا مقرلا لدعلا ةرازو (٢٣/١٤٠) مقر صيخرت ةاماحملاو ةينوناقلا تاراشتسإلل بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT NO.: 310041499400003 ( ةيصخشلا </t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: مكتب المحامي خالد سامي أبو راشد للإستشارات القانونية والمحاماة ترخيص رقم (٢٣/١٤٠) وزارة العدل الرقم الضريبي: ٣١٠٠٤١٤٩٩٤٠٠٠٠٣ بسم الله الرحمن الرحيم Law office of Khalid Sami Abu Rashed Legal Consultancy and Legal Profession License No. (23/140) Ministry of Justice VAT NO.: 310041499400003 سعادة الأس</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك اممدعة العربية السعودية هما وزارة العدل ضبط انا لالا 2س -- وير المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 2417814017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎1</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك اممدعة العربية السعودية هما وزارة العدل ضبط الال انا 2س -- وير المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: 2417814017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام على رسول الله أما يعد: قلدى الدائرة الاولى وبناء على القضيّة رقم لا١/ا2587151‏ وتاريخ ‎1</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 241474111 رقمالجلسة: ‎١7‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط الال انا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 241474111 رقمالجلسة: ‎١7‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2578148017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط الال انا مصع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2578148017 رقمالجلسة: ‎١+‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 47814117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١55</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط الال انا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 47814117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١55</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط انا لالا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2478148117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك تملع العربية السعودية 5ه وزارة اتعدل ضبط الال انا مع-11.- المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 2478148117 رقمالجلسة: ‎١4‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 لكك لتمدعة انعربية السعودية 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 257414117 رقمالجلسة: ‎١/‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 لكك لتمدعة انعربية السعودية 5ه وزارة اتعدل ضبط الال انا عملجل- 1خ المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 257414117 رقمالجلسة: ‎١/‏ سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مقتطف: 2 الاك امملعة العربية السعودية هما وزارة العدل ضبط لال انا 0000022222220 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‏ 2141748751107 رقمالجلسة: .”, جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 1,000,070 ريال | مقتطف: 2 الاك امملعة العربية السعودية هما وزارة العدل ضبط لال انا 0000022222220 المحكمة التجارية بجدة رقم الصفحة: ‎١‏ ص ا .]م الدائرة الاولى ‎١‏ رقم القضية: ‏ 2141748751107 رقمالجلسة: .”, جا نت ل له] الحمد لله والصلاة والسلام على رسول الله أما يعد: فلدى الدائرة الاولى وبناء على القضيّة رقم /لا١/ا‏ 2758175 </t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 372,426,828، 120 ريال | تواريخ هجرية: 10/ 2/ 1438 | مقتطف: 2 لكك لتمدعة انعربية السعودية 5ه وزارة اتعدل ضبط انا لالا خ1 -لجلمع المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 247814017 رقمالجلسة: ام سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
+          <t>النوع: محضر | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية، المحكمة العامة بجدة | مبالغ: 372,426,828، 120 ريال | تواريخ هجرية: 10/ 2/ 1438 | مقتطف: 2 لكك لتمدعة انعربية السعودية 5ه وزارة اتعدل ضبط الال انا عملجل- 1خ المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ مي ا الدائرة الاولى ‎١‏ رقم القضية: 247814017 رقمالجلسة: ام سبا نسل لها الحمد لله والصلاة والسلام”على رشّول الله أما يعد: قلدى الدائرة الاولى وبناء على القضية رقم /ا١/ا23587151‏ وتاريخ ‎14/١5/١</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 20,000، 17,000، 1,000 ريال | تواريخ هجرية: 1434/06/30، 1434/11/24، 1454/05/9 | مقتطف: ===== ملف داخلي: 1434/1434 fil no-14- inv 1422.pdf ===== [صفحة 1 - OCR] شركة ابناء محمد عبيد القثمي ‎Mohd. 0. AL Guthmi Sons Co‏ شركة ابناء محمد عبيد القثمي ‎Quotation QS‏ ةيلحتلا:عرفلا التاريخ ‎Date: 1 / Verte Vive‏ أسم العميل: الشيخاحمدزيني ا ‎Clients‏ ‏Clients‎ ظلي طق للمعلم : ليمعلا مقر‏ ‏رقم ال</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 20,000، 17,000، 1,000 ريال | تواريخ هجرية: 1434/06/30، 1434/11/24، 1454/05/9 | مقتطف: ===== ملف داخلي: 1434/1434 fil no-14- inv 1422.pdf ===== [صفحة 1 - OCR] شركة ابناء محمد عبيد القثمي ‎Mohd. 0. AL Guthmi Sons Co‏ شركة ابناء محمد عبيد القثمي ‎Quotation QS‏ الفرع:التحلية التاريخ ‎Date: 1 / Verte Vive‏ أسم العميل: الشيخاحمدزيني ا ‎Clients‏ ‏رقم العميل : ملعملل قط يلظ ‎Clients‏ ‏رقم ال</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 36,171، 30,000، 3,325، 2,000 ريال | تواريخ هجرية: 1435-11-02، 1435/02/01، 1435/02/07، 1435/06/30 | مقتطف: ===== ملف داخلي: 1435/1435 fil no 11 inv 1073.pdf ===== [صفحة 1 - OCR] - 0 ‘ شركة احمد زينى واولاده ‎AHMED ZAINY &amp;SG@MS co...‏ جدة ‏ عمارة اوزكو 1 ‎JEDDAH - 0260 BULLDING‏ هاتف: ١١5؟5.561‏ لس :ا ‎Tel:‏ Fax: 5“ TENE ‏فاكس:‎ مصاريف منزل الشيخ/احمد زينى عن شهر ابريل؟ ‎١١١‏ التاريخ: لل اك ‎Vel‏ ائن مصار</t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 36,171، 30,000، 25,000، 22,500 ريال | تواريخ هجرية: 1435-11-02، 1435/02/01، 1435/02/07، 1435/06/30 | مقتطف: ===== ملف داخلي: 1435/1435 fil no 11 inv 1073.pdf ===== [صفحة 1 - OCR] - 0 ‘ شركة احمد زينى واولاده ‎AHMED ZAINY &amp;SG@MS co...‏ جدة ‏ عمارة اوزكو 1 ‎JEDDAH - 0260 BULLDING‏ هاتف: ١١5؟5.561‏ لس :ا ‎Tel:‏ Fax: 5“ TENE ‏فاكس:‎ مصاريف منزل الشيخ/احمد زينى عن شهر ابريل؟ ‎١١١‏ التاريخ: لل اك ‎Vel‏ ائن مصار</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 60,900، 60,000، 30,000، 20,000 ريال | تواريخ هجرية: 02/10/1435، 02/11/1435، 08/02/1435، 08/04/1434 | مقتطف: ===== ملف داخلي: 1436/1436 OZCO -2015 fil no -13-inv no -971.pdf ===== [صفحة 1 - OCR] 01:28:46 م 2015/7/1 : خيراتلا ‏١‎ ةدودحملاوكزوأ ةكرش ‎Le‏ 55"؛ ه جدة ‎VVOVE‏ صفحة رقم : 1 3 pe re 2 : لسلسملا : ةيعرفلاةيمويلا :2015/7/1 خيراتلا 971 :لسلسم رقم القيد: 971 شرح القيد: مصاريف منزل الشيخ/ احمد زينى عن </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 60,900، 60,000، 30,000، 26,100 ريال | تواريخ هجرية: 02/10/1435، 02/11/1435، 08/02/1435، 08/04/1434 | مقتطف: ===== ملف داخلي: 1436/1436 OZCO -2015 fil no -13-inv no -971.pdf ===== [صفحة 1 - OCR] شركة أوزكوالمحدودة ‎١‏ التاريخ : 2015/7/1 م 01:28:46 ‎Le‏ 55"؛ ه جدة ‎VVOVE‏ صفحة رقم : 1 3 pe re 2 مسلسل: 971 التاريخ :2015/7/1 اليوميةالفرعية : المسلسل : رقم القيد: 971 شرح القيد: مصاريف منزل الشيخ/ احمد زينى عن </t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 40,901,050، 1,662,326، 1,390,810، 60,000 ريال | تواريخ هجرية: 02/10/1435، 02/11/1435، 06/01/1437، 08/02/1435 | مقتطف: ===== ملف داخلي: 2015/2015 OZCO -fil no 18 -inv no 1281.pdf ===== [صفحة 1 - OCR] 09:47:33 ص 2015/8/30 : خيرلتلا ةدودحملا وكزوأ ةكرش ‎ge‏ 514"45 جدة ‎YVOVE‏ صفحة رقم : 1 *- . تقرير رقم : 861009 - : ةيعرفلاةيمويلا :2015/8/30 خيراستلا شرح القيد: مخصص فيلا الشيخ احمد زيني عن شهر اغسطس 9١١1م‏ ]700,50 ]70</t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | مبالغ: 40,901,050، 1,662,326، 1,390,810، 60,000 ريال | تواريخ هجرية: 02/10/1435، 02/11/1435، 06/01/1437، 08/02/1435 | مقتطف: ===== ملف داخلي: 2015/2015 OZCO -fil no 18 -inv no 1281.pdf ===== [صفحة 1 - OCR] شركة أوزكو المحدودة التلريخ : 2015/8/30 ص 09:47:33 ‎ge‏ 514"45 جدة ‎YVOVE‏ صفحة رقم : 1 *- . تقرير رقم : 861009 - التساريخ :2015/8/30 اليوميةالفرعية : شرح القيد: مخصص فيلا الشيخ احمد زيني عن شهر اغسطس 9١١1م‏ ال 50,700[ </t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 03/05/1433، 1/2/1433، 1/3/1433، 1433/02/20 | مقتطف: ===== ملف داخلي: 1433/1433 fil no 12 inv 1238.pdf ===== [صفحة 1 - OCR] SHEIKH AHMED ZAINYS FARM ACCOUNT - GARDEN | ‏مزرعة الشيخ أحمد زينى‎ حساب شهرٌ أبريل 2012م . . + 2012 ‎APRIL,‏ ناتسبلا نايبلا ‏Date‎ خيراتلا | لسلسم مقر‏ ‎Garden Details Ref.No. 2012 S.No.‏ | .م 2012 سرام رهش نع رمع راشب/د مانغألا</t>
+          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 10,851 ريال | تواريخ هجرية: 03/05/1433، 1/2/1433، 1/3/1433، 1433/02/20 | مقتطف: ===== ملف داخلي: 1433/1433 fil no 12 inv 1238.pdf ===== [صفحة 1 - OCR] SHEIKH AHMED ZAINYS FARM ACCOUNT - GARDEN | ‏مزرعة الشيخ أحمد زينى‎ حساب شهرٌ أبريل 2012م . . + 2012 ‎APRIL,‏ ‏رقم مسلسل | التاريخ ‎Date‏ البيان البستان ‎Garden Details Ref.No. 2012 S.No.‏ | - 11255 اتب استشارى الأغنام د/بشار عمر</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 1435/01/06، 1435/03/11، 1435/04/10، 1435/05/11 | مقتطف: ===== ملف داخلي: 1435/1435 fil no 10 inv 955.pdf ===== [صفحة 1 - OCR] e 7 1 AHMED ZAINY &amp;SONS CO ‏شركة احمد زينى واولاده‎ JEDDAH - 0200 BULLDING ‏عمارة اوزكو‎ ةدج‎ Tel: ‏هاتف: 5.5551 كلكفكء5ا‎ Fax: 0“ 5.51.4 ‏فاكس:‎ = رقم القيد: هه؟ ‏١‎ :ةحفصلا نجاودلاةعرزم ةطساوب 1 ‏٠14‎ رياني رهش نع ةيناويحلاو ةيع</t>
+          <t xml:space="preserve">النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 9,290، 9,240 ريال | تواريخ هجرية: 1435/01/06، 1435/03/11، 1435/04/10، 1435/05/11 | مقتطف: ===== ملف داخلي: 1435/1435 fil no 10 inv 955.pdf ===== [صفحة 1 - OCR] e 7 1 AHMED ZAINY &amp;SONS CO ‏شركة احمد زينى واولاده‎ JEDDAH - 0200 BULLDING ‏عمارة اوزكو‎ ةدج‎ Tel: ‏هاتف: 5.5551 كلكفكء5ا‎ Fax: 0“ 5.51.4 ‏فاكس:‎ = رقم القيد: هه؟ بيان القيد: المنصرف على شركة اسامة زينى الزراعية والحيوانية عن شهر </t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 1436/03/23، 1436/6/24، 1436/8/21، 1436/9/27 | مقتطف: ===== ملف داخلي: 1436/OZCO -2015 fil no 5 inv 384.pdf ===== [صفحة 1 - OCR] ةدودحملا وفقك زوأ ةكرش ص.ب 5499 جدة ‎VVOVE‏ 08:41:07 ص 2015/3/11 :(تيراتلا صفحة رقم : 1 تقرير رقم : 4061.009 : ةيعرفلاةيمويلا :2015/3/11 خيراتلا 384 :لسلسم ‏cae‎ ةاعساوب ةيعارلا ةماسا ةكرش ىلع ةفوصتملا ديقلا حرش 384 :ديقلا مق</t>
+          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 1436/03/23، 1436/6/24، 1436/8/21، 1436/9/27 | مقتطف: ===== ملف داخلي: 1436/OZCO -2015 fil no 5 inv 384.pdf ===== [صفحة 1 - OCR] شركة أوز كقفو المحدودة ص.ب 5499 جدة ‎VVOVE‏ التاريت): 2015/3/11 ص 08:41:07 صفحة رقم : 1 تقرير رقم : 4061.009 مسلسل: 384 التاريخ :2015/3/11 اليوميةالفرعية : رقم القيد: 384 شرح القيد المتصوفة على شركة اسامة الراعية بواسعاة ‎cae</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>النوع: مستند مالي | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 01/11/1432، 04/03/1434، 05/11/1431، 06/08/1433 | مقتطف: " ةروكذملا ةرتفلل فيراصملاريتاوف ينيز ةماسأ دمحأ خيشلا نم دمعم ينيز دباع خيشلا ىلا ةعرزملا ريدم نم هجوم عرازملا فيراصم لكب ماع باطخ يلاملا ريدملا و بساحملا نم عقوم يبساحم ديق دنس دمتعم فرص دنس ةعرزملا ريدم نم عقوم 2010 وينوي رهش لالخ ينيز دمحأ خيشلا ةعرزم تافورصمب نايب",يداولاب ينيز دمحأ خيشلا ةعرزم</t>
+          <t xml:space="preserve">النوع: مستند مالي | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 01/11/1432، 04/03/1434، 05/11/1431، 06/08/1433 | مقتطف: مصاريف المزرعة ,,,,,,,,,, 52 ,, ,,,,,,,,,," 2,718,334 ",, ,التسلسل,السنة,رقم القيد,تاريخ الدفعة,نوع العملية,تصنيف العملية,"مستند الصرف (شيك / تحويل بنكي / نقد / اشعار مدين)",طبيعة العملية," المبلغ (ريال سعودي) ",إسم المستفيد,المستندات الداعمة ,1,1431,136,13/01/1431,16/02/2009,مصاريف المزرعة,"مصاريف </t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 03/05/1433، 1/2/1433، 1433/02/20، 1433/03/21 | مقتطف: ===== ملف داخلي: ‏‏1433 - نسخة/1433 fil no 12 inv 1237.pdf ===== [صفحة 1 - OCR] 15.04.12 16.04.12 16.04.12 21.04.12 21.04.12 24.04.12 26.04.12 26.04.12 29.04.12 30.04.12 30.04.12 قمأشارة ‎Ref. wo‏ - 11245 #11254 +11293 +14295 711301 -11306 AP100007244 211322 - 11324 ~ 11326 ~ 11328 ~ 11330 - 11369 “</t>
+          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 19,000,500، 35,000، 1,318 ريال | تواريخ هجرية: 03/05/1433، 1/2/1433، 1433/02/20، 1433/03/21 | مقتطف: ===== ملف داخلي: ‏‏1433 - نسخة/1433 fil no 12 inv 1237.pdf ===== [صفحة 1 - OCR] 15.04.12 16.04.12 16.04.12 21.04.12 21.04.12 24.04.12 26.04.12 26.04.12 29.04.12 30.04.12 30.04.12 قمأشارة ‎Ref. wo‏ - 11245 #11254 +11293 +14295 711301 -11306 AP100007244 211322 - 11324 ~ 11326 ~ 11328 ~ 11330 - 11369 “</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>النوع: غير مصنف | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 556,415 ريال | مقتطف: ===== ملف داخلي: ‏‏2015 - نسخة/Ozco -2015 -fil no 18 -inv no 1275.pdf ===== [صفحة 1 - OCR] 09:23:09 ص 2015/8/30 : خيراتلا ةدودحملا ‏jal pS‎ ةكرش ص.ب 464":ه ‎11١614 ban‏ صفحة رقم : 1 10095160 10095742 10095720 10095749 10095727 10011000 تقرير رقم : #31009 : ةيعرفلاةيمويلا :2015/8/30 خيرالتلا شر القيد</t>
+          <t>النوع: غير مصنف | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 556,415 ريال | مقتطف: ===== ملف داخلي: ‏‏2015 - نسخة/Ozco -2015 -fil no 18 -inv no 1275.pdf ===== [صفحة 1 - OCR] شركة ‎pS jal‏ المحدودة التاريخ : 2015/8/30 ص 09:23:09 ص.ب 464":ه ‎11١614 ban‏ صفحة رقم : 1 10095160 10095742 10095720 10095749 10095727 10011000 تقرير رقم : #31009 التلاريخ :2015/8/30 اليوميةالفرعية : شر القيد</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K134" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 10-07-1434 | مقتطف: ,,"ينيز ةماسأ خيشلا باسح يكيرمألا يدوعسلا كنبلا","عبارلا عيزوتلا -( دوعس لآ زيزعلا دبع نب دمحأ ريمألا ومس و ينيز سابع دمحأ خيشلا نيب ةصاحم دقع) دوعس لآ زيزعلا دبع نب دمحأ ريمألا ومس مسإب يكيرمألا يدوعسلا كنبلا نم رداص 01153128 مقر يفرصم كيش",دوعس لآ زيزعلا دبع نب دمحأ ريمألا," 000,320,2",دوعس لآ زيز</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 10-07-1434 | مقتطف: عقد المحاصة ,التسلسل,السنة,تاريخ العملية,نوع العملية,طبيعة العملية, المبلغ ,إسم المستفيد,المستندات الداعمة,الحساب البنكي المحول منه,, ,1,1434,10-07-1434,عقد المحاصة,ثلاثة شيكات مصرفية صادرة من البنك السعودي الأمريكي من حساب الشيخ أسامة زيني رقم 11210006 لأمر السيد طارق نيازي محمد بدوي,"634,827 ",طار</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>النوع: مستند مالي | الأطراف: أحمد زيني (المورّث) | مقتطف: "هدالوأو ينيز دمحأ ةكرش 4245695 مقر باسح يكيرمألا يدوعسلا كنبلا","يلاملا ريدملا و بساحملا نم دمتعم يبساحم ديق دنس ضرقلا دادس غلبم حضوي هدالوأ و ينيز دمحأ ةكرشل يكيرمألا يدوعسلا كنبلا باسح فشك", يكيرمألا يدوعسلا كنبلا," 308,500 ","12/01/2015 طسق ينيز دمحأ خيشلاب صاخلا يكيرمألا يدوعسلا كنبلا ضرق طسق د</t>
+          <t>النوع: مستند مالي | الأطراف: أحمد زيني (المورّث) | مقتطف: 20M تفاصيل القروض البنكية ,,,,,,,, 25 ,,, ,,,,,,,," 20,043,862 ",,, ,التسلسل,السنة,رقم القيد,تاريخ الدفعة,طريقة السداد,"مستند الصرف (شيك / تحويل بنكي / نقد)",طبيعة العملية," المبلغ (ريال سعودي) ",إسم المستفيد,المستندات الداعمة,الحساب البنكي المحول منه ,1,1431,2947,03/11/2010,سداد مباشر,شيك مصرفي,شيك</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 478,757,110، 11,574,017، 450,000، 170 ريال | مقتطف: 25 1 ةيدوعسلا ةيبرعلا ةكلمللا كلا ل 3 الا حا لست _حجججججججججججججججججبببجب ‏ 3 3 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ 97 م 0_0 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: 8١/8./ة44١‏ 3 90 الآ الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 17/ا27801'4</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | مبالغ: 478,757,110، 368,757,931، 11,574,017، 450,000 ريال | مقتطف: 25 الك اللملكة العربية السعودية 1 ل 3 الا حا لست _حجججججججججججججججججبببجب ‏ 3 3 المحكمة التجارية بجدة رقم الصفحة ‎١ ١‏ 97 م 0_0 دائرة الاستئناف الثانية ‎١‏ تاريخ الصك: 8١/8./ة44١‏ 3 90 الآ الحمد لله والصلاة والسلام”على رشّول الله أما يعد: فلدى دائرة الاستئناف الثانية وبناء على القضية رقم 17/ا27801'4</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>النوع: مستند مالي | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: أسامه بن احمد بن عباس زيني [ملاحظة المعالجة: ملف بعنوان "جزء من مسحوبات مصروفات الشيخ أحمد زيني رحمه الله". ملف PDF حجمه نحو 872 كيلوبايت. النص المستخرج بالكامل عبارة عن العنوان "أسامة بن أحمد بن عباس زيني" مكرر بترميز عربي معكوس عبر المستند، ولا يحتوي على بيانات جدول مالية قابلة للاستخراج النصي (ال</t>
+          <t>النوع: مستند مالي | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: ينيز سابع نب دمحا نب هماسأ [العنوان مكرر مرات عديدة بترميز معكوس عبر المستند بالكامل] [ملاحظة المعالجة: ملف بعنوان "جزء من مسحوبات مصروفات الشيخ أحمد زيني رحمه الله". ملف PDF حجمه نحو 872 كيلوبايت. النص المستخرج بالكامل عبارة عن العنوان "أسامة بن أحمد بن عباس زيني" مكرر بترميز عربي معكوس عبر المستند</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>النوع: مستند مالي | الأطراف: أسامة زيني | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني نيز سابع نب دمحا نب هماسأ نيز سابع نب دمحا نب هماسأ أسامه بن احمد بن عباس زيني أسامه</t>
+          <t>النوع: مستند مالي | الأطراف: أسامة زيني | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زيني أسامه بن احمد بن عباس زين أسامه بن احمد بن عباس زين أسامه بن احمد بن عباس زيني أسامه</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: أسامة زيني | تواريخ هجرية: 1445/03/20، 1446/03/20 | مقتطف: أسامه بن احمد بن عباس زيني [المحتوى مكرر لاسم "أسامة بن احمد بن عباس زيني" مئات المرات — تمثيل OCR متكرر] ،لدعلا ةرازول ةينو كللإا تامد ا ع ةقيثولا ة نم ققحتلا نكم و ، قيثوتلا تامد ي و كللإا ماظنلا نم ةقيثولا هذ تردص : فارطلأا ةفصلا ة و لا مقر ة و لا عون ةيس ا مسلاا فرطلا \# ١ مو ل أسامه بن احمد بن </t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: أسامة زيني | تواريخ هجرية: 1445/03/20، 1446/03/20 | مقتطف: أسامه بن احمد بن عباس زيني [المحتوى مكرر لاسم "أسامة بن احمد بن عباس زيني" مئات المرات — تمثيل OCR متكرر] ،لدعلا ةرازول ةينو كللإا تامد ا ع ةقيثولا ة نم ققحتلا نكم و ، قيثوتلا تامد ي و كللإا ماظنلا نم ةقيثولا هذ تردص : فارطلأا #\ الطرف االسم ا سية نوع ال و ة رقم ال و ة الصفة ١ مو ل أسامه بن احمد بن </t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000، 500 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمد رزيني التاريخ: 1445/04/30هـ بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الح</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000، 50,000 ريال | تواريخ هجرية: 01/ 09/ 1442، 01/08/1444، 02/04/1444، 02/12/1432 | مقتطف: الساعة احمد رزيني التاريخ: 1445/04/30هـ بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الح</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: خدمة الشكوى الإلكترونية :. المجلس الأعلى للقضاء ةينوتركللإا نييز سابع نب دمحا نب هماسأ ابحرم بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا ةيسيئرلا لولأا مسلاا زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة ع</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: خدمة الشكوى الإلكترونية :. المجلس الأعلى للقضاء مرحبا أسامه بن احمد بن عباس زيين اإللكرتونية بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا االسم األول الرئيسية زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى الجنسية رقم الجوال رقم الهوية أصالة ع</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ىوكشلا ةدعاسملا ó°¡3⁄4 تيانايب ó°­μ ةيسيئرلا ó° خي راتلا ةفصلا رقم القضية رقم الشكوى 1445/06/18 أصالة </t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° التار يخ °ó الرئيسية μ­°ó بيانايت 4⁄3¡°ó المساعدة الشكوى الصفة رقم القضية رقم الشكوى 1445/06/18 أصالة </t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | تواريخ هجرية: 1445/06/18 | مقتطف: خدمة الشكوى الإلكترونية المجند الاعلى للقضاء تفاصيل الشكوى الرئيسية طلباتي طلبات غير مكتملة بياناتي للمساعدة ن خروج مرحبا أسامه بن احمد بن عباس زيق بلطلا ةجلاعم مت :ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعترا</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | تواريخ هجرية: 1445/06/18 | مقتطف: خدمة الشكوى الإلكترونية المجند الاعلى للقضاء تفاصيل الشكوى الرئيسية طلباتي طلبات غير مكتملة بياناتي للمساعدة ن خروج مرحبا أسامه بن احمد بن عباس زيق حالة الشكوى: تم معالجة الطلب عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعترا</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمت رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد: ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك </t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمت رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد: ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك </t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمت رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد: ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك </t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمت رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد: ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك </t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/06/18، 1445/11/13 | مقتطف: الشكوى الإلكترونية .اهنلا عارصلا :: الرئيسية طلبانی طلبات غير مكتملة معدلاو لصاوتلا زكرم مرحبا أسامه بن احمد بن عباس زيني بلطلا ةجلاعم مت ىوكشلا ةلاح عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد.. فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/06/18، 1445/11/13 | مقتطف: الشكوى الإلكترونية الصراع النها. :: الرئيسية طلبانی طلبات غير مكتملة مركز التواصل والدعم مرحبا أسامه بن احمد بن عباس زيني حالة الشكوى تم معالجة الطلب عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد.. فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° °ó بيانات مقدم الشكوى ةيضقلا تانايب ó°· ةمكحملا جتلا ةمكحملا ةلئاعلا مسا نييز خي راتلا 1445/06/18 لاوجلا مقر 56355663 دجلا مسا سابع نب يراجت</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° °ó بيانات مقدم الشكوى ·°ó بيانات القضية المحكمة المحكمة التج ةلئاعلا مسا نييز خي راتلا 1445/06/18 رقم الجوال 56355663 دجلا مسا سابع نب يراجت</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K154" t="n">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوى الإلكترونية الرئيسية بیاناتی ةدعاسملا *\ بلطلا رقم الحكم رقم القضية 4431025114 ةفلاخملا يف رظنلا إلغاء 42824717 حدد الحكم المعين تاريخ النطق بالحكم تاريخ تسليم الحكم 1445/01/01 1445/01/01 قباسلا تقديم أسامه بن احمد بن عباس زيني</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوى الإلكترونية الرئيسية بیاناتی المساعدة الطلب \* رقم الحكم رقم القضية 4431025114 النظر في المخالفة إلغاء 42824717 حدد الحكم المعين تاريخ النطق بالحكم تاريخ تسليم الحكم 1445/01/01 1445/01/01 السابق تقديم أسامه بن احمد بن عباس زيني</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: :خیراتلا ٢٦ / ٠٤ / ١٤٤٦ ھـ : لســـالم علیکم ورحمة هللا وبرکاتــــھ .. وبعد ا معالي الدکتور/ ولید بن محمد الصمعاني وزیر العدل ورئیس المجلس األعلی للقضاء ،، سلمھ هللا ھـ ١٤٤٥ - ١١ - ١٣ في ١٩٩٠٥٨ رقم وإلحاقا للشکوى ) ٤٢٨٢٤٧١٧ ھـ في القضیة رقم ( ١٤٤٥ / ٠٣ / ١٣ ) وتاریخ ٤٥٣٠٢٤١٦٢٢ رقم( دائرة االستئناف ال</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: :خیراتلا ٢٦ / ٠٤ / ١٤٤٦ ھـ : لســـالم علیکم ورحمة هللا وبرکاتــــھ .. وبعد ا معالي الدکتور/ ولید بن محمد الصمعاني وزیر العدل ورئیس المجلس األعلی للقضاء ،، سلمھ هللا ھـ ١٤٤٥ - ١١ - ١٣ في ١٩٩٠٥٨ رقم وإلحاقا للشکوى ) ٤٢٨٢٤٧١٧ ھـ في القضیة رقم ( ١٤٤٥ / ٠٣ / ١٣ ) وتاریخ ٤٥٣٠٢٤١٦٢٢ رقم( دائرة االستئناف ال</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | قضايا: 42824717 | تواريخ هجرية: 25/12/1442 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت يرجى تحديد نوع الشكوى أخرى محاكم التنفيذ مرتبطة بقضية ماعلا ءاضقلا في ةروظنملا اياضقلاب ةطبترملا ىواكشلا يدلايم خيراتلا ó°­ عونلا ó° ةفصل</t>
+          <t>النوع: شكوى | قضايا: 42824717 | تواريخ هجرية: 25/12/1442 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت يرجى تحديد نوع الشكوى أخرى محاكم التنفيذ مرتبطة بقضية الشكاوى المرتبطة بالقضايا المنظورة يف القضاء العام ­°ó التاريخ ميالدي عونلا ó° الصف</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة مكحلا ميلست خي رات 1445/01/01 ó°3⁄4ءاغلإ قباسلا ó° لياتلا ó° تواصل معنا المساعدة عن المجلس األعلى للقضاء © ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت مكحلاب قطنلا خي رات 1445/01/01</t>
+          <t>النوع: شكوى | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة °ó التايل °ó السابق إلغاء4⁄3°ó 1445/01/01 تار يخ تسليم الحكم تواصل معنا المساعدة عن المجلس األعلى للقضاء © ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت تار يخ النطق بالحكم 1445/01/01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت مكحلا ميلست خي رات 1445/01/01 ó°3⁄4 ةلئاعلا مسا نييز مكحلاب قطنلا خي رات 1445/01/01 °ó بيانات مقدم الشكوى دجلا مسا سابع نب لاوجلا مقر 556</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت تار يخ تسليم الحكم 1445/01/01 ó°3⁄4 ةلئاعلا مسا نييز تار يخ النطق بالحكم 1445/01/01 °ó بيانات مقدم الشكوى دجلا مسا سابع نب رقم الجوال 556</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01، 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: ءاضقلل ىلعألا سلجملا | ةينورتكلإلا يوكشلا ةمدخ °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ةساردلا ديق بلطلا ó° °ó بيانات مقدم الشكوى خي راتلا 1445/01/05 خي راتلا 1445/06/18 خي راتلا 1446/04/27 ةفصلا أصالة عن نفس</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01، 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° بلطلا ةجلاعم مت ó° ةساردلا ديق بلطلا ó° °ó بيانات مقدم الشكوى خي راتلا 1445/01/05 خي راتلا 1445/06/18 خي راتلا 1446/04/27 الصفة أصالة عن نفس</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: :خيراتلا 09 / 06 / 1446 هـ : لســـالم علیکم ورحمة هللا وبرکاتــــھ .. وبعد ا معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس األعلى للقضاء ،، سلمه هللا 2024 - 10 - 30 ـ 1446 - 04 - 27 في 243138211 والشكوى رقم هـ 1445 - 11 - 13 في 199058 رقم وإلحاقا للشكوى ( 42824717 هـ في القضية رقم ) 1</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: ـه 1446 / 06 / 09 التاريخ: : لســـالم علیکم ورحمة هللا وبرکاتــــھ .. وبعد ا معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس األعلى للقضاء ،، سلمه هللا 2024 - 10 - 30 ـ 1446 - 04 - 27 في 243138211 والشكوى رقم هـ 1445 - 11 - 13 في 199058 رقم وإلحاقا للشكوى ( 42824717 هـ في القضية رقم ) 1</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450، 120 ريال | مقتطف: التاريخ: 17/11 /1445هـ هللا هظفح زيزعلا دبع نب ناملس نب دمحم /ريمألا يكلملا ومسلا بحاص يديس ولي العهد رئيس مجلس الوزراء الســـلام عليكم ورحمة الله وبركاتــــه، وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم رقم( 4530241622) وتاريخ 13/03/1445هـ</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450، 120 ريال | مقتطف: التاريخ: 17/11 /1445هـ سيدي صاحب السمو الملكي الأمير/ محمد بن سلمان بن عبد العزيز حفظه الله ولي العهد رئيس مجلس الوزراء الســـلام عليكم ورحمة الله وبركاتــــه، وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم رقم( 4530241622) وتاريخ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450، 268 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: اسامة احمت رزيني الله الرحمن الرحيم التاريخ: 1445/11/17هـ . ءارزولا سلجم سيئر دهعلا يلو زيزعلا دبع نب ناملس نب دمحم / ريمألا يكلملا ومسلا بحاص يديس السلام عليكم ورحمة الله وبركاته، وبعد: Ossama A. Zainy حفظه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنه</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، ديوان المظالم | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 79,929,906، 36,877,936، 150,000، 17,000 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: اسامة احمت رزيني الله الرحمن الرحيم التاريخ: 1445/11/17هـ . سيدي صاحب السمو الملكي الأمير / محمد بن سلمان بن عبد العزيز ولي العهد رئيس مجلس الوزراء السلام عليكم ورحمة الله وبركاته، وبعد: Ossama A. Zainy حفظه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنه</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/17، 1445/11/22 | مقتطف: تفاصيل الشكوى تفاصیل الشكوى AM 11:12 ,5/30/24 جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/3 » تواصل » تفاصيل الشكوى ردص : : يه يه ةيلاحلا ىوكشلا ةلاح ةيصخشلا تامولعملا 05</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/17، 1445/11/22 | مقتطف: تفاصيل الشكوى تفاصیل الشكوى AM 11:12 ,5/30/24 أهال بك أسامه بن احمد بن عباس زيني | خروج × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/3 » تواصل » تفاصيل الشكوى المعلومات الشخصية حالة الشكوى الحالية هي هي : : صدر مع</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تفاصيل الشكوى تفاصیل الشكوى PM 11:02 ,5/24/24 جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/2 » تواصل » تفاصيل الشكوى ديدج : : يه يه ةيلاحلا ىوكشلا ةلاح ةيصخشلا تامولعملا 0</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تفاصيل الشكوى تفاصیل الشكوى PM 11:02 ,5/24/24 أهال بك أسامه بن احمد بن عباس زيني | خروج × https://tawasol.royalcourt.gov.sa/User/Requests/ComplaintRequestDetails.aspx?ItemID=9f052732-519d-4922-89bf-db7852e863ac\&amp;Msg=0 1/2 » تواصل » تفاصيل الشكوى المعلومات الشخصية حالة الشكوى الحالية هي هي : : جديد ت</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/06/19 | مقتطف: 5/26/24, 9:48 AM دیعاوملا ماظن https://appointments.scj.gov.sa/appointment/appointmentrequest/e2020455-ca34-4f3e-b67c-960e07a223a1 ق 1/2 5/26/24, 9:48 AM دیعاوملا ماظن طلب رقم معلومات مقدم الطلب °ó بلطلا ليصافت دعوملا ببس شأن قضايئ بلطلا مدقم ةفص أصالة عن نفسه رقم القضية 42824717 رقم الشكوى 23074762</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445/06/19 | مقتطف: نظام المواعید AM 9:48 ,5/26/24 https://appointments.scj.gov.sa/appointment/appointmentrequest/e2020455-ca34-4f3e-b67c-960e07a223a1 ق 1/2 نظام المواعید AM 9:48 ,5/26/24 طلب رقم ó° بلطلا مدقم تامولعم بلطلا ليصافت دعوملا ببس ئياضق نأش بلطلا مدقم ةفص أصالة عن نفسه رقم القضية 42824717 رقم الشكوى 23074762</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | مقتطف: تواصل علا ةكلمملا يكلملا ناويدلا » تواصل » طلباتي بلطلا عون بحث --لكلا--\ بلطلا ةلاح --لكلا--\ أهلا بك أسامه بن احمد بن عباس زيني | خروج ـه 1445 ةدعقلا وذ 16 1 :جئاتنلا ددع الرقم الموضوع ةلاحلا تاريخ الطلب بلطلا عون خيارات 1 شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة للقضية ر</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | مقتطف: تواصل المملكة الع الديوان الملكي » تواصل » طلباتي نوع الطلب بحث \--الكل-- حالة الطلب \--الكل-- أهلا بك أسامه بن احمد بن عباس زيني | خروج 16 ذو القعدة 1445 هـ عدد النتائج: 1 الرقم الموضوع الحالة تاريخ الطلب نوع الطلب خيارات 1 شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة للقضية ر</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تأكيد الشكوى تأكید الشكوى PM 10:55 ,5/24/24 جورخ | ينيز سابع نب دمحا نب هماسأ كب لاهأ » تواصل » تأكيد الشكوى 2 ةوطخلا ةيصخشلا تامولعملا 0556355663 :لاوجلا ينيز سابع نب دمحا نب هماسأ :لماكلا مسلاا ossama.zainy@ozco.com :ينورتكللإا ديربلا 1008017301 :ةيوهلا مقر ىوكشلا ليصافت ديدج : ىوكشلا ةلاح نوع الش</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: تأكيد الشكوى تأكید الشكوى PM 10:55 ,5/24/24 أهال بك أسامه بن احمد بن عباس زيني | خروج » تواصل » تأكيد الشكوى 2 ةوطخلا ةيصخشلا تامولعملا تفاصيل الشكوى رقم الهوية: 1008017301 البريد اإللكتروني: ossama.zainy@ozco.com االسم الكامل: أسامه بن احمد بن عباس زيني الجوال: 0556355663 حالة الشكوى : جديد نوع الش</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: التنفيذيون ةيريلاكلا تاراشتسا دلو ةاماحملا نورقلا ةكرش التاريخ : ١٤٤٥/٠٧/١٣ هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم ( </t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/ 09/ 1442، 01/08/1444، 02/04/1444، 02/12/1432 | مقتطف: التنفيذيون شركة القرون المحاماة ولد استشارات الكاليرية التاريخ : ١٤٤٥/٠٧/١٣ هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم ( </t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K170" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K171" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530828230 | مقتطف: التاريخ: .../05/1446هـ م.../11/2024 :قفاوملا "ساـــــمتلا" بــــلط رظــــــــنلا ةداــــعإ صاحب الفضيلة/ رئيس محكمة الاستئناف بالمحكمة التجارية بجدة حفظه الله ورعاه السلام عليكم ورحمة الله وبركاته،،، الحمد لله وحده، والصلاة والسلام على من لا نبي بعده محمد وآلة وصحبه، وبعد ... الموضوع: نلتمس من فضيلت</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530828230 | مقتطف: التاريخ: .../05/1446هـ الموافق: .../11/2024م طلــــب "التمـــــاس" إعــــادة النــــــــظر صاحب الفضيلة/ رئيس محكمة الاستئناف بالمحكمة التجارية بجدة حفظه الله ورعاه السلام عليكم ورحمة الله وبركاته،،، الحمد لله وحده، والصلاة والسلام على من لا نبي بعده محمد وآلة وصحبه، وبعد ... الموضوع: نلتمس من فضيلت</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: صاحب الفضيلة رئيس محكمة الاستئناف بجدة وفقكم االله أصحاب الفضيلة قضاء الدائرة التجارية الثانية بمحكمة الاستئناف بجدة وفقكم الله السلام عليكم ورحمه الله وبركاته الموضوع / التماس إعادة نظر على القضية رقم (42824717) وتاريخ 25/12/1442هـ ةدج :ةماقإلا ناكم () مقر ةيوه ينيز سابع دمحأ ةماسأ / سمتلملا الملتم</t>
+          <t>النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: صاحب الفضيلة رئيس محكمة الاستئناف بجدة وفقكم االله أصحاب الفضيلة قضاء الدائرة التجارية الثانية بمحكمة الاستئناف بجدة وفقكم الله السلام عليكم ورحمه الله وبركاته الموضوع / التماس إعادة نظر على القضية رقم (42824717) وتاريخ 25/12/1442هـ الملتمس / أسامة أحمد عباس زيني هوية رقم () مكان الإقامة: جدة الملتم</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 4,690,483، 2,463,761 ريال | تواريخ هجرية: 1432/4/10، 1432/4/30 | مقتطف: تقرير خبرة ـلوألا ةلحرملا مقدم إلى أطراف النزاع فيما يتعلق ةدجب ةيرادإلا ةمكحملا يف رشع ةعباسلا ةرئادلا ىدل نيتروظنملاو ـه١٤٣٢ ماعل ق ٢/١٣٧٥/ مقرو ـه ١٤٣١ ماعل ق ٢/٥٧٩٨/ مقر نيتيضقلاب مئاقلا عازنلا صوصخب بين المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد زيني والمدعى عليه ال</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 4,690,483، 2,463,761 ريال | تواريخ هجرية: 1432/4/10، 1432/4/30 | مقتطف: تقرير خبرة المرحلة الأولـ مقدم إلى أطراف النزاع فيما يتعلق بالقضيتين رقم ٢/٥٧٩٨/ ق لعام ١٤٣١ هـ ورقم ٢/١٣٧٥/ ق لعام ١٤٣٢هـ والمنظورتين لدى الدائرة السابعة عشر في المحكمة الإدارية بجدة بخصوص النزاع القائم بين المدعين السادة / عدنان أحمد عباس زيني وفيصل وغدير وطلال أبناء غازي أحمد زيني والمدعى عليه ال</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K174" t="n">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: إخطار مطالبة | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 يلدعلا غيلبتلا ةيئاضقلا فيلاكتلا يلدعلا لصاوتلا 1950 ديعاوملا صيخارتلا ةيلدعلا قيثوتلا ذيفنتلا سلافلإا ءاضقلا ... محا نب هماسأ تامولعملا / ابحرم ةحول ةلحرم ءاهنلاا هيلاملا ةكرحلا رشؤم الدائرة تاريخ تقديم ةمكحملا دنسلا عون دنسلا </t>
+          <t>النوع: إخطار مطالبة | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية محا نب هماسأ تامولعملا / ابحرم ةحول ةلحرم ءاهنلاا هيلاملا ةكرحلا رشؤم الدائرة تاريخ تقديم الطلب الصفة في نوع السند</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: منصة ناجز AM 9:02 ,10/3/23 بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 مقر ذيفنت بلط بلطلا ميدقت ينمزلا طخلا بلطلا تانايب نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 ... محا نب هماسأ / ابحرم https://new.najiz.sa/applications/iexecution/Request</t>
+          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: 10/3/23, 9:02 AM زجان ةصنم بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 دليل المرخصين بيانات الطلب الخط الزمني تقديم الطلب طلب تنفيذ رقم ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 ... محا نب هماسأ / ابحرم https://new.najiz.sa/applications/iexecution/Request</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 1423/02/20، 1431/09/20، 1431/09/25، 1431/11/29 | مقتطف: التنفيذيون ةيريلاكلا تاراشتسا دلو ةاماحملا نورقلا ةكرش التاريخ : ١٤٤٥/٠٧/١٣ هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم ( </t>
+          <t xml:space="preserve">النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 1423/02/20، 1431/09/20، 1431/09/25، 1431/11/29 | مقتطف: التنفيذيون شركة القرون المحاماة ولد استشارات الكاليرية التاريخ : ١٤٤٥/٠٧/١٣ هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية بجدة بموجب الصك رقم ( </t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 1423/02/20، 1431/11/29، 1431/9/20، 1434/11/24 | مقتطف: التنفيذيون ةينوناقلا تاراشتسالاو ةاماحملل نوب ريظنتلا ةكرش التاريخ : ١٤٤٥/٠٧/١٣هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية ١٤٤٢/١٢/٢٥هـ بجدة ب</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 1423/02/20، 1431/11/29، 1431/9/20، 1434/11/24 | مقتطف: التنفيذيون شركة التنظير بون للمحاماة والاستشارات القانونية التاريخ : ١٤٤٥/٠٧/١٣هـ أصحاب الفضيلة رئيس وقضاة محكمة الاستئناف التجارية بمحافظة جدة سلمهم الله السلام عليكم ورحمة الله وبركاته، وبعد: الموضوع التماس إعادة نظر على الحكم الصادر من دائرة الاستئناف الثانية بالمحكمة التجارية ١٤٤٢/١٢/٢٥هـ بجدة ب</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا مرحبا أسامه بن احمد بن عباس زيني خدمة الشكوى اإللكترونية االسم األول زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى ةيسنجلا لاوجلا مقر رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 ةيضقلا ليصافت ةرئادلا / ةمكحملا ةيضقلا عون ىلولاا</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا مرحبا أسامه بن احمد بن عباس زيني خدمة الشكوى اإللكترونية االسم األول زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى الجنسية رقم الجوال رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 تفاصيل القضية المحكمة / الدائرة نوع القضية ىلولاا</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000، 500 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمد زيني التاريخ: 1445/04/30هـ بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000، 46,000 ريال | تواريخ هجرية: 01/ 09/ 1442، 01/08/1444، 02/04/1444، 02/12/1432 | مقتطف: الساعة احمد زيني التاريخ: 1445/04/30هـ بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000، 500 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمد رزيني التاريخ: 1445/04/30هـ بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الح</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000، 50,000 ريال | تواريخ هجرية: 01/ 09/ 1442، 01/08/1444، 02/04/1444، 02/12/1432 | مقتطف: الساعة احمد رزيني التاريخ: 1445/04/30هـ بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الح</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمت رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد: ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك </t>
+          <t xml:space="preserve">النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمت رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد: ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك </t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K185" t="n">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/13 | مقتطف: بلطلا عون تاريخ الاضافة إعادة فتح الشكوى 1445/11/13 الملاحظة معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء .. سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم رقم ( 453024</t>
+          <t>النوع: مذكرة قضائية | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/13 | مقتطف: نوع الطلب تاريخ الاضافة إعادة فتح الشكوى 1445/11/13 الملاحظة معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء .. سلمه الله السلام عليكم ورحمة الله وبركاته .. وبعد: الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك الحكم رقم ( 453024</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K186" t="n">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/13 | مقتطف: حالة الشكوى: تم معالية الطلب عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما قررته المادة (176) من نظام مكاعري هللاو مكلصاوت مكل نيركاش ةيعرشلا تاعفارملا ةعجارملا تحت لاز امو لسرم حتف ةداعا بلط كي</t>
+          <t>النوع: تقرير خبرة | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف | قضايا: 42824717 | صكوك: 4530241622 | تواريخ هجرية: 1445/11/13 | مقتطف: حالة الشكوى: تم معالية الطلب عزيزي المستفيد من خدمات المجلس الأعلى للقضاء تحية طيبة وبعد... فنفيدكم أن شكواكم محل اهتمامنا وتمت دراستها وتبين أن الاعتراض على الأحكام محكوم وفقا لما قررته المادة (176) من نظام المرافعات الشرعية شاكرين لكم تواصلكم والله يرعاكم يوجد لديك طلب اعادة فتح مرسل وما زال تحت ا</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: بسم الله الرحمن الرحيم عقد بيع إنه في مدينة جدة وبتاريخ 20 / 9 / 1431هـ تم الاتفاق بين كلا من : الطرف الأول / أحمد عباس زيني ينيز دمحأ هماسأ / يناثلا فرطلا تمهيد حيث أن الطرف الأول يملك حصص في شركة أحمد زيني التجارية سجل تجاري : 4030169102 بعدد (450) حصة وحيث أن الطرف الثاني مدير الشركة المذكورة أعل</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: بسم الله الرحمن الرحيم عقد بيع إنه في مدينة جدة وبتاريخ 20 / 9 / 1431هـ تم الاتفاق بين كلا من : الطرف الأول / أحمد عباس زيني الطرف الثاني / أسامه أحمد زيني تمهيد حيث أن الطرف الأول يملك حصص في شركة أحمد زيني التجارية سجل تجاري : 4030169102 بعدد (450) حصة وحيث أن الطرف الثاني مدير الشركة المذكورة أعل</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 100,000,000، 1,000 ريال | تواريخ هجرية: 10/ 2 / 1434، 1411/08/03، 1413/10/26، 15 / 2 / 1434 | مقتطف: untitled الملكة العربية السعودية وزارة العدل وزارة العدل الموضوع : الرقم ٣٤٧٤٩ التاريخ : ١٠/ ٢ / ١٤٣٤ هـ المرفقات : ةدج ةظفاحمب ةراجتلا ةرازو عرف ماع ريدم ةداعس سلمه الله السلام عليكم ورحمة الله وبركاته وبعد إشارة إلى خطاب سعادتكم رقم : ٦١٦٠٨٩ وتاريخ ٢٧/ ١١ / ١٤٣٩هـ والمقيد لدينا بالرقم : ٣٤٧١٤٩ وتا</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 100,000,000، 46,000، 1,000 ريال | تواريخ هجرية: 10/ 2 / 1434، 1411/08/03، 1413/10/26، 15 / 2 / 1434 | مقتطف: untitled الملكة العربية السعودية وزارة العدل وزارة العدل الموضوع : الرقم ٣٤٧٤٩ التاريخ : ١٠/ ٢ / ١٤٣٤ هـ المرفقات : سعادة مدير عام فرع وزارة التجارة بمحافظة جدة سلمه الله السلام عليكم ورحمة الله وبركاته وبعد إشارة إلى خطاب سعادتكم رقم : ٦١٦٠٨٩ وتاريخ ٢٧/ ١١ / ١٤٣٩هـ والمقيد لدينا بالرقم : ٣٤٧١٤٩ وتا</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 500,000، 1,000 ريال | تواريخ هجرية: 10/ 2 / 1434، 1392/2/15، 1433/11/21، 1438/3/14 | مقتطف: untitled لدعلا ةرازو ةرحلا ةيحلا ةكلملا وزارة العدل الموضوع : الرقم : ٣٤/٧٠٥٠ التاريخ: ١٠/ ٢ / ١٤٣٤ هـ المرفقات : ةدج ةظفاحمب ةراجتلا ةرازو عرف ماع ريدم ةداعس سلمه الله السلام عليكم ورحمة الله وبركاته ...... وبعد إشارة إلى خطاب سعادتكم رقم : ٦٦١٦٠٩٠ وتاريخ ٢٧ / ١١ /٢٤ ١٤هـ -اجتلا نيز دمحأ ةكرش دقع ل</t>
+          <t>النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | مبالغ: 500,000، 1,000 ريال | تواريخ هجرية: 10/ 2 / 1434، 1392/2/15، 1433/11/21، 1438/3/14 | مقتطف: untitled الملكة الحية الحرة وزارة العدل وزارة العدل الموضوع : الرقم : ٣٤/٧٠٥٠ التاريخ: ١٠/ ٢ / ١٤٣٤ هـ المرفقات : سعادة مدير عام فرع وزارة التجارة بمحافظة جدة سلمه الله السلام عليكم ورحمة الله وبركاته ...... وبعد إشارة إلى خطاب سعادتكم رقم : ٦٦١٦٠٩٠ وتاريخ ٢٧ / ١١ /٢٤ ١٤هـ والمقيد لدينا بالرقم : ١٥٠</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901، 6,061,304 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمد رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك ا</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة، محكمة الاستئناف / دائرة الاستئناف، المحكمة العامة بجدة | قضايا: 42824717 | صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929، 79,924,901 ريال | تواريخ هجرية: 01/08/1444، 02/04/1444، 02/12/1432، 08/04/1445 | مقتطف: الساعة احمد رزيني التاريخ: 1445/11/13ه. بسم الله الرحمن الرحيم Ossama A. Zainy معالي الدكتور/ وليد بن محمد الصمعاني وزير العدل ورئيس المجلس الأعلى للقضاء السلام عليكم ورحمة الله وبركاته .. وبعد ،، سلمه الله الموضوع / شكوى ضد رئيس وأعضاء دائرة الاستئناف الثانية بالمحكمة التجارية بجدة الصادر عنها صك ا</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: بسم الله الرحمن الرحيم صلاح الحجيلات للمحاماة والاستشارات القانونية منذ ١٩٦٨ (ذ.م.م) بالتعاون مع فريشفيلدز بروكهاوس ديرنغر ( تقرير ) دة فرع جـ ص.ب ١٥١٤١ جدة ٢١٤٤٤ ترخيص (٢٧/١٧٦) هاتف: ۱۹۸۵۸۸۸-۰۱۲ فاكس: ۲۸۲۱۲۷۷-۰۱۲ بريد الكتروني : Lfalijeddah@hejallanlaw.com الموقع : Web: www.hajailanlaw.com المملكة </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة، الدائرة الأولى التجارية | قضايا: 42824717 | مقتطف: بسم الله الرحمن الرحيم (م.م.ذ) ١٩٦٨ ذنم ةينوناقلا تاراشتسالاو ةاماحملل تاليجحلا حالص بالتعاون مع فريشفيلدز بروكهاوس ديرنغر ( تقرير ) دة فرع جـ ص.ب ١٥١٤١ جدة ٢١٤٤٤ ترخيص (٢٧/١٧٦) هاتف: ۱۹۸۵۸۸۸-۰۱۲ فاكس: ۲۸۲۱۲۷۷-۰۱۲ بريد الكتروني : Lfalijeddah@hejallanlaw.com الموقع : Web: www.hajailanlaw.com المملكة </t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | تواريخ هجرية: 1443/01/03، 1443/01/04، 1443/01/08، 1443/01/09 | مقتطف: ٧E٥A٢E٢A٨٣١B٢C٢٥٤٥A٩٤٠١٤٣C٧٠ أسامه بن احمد بن عباس زيني م ١٢:٥٨ تقولا ١٤٤٣/٠١/٠٣ : خيراتلا مواعيد وتبادل مذكرات ومستندات بیانات الدعوى ١٤٤٣/٠١/٠٣ خیراتلا ءاعبرلاا مویلا ١٤٤٢ ماعل عاتقة محمديحيى محمدعلي الحرازي,وآخرون المدعي الدائرة رقم الدعوى ھیلع یعدملا لدابتلاو عاديلإا ديعاوم عدنان احمد عباس زيني </t>
+          <t xml:space="preserve">النوع: مذكرة قضائية | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | تواريخ هجرية: 1443/01/03، 1443/01/04، 1443/01/08، 1443/01/09 | مقتطف: ٧E٥A٢E٢A٨٣١B٢C٢٥٤٥A٩٤٠١٤٣C٧٠ أسامه بن احمد بن عباس زيني م ١٢:٥٨ تقولا ١٤٤٣/٠١/٠٣ : خيراتلا مواعيد وتبادل مذكرات ومستندات بیانات الدعوى ١٤٤٣/٠١/٠٣ خیراتلا ءاعبرلاا مویلا ١٤٤٢ ماعل عاتقة محمديحيى محمدعلي الحرازي,وآخرون المدعي الدائرة رقم الدعوى ھیلع یعدملا مواعيد اإليداع والتبادل عدنان احمد عباس زيني </t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية محا نب هماسأ تامولعملا / ابحرم ةحول ةلحرم ءاهنلاا هيلاملا ةكرحلا رشؤم الدائرة تاريخ تقديم الطلب الصفة في نوع السند</t>
+          <t>النوع: حكم / صك | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية لوحة مرحبا / المعلومات أسامه بن احم ةلحرم ءاهنلاا مؤشر الحركة الماليه الدائرة تاريخ تقديم الطلب الصفة في نوع السند</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير طبي | الأطراف: أسامة زيني | تواريخ هجرية: 1445/03/24، 1445/03/25، 1445/03/28، 1445/03/29 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 3991 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية محا نب هماسأ تامولعملا / ابحرم ةحول 46 رارق ليصافت رارقلا ةلاح فعال رقم 400464504823219 رارقلا رادصإ تقو 7:17:05 ص</t>
+          <t>النوع: تقرير طبي | الأطراف: أسامة زيني | تواريخ هجرية: 1445/03/24، 1445/03/25، 1445/03/28، 1445/03/29 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 3991 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية تفاصيل قرار 46 لوحة مرحبا / المعلومات أسامه بن احم رارقلا ةلاح فعال رقم 400464504823219 رارقلا رادصإ تقو 7:17:05 ص</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: محضر | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 3,000,000 ريال | تواريخ هجرية: 10-07-1434 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن = من عبا شرکةس تخارج زين أباري .279*000,750,136 وزیني ( ١٤٢٨ ) : أسامه بن احمد بن عباس زيني 250,153,38 حصة الشیخ أحمد عباس زیني ( ١٤٢٩ ماعل ةمیقلا) 178,223,956.69*.279 228,785,567 ةیراقعلا ي:ينیز نيز لامعلأل :ةکرشلا سابع x سةفایضلا نم .779 دمحأ ينیز ابع = </t>
+          <t>النوع: محضر | الأطراف: أسامة زيني، أحمد زيني (المورّث) | تواريخ هجرية: 10-07-1434 | مقتطف: أسامه بن احمد بن عباس زيني أسامه بن احمد بن = من عبا شرکةس تخارج زين أباري .279*000,750,136 وزیني ( ١٤٢٨ ) : أسامه بن احمد بن عباس زيني 250,153,38 حصة الشیخ أحمد عباس زیني ( ١٤٢٩ ماعل ةمیقلا) 178,223,956.69*.279 228,785,567 ةیراقعلا ي:ينیز 483.92,724,49 آل 956.69,223,178 = الشیخ شرکة = عبا زیني أحمد</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">النوع: عقد / اتفاقية | المحاكم: ديوان المظالم | تواريخ هجرية: 02 / 12 / 1432، 1431 / 10 / 16، 1434 / 02 / 10 | مقتطف: ان المورث نقل الحصص بتاریخ : صفة المدعي حیث عدم ھـ ١٤٣٤ / ٠٢ / ١٠ الغبن ، ثم تم تخارج االخوة في حصصھم بتاریخ : ) أعوام ولم یدعي ٧ ھـ وبقي بعدھا علی قید الحیاة لمدة ( ١٤٣١ / ١٠ / ١٦ . ایضا ولم یدعو الغبن وبعد وفاة المورث رفعو دعوى الغبن في قیمة حصة السھم عند شرائي ھـ ، مما یدل عدم صفتھم فالدعوى ١٤٣١ </t>
+          <t xml:space="preserve">النوع: عقد / اتفاقية | المحاكم: ديوان المظالم | تواريخ هجرية: 1431 / 10 / 16، 1432 / 12 / 02، 1434 / 02 / 10 | مقتطف: ان المورث نقل الحصص بتاریخ : صفة المدعي حیث عدم ھـ ١٤٣٤ / ٠٢ / ١٠ الغبن ، ثم تم تخارج االخوة في حصصھم بتاریخ : ) أعوام ولم یدعي ٧ ھـ وبقي بعدھا علی قید الحیاة لمدة ( ١٤٣١ / ١٠ / ١٦ . ایضا ولم یدعو الغبن وبعد وفاة المورث رفعو دعوى الغبن في قیمة حصة السھم عند شرائي ھـ ، مما یدل عدم صفتھم فالدعوى ١٤٣١ </t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: 10/3/23, 9:02 AM زجان ةصنم بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 دليل المرخصين بيانات الطلب الخط الزمني تقديم الطلب طلب تنفيذ رقم ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 ... محا نب هماسأ / ابحرم https://new.najiz.sa/applications/iexecution/Request</t>
+          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: 10/3/23, 9:02 AM زجان ةصنم بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 دليل المرخصين بيانات الطلب الخط الزمني تقديم الطلب طلب تنفيذ رقم ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 1/4 _QqMcKhm0j-pA-anKTqv4PZKLbIuKCUlN6BzYabVx-I...\_w7MnkTUnuxaoXwSot76\CfDJ8</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>النوع: حكم / صك | الأطراف: عدنان زيني، عاتقة الحرازي | مقتطف: أسامھ بن احمد بن عباس زيني تاكرشلا من والتخارج ينيز التنازل سابع إثبات نحكم أسامھ بن احمد ب أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسام</t>
+          <t>النوع: حكم / صك | الأطراف: عدنان زيني، عاتقة الحرازي | مقتطف: أسامھ بن احمد بن عباس زيني تاكرشلا مكحن تابثإ عباس لزانتلا زيني جراختلاو نم أسامھ بن احمد ب أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسامھ بن احمد بن عباس زيني أسامھ بن احمد بن عبا أسام</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>منطقي</t>
+          <t>OCR مُصحَّح</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>OCR مُصحَّح</t>
+          <t>منطقي</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 19,000,500، 35,000، 1,318 ريال | تواريخ هجرية: 03/05/1433، 1/2/1433، 1433/02/20، 1433/03/21 | مقتطف: ===== ملف داخلي: ‏‏1433 - نسخة/1433 fil no 12 inv 1237.pdf ===== [صفحة 1 - OCR] 15.04.12 16.04.12 16.04.12 21.04.12 21.04.12 24.04.12 26.04.12 26.04.12 29.04.12 30.04.12 30.04.12 قمأشارة ‎Ref. wo‏ - 11245 #11254 +11293 +14295 711301 -11306 AP100007244 211322 - 11324 ~ 11326 ~ 11328 ~ 11330 - 11369 “</t>
+          <t>النوع: تقرير خبرة | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مبالغ: 19,000,500 ريال | تواريخ هجرية: 03/05/1433، 1/2/1433، 1433/02/20، 1433/03/21 | مقتطف: ===== ملف داخلي: ‏‏1433 - نسخة/1433 fil no 12 inv 1237.pdf ===== [صفحة 1 - OCR] 15.04.12 16.04.12 16.04.12 21.04.12 21.04.12 24.04.12 26.04.12 26.04.12 29.04.12 30.04.12 30.04.12 قمأشارة ‎Ref. wo‏ - 11245 #11254 +11293 +14295 711301 -11306 AP100007244 211322 - 11324 ~ 11326 ~ 11328 ~ 11330 - 11369 “</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>منطقي</t>
+          <t>OCR مُصحَّح</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>النوع: مستند مالي | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: ينيز سابع نب دمحا نب هماسأ [العنوان مكرر مرات عديدة بترميز معكوس عبر المستند بالكامل] [ملاحظة المعالجة: ملف بعنوان "جزء من مسحوبات مصروفات الشيخ أحمد زيني رحمه الله". ملف PDF حجمه نحو 872 كيلوبايت. النص المستخرج بالكامل عبارة عن العنوان "أسامة بن أحمد بن عباس زيني" مكرر بترميز عربي معكوس عبر المستند</t>
+          <t>النوع: مستند مالي | الأطراف: أسامة زيني، أحمد زيني (المورّث) | مقتطف: أسامه بن احمد بن عباس زيني [ملاحظة المعالجة: ملف بعنوان "جزء من مسحوبات مصروفات الشيخ أحمد زيني رحمه الله". ملف PDF حجمه نحو 872 كيلوبايت. النص المستخرج بالكامل عبارة عن العنوان "أسامة بن أحمد بن عباس زيني" مكرر بترميز عربي معكوس عبر المستند، ولا يحتوي على بيانات جدول مالية قابلة للاستخراج النصي (ال</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: خدمة الشكوى الإلكترونية :. المجلس الأعلى للقضاء مرحبا أسامه بن احمد بن عباس زيين اإللكرتونية بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا االسم األول الرئيسية زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى الجنسية رقم الجوال رقم الهوية أصالة ع</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: خدمة الشكوى الإلكترونية :. المجلس الأعلى للقضاء مرحبا أسامه بن احمد بن عباس زيين اإللكرتونية بيانات مقدم الشكوى جورخ ةلئاعلا معدلاو مسا لصاوتلا زكرم تيانايب دجلا مسا ةلمتكم يرغ تابلط بلأا تيابلط مسا ةيسيئرلا لولأا مسلاا زيني بن عباس بن احمد أسامه صفة مقدم الشكوى الجنسية رقم الجوال رقم الهوية أصالة ع</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° °ó بيانات مقدم الشكوى ·°ó بيانات القضية المحكمة المحكمة التج ةلئاعلا مسا نييز خي راتلا 1445/06/18 رقم الجوال 56355663 دجلا مسا سابع نب يراجت</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | المحاكم: المحكمة العليا | قضايا: 42824717 | تواريخ هجرية: 1445/01/05، 1445/04/30، 1445/06/18 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó الصفحة الرئيسية خدمة الشكوى اإللكرتونية الصفحة الرئيسية ó° °ó شكوى جديدة ىواكشلا ةمئاق ó°· بلطلا ةجلاعم مت ó° °ó بيانات مقدم الشكوى ·°ó بيانات القضية المحكمة المحكمة التج ةلئاعلا مسا نييز خي راتلا 1445/06/18 رقم الجوال 56355663 دجلا مسا بن عباس يراجت</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت تار يخ تسليم الحكم 1445/01/01 ó°3⁄4 ةلئاعلا مسا نييز تار يخ النطق بالحكم 1445/01/01 °ó بيانات مقدم الشكوى دجلا مسا سابع نب رقم الجوال 556</t>
+          <t>النوع: شكوى | الأطراف: أسامة زيني | قضايا: 42824717 | صكوك: 4431025114 | تواريخ هجرية: 1445/01/01 | مقتطف: خدمة الشكوي الإلكترونية | المجلس الأعلى للقضاء °ó خدمة الشكوى اإللكرتونية شكوى جديدة شكوى جديدة ó° °ó معاينة الشكوى ·°ó تفاصيل الشكوى 4⁄1­±ó نوع الشكوى °ó بيانايت تار يخ تسليم الحكم 1445/01/01 ó°3⁄4 ةلئاعلا مسا نييز تار يخ النطق بالحكم 1445/01/01 °ó بيانات مقدم الشكوى دجلا مسا بن عباس رقم الجوال 556</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية محا نب هماسأ تامولعملا / ابحرم ةحول ةلحرم ءاهنلاا هيلاملا ةكرحلا رشؤم الدائرة تاريخ تقديم الطلب الصفة في نوع السند</t>
+          <t>النوع: إخطار مطالبة | الأطراف: أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 08/04/1445، 1445-4-7، 1445/04/08 | مقتطف: ثحبلل نيصخرملا ليلد ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ انه بتكا 4024 التبليغ العدلي التكاليف القضائية التواصل العدلي 1950 ديعاوملا صيخارتلا ... القضاء اإلفالس التنفيذ التوثيق العدلية لوحة مرحبا / المعلومات أسامه بن احم ةلحرم ءاهنلاا مؤشر الحركة الماليه الدائرة تاريخ تقديم الطلب الصفة في نوع السند</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: 10/3/23, 9:02 AM زجان ةصنم بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 دليل المرخصين بيانات الطلب الخط الزمني تقديم الطلب طلب تنفيذ رقم ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 ... محا نب هماسأ / ابحرم https://new.najiz.sa/applications/iexecution/Request</t>
+          <t>النوع: إخطار مطالبة | الأطراف: عدنان زيني، أسامة زيني، أحمد زيني (المورّث) | المحاكم: المحكمة التجارية بجدة | قضايا: 42824717 | تواريخ هجرية: 1445-3-13، 1445/03/16، 16/03/1445 | مقتطف: 10/3/23, 9:02 AM زجان ةصنم بلطلا ليصافت رجوع لوحة المعلومات / التنفيذ / قيد التنفيذ 401024501215577 دليل المرخصين بيانات الطلب الخط الزمني تقديم الطلب طلب تنفيذ رقم ةينورتكللإا تامدخلا عيمج ققحتلا تامدخ ثحبلل انه بتكا 3933 1/4 _QqMcKhm0j-pA-anKTqv4PZKLbIuKCUlN6BzYabVx-I...\_w7MnkTUnuxaoXwSot76\CfDJ8</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا مرحبا أسامه بن احمد بن عباس زيني خدمة الشكوى اإللكترونية االسم األول زيني سابع نب بن احمد هماسأ صفة مقدم الشكوى الجنسية رقم الجوال رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 تفاصيل القضية المحكمة / الدائرة نوع القضية ىلولاا</t>
+          <t>النوع: شكوى | الأطراف: عدنان زيني، أسامة زيني | المحاكم: المحكمة التجارية بجدة، المحكمة العليا | قضايا: 42824717 | صكوك: 4530241622 | مقتطف: بيانات مقدم لشكوى ةلئاعلا مسا دجلا مسا بلأا مسا مرحبا أسامه بن احمد بن عباس زيني خدمة الشكوى اإللكترونية االسم األول زيني بن عباس بن احمد أسامه صفة مقدم الشكوى الجنسية رقم الجوال رقم الهوية أصالة عن نفسه المملكة العربية السعودية 0556355663 1008017301 تفاصيل القضية المحكمة / الدائرة نوع القضية الدائر</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
+++ b/zaini_case_audit_output/outputs/excel/00_master_documents.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="كل المستندات" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بطاقات التعريف" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12828,4 +12829,8225 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K196"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>العنوان</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>نوع المستند</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>الجهة المصدِرة</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>الدائرة</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>رقم القضية</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الصك/الحكم</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>الأطراف</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>مبالغ بارزة</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ملف Word</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>كتابة العدل</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>وكالة</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>المحكمة العامة</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1,769,886,051 ريال</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>إخطار بمطالبة مالية مقدم بتاريخ 14/7/2024م والخاص بالمبلغ المحكوم به للسيد/ عدنان زيني، في صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (96,779,270) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>14/7/2024</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>عدنان زيني</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>اقرار من الوالدة عاتقة توكيل الثعلي في الدعوى 42824717 ضد اسامة زيني ـ 04-03-1445.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>وكالة</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>04-03-1445</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4530828230</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>25/08/1445</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>02/06/1446</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>الدائرة الأولى</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16-07-1446</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>27/6/2011</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,690,483، 2,463,761 ريال</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف / دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>17-04-2025</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى المقيدة برقم (42824717) وقضية أرض التنس.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10/02/1447</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>تقييم العيوطي للشركات.pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>جدول مواعيد تبادل المذكرات والمستندات في الدعوى رقم (4717) لعام 1442هـ أمام الدائرة التجارية الأولى في الدعوى المقامة من عدنان زيني ضد عاتقة وآخرون. ـ —</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>المحكمة العامة</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>الدائرة الأولى</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>٣٤٢٨١٤٤٩</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>26-07-1434</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,700,000,000، 370,000,000، 120,000,000 ريال</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>المحكمة العامة</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>الدائرة الأولى</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>٣٣٢٨٦٣٩٢</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>08-06-1433</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>450 ريال</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>خطاب وزارة التجارة بتوثيق تخارج المدعين من شركة احمد زيني واولاده ـ 10-02-1434 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>مراسلة</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10-02-1434</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>25/08/1445</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>التفتيش القضائي</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>16-07-2025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1447/02/13</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>صحيفة دعوى</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>17-12-1442</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-01-1445</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>372,426,828، 368,757,931، 120,000,000 ريال</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>02-12-1432</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>8,849,447,678، 184,887,445، 8,844,470 ريال</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>18-06-1446</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>25-08-1445</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>478,757,110، 368,757,931، 11,574,017 ريال</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>الدائرة الخامسة</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>13-03-1445</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>368,757,931، 367,757,931، 331,882,138 ريال</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>13-11-1445</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>13/03/1445</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>عقد بيع حصص الشيخ احمد زيني في شركة احمد زيني التجارية الى اسامة ـ 20-09-1431.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>20-09-1431</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>قرار تطبيق المادة (46) على السيد/ أسامة الزيني بخصوص طلب التنفيذ المقدم من السيد/ عدنان. ـ —</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>تقرير طبي</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ما يفيد استلام السيد/ سليمان السديري أصل عقد البيع موضوع الدعوى والمبرم بين السيد/ أسامة زيني والمورث. ـ —</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>20/ 9 / 1431</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>محضر اجتماع تقسيم شركات ابار وزيني و شيكات الامير احمد و بيان شيكات القروض البنكية.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>محضر تفويض المحكمة وكيل السيد/ عدنان تحديث صك أرض الروضة بموجب طلب الإفلاس المقدم من عدنان رقم (405034600730696) وتاريخ 24/1/1446هـ ـ 24/1/1446هـ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>24/1/1446</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>محضر رفع التصرف على صك أرض التنس بموجب طلب الإفلاس من عدنان رقم (405034600788314) وتاريخ 23/03/1446هـ. ـ 23/03/1446هـ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>23/03/1446</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>250,000,000، 217,250,000، 172,613,467 ريال</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>مرفقات تقييم شركة احمد زيني التجارية مرة بمبلغ 68 مليون ومرة بمبلغ 79 مليون.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>16-10-1431</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>500,000، 450,000، 1,000 ريال</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5/10/2011</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1,037,259,019، 172,613,467، 14,282,008 ريال</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>وكالة الجدة عاتقة الى محمد الثعلي ـ في 19-03-1445 ـ تنتهي 19-03-1446.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>وكالة</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>19-03-1445</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>08-04-1445</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>إخطار مطالبة</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>16-03-1445</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ديوان المظالم</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3,681,664,891، 3,048,489,219، 1,840,832,446 ريال</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>إخطار مطالبة</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>96779270</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96,779,270، 27,651,219 ريال</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>03-01-1443</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>تقديم التماس إعادة نظر في القضية من عدنان وعاتقة ـ 03-12-2024</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>03-12-2024</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>تقرير جلسة القضية ـ 17-12-2024</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>17-12-2024</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>المحكمة العامة</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>٣٨٥٥٨٤٩</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>25-10-1438</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>368,000,000، 120,000,000، 450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>صورة رفض مذكرة طلب النقض ـ 10-04-1445</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10-04-1445</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>محضر جلسة دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4630548401</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>09/09/1447</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامة ـ 20-10-2025 ـ أبو راشد</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>20-10-2025</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامة ـ 29-04-1447</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>29-04-1447</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>02-09-1447</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>المحكمة العامة</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>٣٨٥٥٨٤٩</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>368,000,000، 120,000,000، 450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>13-04-1447</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>330272727</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>87١41١41١1</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>22-07-1447</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>حكما إثبات التنازل والتخارج وإبراء الذمة ومستندات التنازل</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>عدنان زيني، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ردود على حكم الالتماس 717</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>إخطار مطالبة</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>25/08/1445</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>طلب الاعتراض بالنقض ـ 2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1447 / 10 / 07</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>طلب الاعتراض على حكم الدرجة الأولى ـ 15-07-1447 ـ ناجز</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>15-07-1447</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>طلب التماس 20-10-2025 ـ ناجز</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>20-10-2025</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>طلب التماس 20-10-2025 ـ ناجز (صورة)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>20-10-2025</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>طلب النقض 23-09-1445 ـ رقم 45117602 ـ محال للعليا</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>45117602</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>23-09-1445</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>طلب النقض الاحير المقدم في 07-10-1447 ـ القضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>07-10-1447</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>25-02-1446</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>عقود تعيين الشيخ أسامة في إدارة الشركات</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>لائحة المدعي بتفصيل مبلغ الحكم الابتدائي ـ 01-02-1445</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01-02-1445</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20/09/1431</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>120,000,000 ريال</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>28-01-2026</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>4431025114</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>28-01-2026</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>120,000,000 ريال</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>مذكرة الاستئناف اعتراضاً على الدرجة الأولى ـ 15-07-1447</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>15-07-1447</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>8-8-1445</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>368,757,931، 450,000، 170 ريال</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>13-07-1445</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>10-04-1445</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>23-09-1445</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>06-03-1445</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>02-09-1447</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>16-8-1445</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>135، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>4630548401</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>28-08-1447</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>15-08-1445</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>135 ريال</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>16-11-1444</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>أسامة زيني، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>الدائرة الخامسة</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>100,000,000، 5,000,000، 500,000 ريال</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>مذكرة طلب النقض ـ الحجيلان ـ 13-07-1446 ـ أحيلت</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>13-07-1446</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>مذكرة من المحامي السديري 20-02-1445 ـ الاعتراض على تقرير ابو غزالة.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>20-02-1445</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>مذكرة نقض؟ .docx</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>05-07-1434</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>500,000، 1,000 ريال</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>مرفق 2 ـ مذكرة أبو راشد ـ 04-01-1443</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>04-01-1443</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>23-01-1443</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>500,000، 450,000، 1,000 ريال</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>مرفق 4 ـ مذكرة أبو راشد ـ 28-01-1443</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>28-01-1443</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>15-03-1443</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>مرفق 7 ـ مذكرة أبو راشد ـ 27-03-1443</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>المحكمة العامة بجدة</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>43281449</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>27-03-1443</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>06-03-1443</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>25-04-1443</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>01-08-1444</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>27-01-1444</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>01-08-1444</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>15-08-1444</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>29-08-1444</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>20-09-1444</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>19-10-1444</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>03-11-1444</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>10-11-1444</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>10-11-1444</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17-11-1444</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1,000,070 ريال</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>17-11-1444</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>24-11-1444</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>120 ريال</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>الدائرة الاولى</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>24-11-1444</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>372,426,828، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>02-12-1444</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>368,757,931، 97,762,042، 27,932,012 ريال</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>محضر</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>الدائرة الخامسة</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>12-02-1445</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>331,882,138، 120,000,000، 110,672,379 ريال</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>المسحوبات 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>المسحوبات 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>المسحوبات 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>المسحوبات 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>20,000، 17,000، 1,000 ريال</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>المسحوبات 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>36,171، 30,000، 25,000 ريال</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>المسحوبات 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>60,900، 60,000، 30,000 ريال</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>المسحوبات 2015 (zip)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>40,901,050، 1,662,326، 1,390,810 ريال</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ملف المسحوبات (Excel)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>وكالة</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>10,851 ريال</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>9,290، 9,240 ريال</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>مصاريف مزرعة الشيخ أحمد زيني بالوادي (1).xlsx</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>13/01/1431</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>excelمصاريف فيلا الشيخ أحمد زيني بالوادي.xlsx</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>05-11-1431</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>19,000,500 ريال</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>556,415 ريال</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>سداد عقد المحاصة (Excel)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>10-07-1434</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>مرفق (1) القروض (zip)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>غير مصنف</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ملف القروض (Excel)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>25-08-1445</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>478,757,110، 368,757,931، 11,574,017 ريال</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>جزء من مسحوبات مصروفات الشيخ احمد زيني رحمه الله.pdf</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات المزرعة</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات فيلا الوادي.pdf</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>مستند مالي</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>13-07-1445</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1445/04/30</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>100,000,000، 500,000، 450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>تفاصيل الشكوى</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1445/04/30</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>30-04-1445</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>21-05-2024</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>13-11-1445</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>الدائرة الرابعة</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>05-11-1445</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>450، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>13-11-1445</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>26/04 /1446</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>450، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>4431025114</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>29-10-2024</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>26-04-1446</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>صفحة 1 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>4431025114</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1445/01/01</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>صفحة 3 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>4431025114</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>1445/01/01</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>4431025114</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1446 / 06 / 09</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>09/06/1446</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>450، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>17/11 /1445</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>450، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1445/11/17</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>79,929,906، 36,877,936، 150,000 ريال</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1445/11/22</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>19-06-1445</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>صورة التقديم (pdf)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد.docx</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>13/03/1445</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>4530828230</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>25/08/1445</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>الدائرة الثانية</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>25/12/1442</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>4,690,483، 2,463,761 ريال</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>-05-11~1.DOC.docx</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>الدائرة الرابعة</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>05/11 /1445</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>450، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>إخطار مطالبة</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>إخطار مطالبة</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>المحكمة التجارية بجدة</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>المحكمة العليا</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>30-04-1445</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>100,000,000، 500,000، 450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>1445/04/30</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>100,000,000، 500,000، 450,000 ريال</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>30/04/1445</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>450,000، 120 ريال</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>13-11-1445</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>الدائرة الخامسة</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>7١551557١</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>26/7/1434</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>368,757,931، 367,757,931، 331,882,138 ريال</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>مذكرة قضائية</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>21-05-2024</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (2)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>تقرير خبرة</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>محكمة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>21-05-2024</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (3)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>21-05-2024</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>عقد البيع 1431-9-20 حصص الشيخ احمد زيني رحمه الله في شركة احمد زيني التجارية الى الشيخ اسامة ـ القرعاوي 120 مليون.pdf</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>1431-9-20</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>13/03/1445</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>عدنان زيني، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>شكوى</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>13/03/1445</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>10-02-1434</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>100,000,000، 46,000، 1,000 ريال</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>عقد / اتفاقية</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>وزارة العدل</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>10-02-1434</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>500,000، 1,000 ريال</t>
+        </is>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ملف مؤقت tmp</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>حكم / صك</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>دائرة الاستئناف</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>42824717</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>1445/11/13</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>عدنان زيني، أسامة زيني، أحمد زيني (المورّث)، عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>368,757,931، 331,882,138، 137,631,929 ريال</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>📄 فتح</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId182"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>